--- a/VT_REG1_RCA_V12.xlsx
+++ b/VT_REG1_RCA_V12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261015\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCBE59E7-E011-41F4-9AF2-526B00F1C21F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EF296E0-DB84-4FA9-B34F-E3ABBF476D19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="901" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="901" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB1" sheetId="133" r:id="rId1"/>
@@ -8363,453 +8363,6 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="EnergyBalance"/>
-      <sheetName val="EB1"/>
-      <sheetName val="EB2"/>
-      <sheetName val="RES&amp;OBJ"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="16">
-          <cell r="D16">
-            <v>0</v>
-          </cell>
-          <cell r="E16">
-            <v>0</v>
-          </cell>
-          <cell r="G16">
-            <v>0</v>
-          </cell>
-          <cell r="H16">
-            <v>0</v>
-          </cell>
-          <cell r="I16">
-            <v>8.7784635600000005</v>
-          </cell>
-          <cell r="J16">
-            <v>0</v>
-          </cell>
-          <cell r="K16">
-            <v>0</v>
-          </cell>
-          <cell r="L16">
-            <v>0</v>
-          </cell>
-          <cell r="M16">
-            <v>0</v>
-          </cell>
-          <cell r="N16">
-            <v>0</v>
-          </cell>
-          <cell r="O16">
-            <v>29.606118840000001</v>
-          </cell>
-          <cell r="P16">
-            <v>0</v>
-          </cell>
-          <cell r="Q16">
-            <v>0</v>
-          </cell>
-          <cell r="R16">
-            <v>0</v>
-          </cell>
-          <cell r="S16">
-            <v>0</v>
-          </cell>
-          <cell r="T16">
-            <v>0</v>
-          </cell>
-          <cell r="U16">
-            <v>15.231997080000001</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="D17">
-            <v>0</v>
-          </cell>
-          <cell r="E17">
-            <v>0</v>
-          </cell>
-          <cell r="G17">
-            <v>0</v>
-          </cell>
-          <cell r="H17">
-            <v>0</v>
-          </cell>
-          <cell r="I17">
-            <v>5.3591040000000003</v>
-          </cell>
-          <cell r="J17">
-            <v>0</v>
-          </cell>
-          <cell r="K17">
-            <v>0</v>
-          </cell>
-          <cell r="L17">
-            <v>0</v>
-          </cell>
-          <cell r="M17">
-            <v>2.0264112000000001E-2</v>
-          </cell>
-          <cell r="N17">
-            <v>0</v>
-          </cell>
-          <cell r="O17">
-            <v>0</v>
-          </cell>
-          <cell r="P17">
-            <v>0</v>
-          </cell>
-          <cell r="Q17">
-            <v>0</v>
-          </cell>
-          <cell r="R17">
-            <v>0</v>
-          </cell>
-          <cell r="S17">
-            <v>0</v>
-          </cell>
-          <cell r="T17">
-            <v>0</v>
-          </cell>
-          <cell r="U17">
-            <v>11.973410640000001</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="D18">
-            <v>20.32984476</v>
-          </cell>
-          <cell r="E18">
-            <v>0</v>
-          </cell>
-          <cell r="G18">
-            <v>9.3960165599999996</v>
-          </cell>
-          <cell r="H18">
-            <v>0</v>
-          </cell>
-          <cell r="I18">
-            <v>2.8470240000000004E-2</v>
-          </cell>
-          <cell r="J18">
-            <v>0</v>
-          </cell>
-          <cell r="K18">
-            <v>0</v>
-          </cell>
-          <cell r="L18">
-            <v>5.0660280000000002E-2</v>
-          </cell>
-          <cell r="M18">
-            <v>0</v>
-          </cell>
-          <cell r="N18">
-            <v>0</v>
-          </cell>
-          <cell r="O18">
-            <v>60.016103280000003</v>
-          </cell>
-          <cell r="P18">
-            <v>0</v>
-          </cell>
-          <cell r="Q18">
-            <v>0</v>
-          </cell>
-          <cell r="R18">
-            <v>0</v>
-          </cell>
-          <cell r="S18">
-            <v>0</v>
-          </cell>
-          <cell r="T18">
-            <v>0</v>
-          </cell>
-          <cell r="U18">
-            <v>15.341691240000001</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="D19">
-            <v>0</v>
-          </cell>
-          <cell r="E19">
-            <v>0</v>
-          </cell>
-          <cell r="G19">
-            <v>8.9932464000000003</v>
-          </cell>
-          <cell r="H19">
-            <v>0</v>
-          </cell>
-          <cell r="I19">
-            <v>0</v>
-          </cell>
-          <cell r="J19">
-            <v>0</v>
-          </cell>
-          <cell r="K19">
-            <v>0</v>
-          </cell>
-          <cell r="L19">
-            <v>0</v>
-          </cell>
-          <cell r="M19">
-            <v>0</v>
-          </cell>
-          <cell r="N19">
-            <v>0</v>
-          </cell>
-          <cell r="O19">
-            <v>0</v>
-          </cell>
-          <cell r="P19">
-            <v>0</v>
-          </cell>
-          <cell r="Q19">
-            <v>0</v>
-          </cell>
-          <cell r="R19">
-            <v>0</v>
-          </cell>
-          <cell r="S19">
-            <v>4.1868000000000006E-5</v>
-          </cell>
-          <cell r="T19">
-            <v>0</v>
-          </cell>
-          <cell r="U19">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="D20">
-            <v>0</v>
-          </cell>
-          <cell r="E20">
-            <v>0</v>
-          </cell>
-          <cell r="G20">
-            <v>59.234009040000004</v>
-          </cell>
-          <cell r="H20">
-            <v>2.9927246400000005</v>
-          </cell>
-          <cell r="I20">
-            <v>1.2346873199999999</v>
-          </cell>
-          <cell r="J20">
-            <v>28.510014600000005</v>
-          </cell>
-          <cell r="K20">
-            <v>0</v>
-          </cell>
-          <cell r="L20">
-            <v>1.2556213199999999</v>
-          </cell>
-          <cell r="M20">
-            <v>8.1692841600000001</v>
-          </cell>
-          <cell r="N20">
-            <v>0</v>
-          </cell>
-          <cell r="O20">
-            <v>0</v>
-          </cell>
-          <cell r="P20">
-            <v>0</v>
-          </cell>
-          <cell r="Q20">
-            <v>0</v>
-          </cell>
-          <cell r="R20">
-            <v>0</v>
-          </cell>
-          <cell r="S20">
-            <v>0</v>
-          </cell>
-          <cell r="T20">
-            <v>0</v>
-          </cell>
-          <cell r="U20">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="D21">
-            <v>0</v>
-          </cell>
-          <cell r="E21">
-            <v>0</v>
-          </cell>
-          <cell r="G21">
-            <v>0</v>
-          </cell>
-          <cell r="H21">
-            <v>0</v>
-          </cell>
-          <cell r="I21">
-            <v>0</v>
-          </cell>
-          <cell r="J21">
-            <v>0</v>
-          </cell>
-          <cell r="K21">
-            <v>0</v>
-          </cell>
-          <cell r="L21">
-            <v>0</v>
-          </cell>
-          <cell r="M21">
-            <v>0</v>
-          </cell>
-          <cell r="N21">
-            <v>0</v>
-          </cell>
-          <cell r="O21">
-            <v>9.4575625199999998</v>
-          </cell>
-          <cell r="P21">
-            <v>0</v>
-          </cell>
-          <cell r="Q21">
-            <v>0</v>
-          </cell>
-          <cell r="R21">
-            <v>0</v>
-          </cell>
-          <cell r="S21">
-            <v>2.51208E-4</v>
-          </cell>
-          <cell r="T21">
-            <v>1.0048319999999998E-3</v>
-          </cell>
-          <cell r="U21">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="D22">
-            <v>0</v>
-          </cell>
-          <cell r="E22">
-            <v>0</v>
-          </cell>
-          <cell r="G22">
-            <v>0</v>
-          </cell>
-          <cell r="H22">
-            <v>0</v>
-          </cell>
-          <cell r="I22">
-            <v>0</v>
-          </cell>
-          <cell r="J22">
-            <v>0</v>
-          </cell>
-          <cell r="K22">
-            <v>0</v>
-          </cell>
-          <cell r="L22">
-            <v>0</v>
-          </cell>
-          <cell r="M22">
-            <v>0</v>
-          </cell>
-          <cell r="N22">
-            <v>0</v>
-          </cell>
-          <cell r="O22">
-            <v>0</v>
-          </cell>
-          <cell r="P22">
-            <v>0</v>
-          </cell>
-          <cell r="Q22">
-            <v>0</v>
-          </cell>
-          <cell r="R22">
-            <v>0</v>
-          </cell>
-          <cell r="S22">
-            <v>0</v>
-          </cell>
-          <cell r="T22">
-            <v>0</v>
-          </cell>
-          <cell r="U22">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="D23">
-            <v>0</v>
-          </cell>
-          <cell r="E23">
-            <v>0</v>
-          </cell>
-          <cell r="G23">
-            <v>0</v>
-          </cell>
-          <cell r="H23">
-            <v>0</v>
-          </cell>
-          <cell r="I23">
-            <v>0</v>
-          </cell>
-          <cell r="J23">
-            <v>0</v>
-          </cell>
-          <cell r="K23">
-            <v>0</v>
-          </cell>
-          <cell r="L23">
-            <v>0</v>
-          </cell>
-          <cell r="M23">
-            <v>0</v>
-          </cell>
-          <cell r="N23">
-            <v>0</v>
-          </cell>
-          <cell r="O23">
-            <v>0</v>
-          </cell>
-          <cell r="P23">
-            <v>0</v>
-          </cell>
-          <cell r="Q23">
-            <v>0</v>
-          </cell>
-          <cell r="R23">
-            <v>0</v>
-          </cell>
-          <cell r="S23">
-            <v>0</v>
-          </cell>
-          <cell r="T23">
-            <v>0</v>
-          </cell>
-          <cell r="U23">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
       <sheetName val="EB2"/>
       <sheetName val="RES_RCA"/>
       <sheetName val="Sector_Fuels_AGR"/>
@@ -8881,38 +8434,6 @@
             <v>Electricity</v>
           </cell>
         </row>
-        <row r="6">
-          <cell r="D6">
-            <v>19.923749999999998</v>
-          </cell>
-          <cell r="E6">
-            <v>1051.038</v>
-          </cell>
-          <cell r="G6">
-            <v>368.84399999999999</v>
-          </cell>
-          <cell r="H6">
-            <v>1.677</v>
-          </cell>
-          <cell r="I6">
-            <v>31.602</v>
-          </cell>
-          <cell r="J6">
-            <v>5.72</v>
-          </cell>
-          <cell r="L6">
-            <v>19.32</v>
-          </cell>
-          <cell r="M6">
-            <v>0.24199999999999999</v>
-          </cell>
-          <cell r="O6">
-            <v>13</v>
-          </cell>
-          <cell r="U6">
-            <v>1263.6955</v>
-          </cell>
-        </row>
         <row r="20">
           <cell r="C20" t="str">
             <v>OT</v>
@@ -8967,6 +8488,453 @@
       <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
       <sheetData sheetId="9"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="EnergyBalance"/>
+      <sheetName val="EB1"/>
+      <sheetName val="EB2"/>
+      <sheetName val="RES&amp;OBJ"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="16">
+          <cell r="D16">
+            <v>0</v>
+          </cell>
+          <cell r="E16">
+            <v>0</v>
+          </cell>
+          <cell r="G16">
+            <v>0</v>
+          </cell>
+          <cell r="H16">
+            <v>0</v>
+          </cell>
+          <cell r="I16">
+            <v>8.7784635600000005</v>
+          </cell>
+          <cell r="J16">
+            <v>0</v>
+          </cell>
+          <cell r="K16">
+            <v>0</v>
+          </cell>
+          <cell r="L16">
+            <v>0</v>
+          </cell>
+          <cell r="M16">
+            <v>0</v>
+          </cell>
+          <cell r="N16">
+            <v>0</v>
+          </cell>
+          <cell r="O16">
+            <v>29.606118840000001</v>
+          </cell>
+          <cell r="P16">
+            <v>0</v>
+          </cell>
+          <cell r="Q16">
+            <v>0</v>
+          </cell>
+          <cell r="R16">
+            <v>0</v>
+          </cell>
+          <cell r="S16">
+            <v>0</v>
+          </cell>
+          <cell r="T16">
+            <v>0</v>
+          </cell>
+          <cell r="U16">
+            <v>15.231997080000001</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="D17">
+            <v>0</v>
+          </cell>
+          <cell r="E17">
+            <v>0</v>
+          </cell>
+          <cell r="G17">
+            <v>0</v>
+          </cell>
+          <cell r="H17">
+            <v>0</v>
+          </cell>
+          <cell r="I17">
+            <v>5.3591040000000003</v>
+          </cell>
+          <cell r="J17">
+            <v>0</v>
+          </cell>
+          <cell r="K17">
+            <v>0</v>
+          </cell>
+          <cell r="L17">
+            <v>0</v>
+          </cell>
+          <cell r="M17">
+            <v>2.0264112000000001E-2</v>
+          </cell>
+          <cell r="N17">
+            <v>0</v>
+          </cell>
+          <cell r="O17">
+            <v>0</v>
+          </cell>
+          <cell r="P17">
+            <v>0</v>
+          </cell>
+          <cell r="Q17">
+            <v>0</v>
+          </cell>
+          <cell r="R17">
+            <v>0</v>
+          </cell>
+          <cell r="S17">
+            <v>0</v>
+          </cell>
+          <cell r="T17">
+            <v>0</v>
+          </cell>
+          <cell r="U17">
+            <v>11.973410640000001</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="D18">
+            <v>20.32984476</v>
+          </cell>
+          <cell r="E18">
+            <v>0</v>
+          </cell>
+          <cell r="G18">
+            <v>9.3960165599999996</v>
+          </cell>
+          <cell r="H18">
+            <v>0</v>
+          </cell>
+          <cell r="I18">
+            <v>2.8470240000000004E-2</v>
+          </cell>
+          <cell r="J18">
+            <v>0</v>
+          </cell>
+          <cell r="K18">
+            <v>0</v>
+          </cell>
+          <cell r="L18">
+            <v>5.0660280000000002E-2</v>
+          </cell>
+          <cell r="M18">
+            <v>0</v>
+          </cell>
+          <cell r="N18">
+            <v>0</v>
+          </cell>
+          <cell r="O18">
+            <v>60.016103280000003</v>
+          </cell>
+          <cell r="P18">
+            <v>0</v>
+          </cell>
+          <cell r="Q18">
+            <v>0</v>
+          </cell>
+          <cell r="R18">
+            <v>0</v>
+          </cell>
+          <cell r="S18">
+            <v>0</v>
+          </cell>
+          <cell r="T18">
+            <v>0</v>
+          </cell>
+          <cell r="U18">
+            <v>15.341691240000001</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="D19">
+            <v>0</v>
+          </cell>
+          <cell r="E19">
+            <v>0</v>
+          </cell>
+          <cell r="G19">
+            <v>8.9932464000000003</v>
+          </cell>
+          <cell r="H19">
+            <v>0</v>
+          </cell>
+          <cell r="I19">
+            <v>0</v>
+          </cell>
+          <cell r="J19">
+            <v>0</v>
+          </cell>
+          <cell r="K19">
+            <v>0</v>
+          </cell>
+          <cell r="L19">
+            <v>0</v>
+          </cell>
+          <cell r="M19">
+            <v>0</v>
+          </cell>
+          <cell r="N19">
+            <v>0</v>
+          </cell>
+          <cell r="O19">
+            <v>0</v>
+          </cell>
+          <cell r="P19">
+            <v>0</v>
+          </cell>
+          <cell r="Q19">
+            <v>0</v>
+          </cell>
+          <cell r="R19">
+            <v>0</v>
+          </cell>
+          <cell r="S19">
+            <v>4.1868000000000006E-5</v>
+          </cell>
+          <cell r="T19">
+            <v>0</v>
+          </cell>
+          <cell r="U19">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="D20">
+            <v>0</v>
+          </cell>
+          <cell r="E20">
+            <v>0</v>
+          </cell>
+          <cell r="G20">
+            <v>59.234009040000004</v>
+          </cell>
+          <cell r="H20">
+            <v>2.9927246400000005</v>
+          </cell>
+          <cell r="I20">
+            <v>1.2346873199999999</v>
+          </cell>
+          <cell r="J20">
+            <v>28.510014600000005</v>
+          </cell>
+          <cell r="K20">
+            <v>0</v>
+          </cell>
+          <cell r="L20">
+            <v>1.2556213199999999</v>
+          </cell>
+          <cell r="M20">
+            <v>8.1692841600000001</v>
+          </cell>
+          <cell r="N20">
+            <v>0</v>
+          </cell>
+          <cell r="O20">
+            <v>0</v>
+          </cell>
+          <cell r="P20">
+            <v>0</v>
+          </cell>
+          <cell r="Q20">
+            <v>0</v>
+          </cell>
+          <cell r="R20">
+            <v>0</v>
+          </cell>
+          <cell r="S20">
+            <v>0</v>
+          </cell>
+          <cell r="T20">
+            <v>0</v>
+          </cell>
+          <cell r="U20">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="D21">
+            <v>0</v>
+          </cell>
+          <cell r="E21">
+            <v>0</v>
+          </cell>
+          <cell r="G21">
+            <v>0</v>
+          </cell>
+          <cell r="H21">
+            <v>0</v>
+          </cell>
+          <cell r="I21">
+            <v>0</v>
+          </cell>
+          <cell r="J21">
+            <v>0</v>
+          </cell>
+          <cell r="K21">
+            <v>0</v>
+          </cell>
+          <cell r="L21">
+            <v>0</v>
+          </cell>
+          <cell r="M21">
+            <v>0</v>
+          </cell>
+          <cell r="N21">
+            <v>0</v>
+          </cell>
+          <cell r="O21">
+            <v>9.4575625199999998</v>
+          </cell>
+          <cell r="P21">
+            <v>0</v>
+          </cell>
+          <cell r="Q21">
+            <v>0</v>
+          </cell>
+          <cell r="R21">
+            <v>0</v>
+          </cell>
+          <cell r="S21">
+            <v>2.51208E-4</v>
+          </cell>
+          <cell r="T21">
+            <v>1.0048319999999998E-3</v>
+          </cell>
+          <cell r="U21">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="D22">
+            <v>0</v>
+          </cell>
+          <cell r="E22">
+            <v>0</v>
+          </cell>
+          <cell r="G22">
+            <v>0</v>
+          </cell>
+          <cell r="H22">
+            <v>0</v>
+          </cell>
+          <cell r="I22">
+            <v>0</v>
+          </cell>
+          <cell r="J22">
+            <v>0</v>
+          </cell>
+          <cell r="K22">
+            <v>0</v>
+          </cell>
+          <cell r="L22">
+            <v>0</v>
+          </cell>
+          <cell r="M22">
+            <v>0</v>
+          </cell>
+          <cell r="N22">
+            <v>0</v>
+          </cell>
+          <cell r="O22">
+            <v>0</v>
+          </cell>
+          <cell r="P22">
+            <v>0</v>
+          </cell>
+          <cell r="Q22">
+            <v>0</v>
+          </cell>
+          <cell r="R22">
+            <v>0</v>
+          </cell>
+          <cell r="S22">
+            <v>0</v>
+          </cell>
+          <cell r="T22">
+            <v>0</v>
+          </cell>
+          <cell r="U22">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="D23">
+            <v>0</v>
+          </cell>
+          <cell r="E23">
+            <v>0</v>
+          </cell>
+          <cell r="G23">
+            <v>0</v>
+          </cell>
+          <cell r="H23">
+            <v>0</v>
+          </cell>
+          <cell r="I23">
+            <v>0</v>
+          </cell>
+          <cell r="J23">
+            <v>0</v>
+          </cell>
+          <cell r="K23">
+            <v>0</v>
+          </cell>
+          <cell r="L23">
+            <v>0</v>
+          </cell>
+          <cell r="M23">
+            <v>0</v>
+          </cell>
+          <cell r="N23">
+            <v>0</v>
+          </cell>
+          <cell r="O23">
+            <v>0</v>
+          </cell>
+          <cell r="P23">
+            <v>0</v>
+          </cell>
+          <cell r="Q23">
+            <v>0</v>
+          </cell>
+          <cell r="R23">
+            <v>0</v>
+          </cell>
+          <cell r="S23">
+            <v>0</v>
+          </cell>
+          <cell r="T23">
+            <v>0</v>
+          </cell>
+          <cell r="U23">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -9516,75 +9484,75 @@
         <v>59</v>
       </c>
       <c r="D5" s="143">
-        <f>[2]EB1!D16</f>
+        <f>[3]EB1!D16</f>
         <v>0</v>
       </c>
       <c r="E5" s="143">
-        <f>[2]EB1!E16</f>
+        <f>[3]EB1!E16</f>
         <v>0</v>
       </c>
       <c r="F5" s="144">
-        <f>[2]EB1!F16</f>
+        <f>[3]EB1!F16</f>
         <v>0</v>
       </c>
       <c r="G5" s="143">
-        <f>[2]EB1!G16</f>
+        <f>[3]EB1!G16</f>
         <v>0</v>
       </c>
       <c r="H5" s="143">
-        <f>[2]EB1!H16</f>
+        <f>[3]EB1!H16</f>
         <v>0</v>
       </c>
       <c r="I5" s="143">
-        <f>[2]EB1!I16</f>
+        <f>[3]EB1!I16</f>
         <v>8.7784635600000005</v>
       </c>
       <c r="J5" s="143">
-        <f>[2]EB1!J16</f>
+        <f>[3]EB1!J16</f>
         <v>0</v>
       </c>
       <c r="K5" s="144">
-        <f>[2]EB1!K16</f>
+        <f>[3]EB1!K16</f>
         <v>0</v>
       </c>
       <c r="L5" s="143">
-        <f>[2]EB1!L16</f>
+        <f>[3]EB1!L16</f>
         <v>0</v>
       </c>
       <c r="M5" s="143">
-        <f>[2]EB1!M16</f>
+        <f>[3]EB1!M16</f>
         <v>0</v>
       </c>
       <c r="N5" s="144">
-        <f>[2]EB1!N16</f>
+        <f>[3]EB1!N16</f>
         <v>0</v>
       </c>
       <c r="O5" s="145">
-        <f>[2]EB1!O16</f>
+        <f>[3]EB1!O16</f>
         <v>29.606118840000001</v>
       </c>
       <c r="P5" s="144">
-        <f>[2]EB1!P16</f>
+        <f>[3]EB1!P16</f>
         <v>0</v>
       </c>
       <c r="Q5" s="144">
-        <f>[2]EB1!Q16</f>
+        <f>[3]EB1!Q16</f>
         <v>0</v>
       </c>
       <c r="R5" s="143">
-        <f>[2]EB1!R16</f>
+        <f>[3]EB1!R16</f>
         <v>0</v>
       </c>
       <c r="S5" s="144">
-        <f>[2]EB1!S16</f>
+        <f>[3]EB1!S16</f>
         <v>0</v>
       </c>
       <c r="T5" s="144">
-        <f>[2]EB1!T16</f>
+        <f>[3]EB1!T16</f>
         <v>0</v>
       </c>
       <c r="U5" s="143">
-        <f>[2]EB1!U16</f>
+        <f>[3]EB1!U16</f>
         <v>15.231997080000001</v>
       </c>
       <c r="V5" s="79">
@@ -9600,75 +9568,75 @@
         <v>61</v>
       </c>
       <c r="D6" s="146">
-        <f>[2]EB1!D17</f>
+        <f>[3]EB1!D17</f>
         <v>0</v>
       </c>
       <c r="E6" s="143">
-        <f>[2]EB1!E17</f>
+        <f>[3]EB1!E17</f>
         <v>0</v>
       </c>
       <c r="F6" s="144">
-        <f>[2]EB1!F17</f>
+        <f>[3]EB1!F17</f>
         <v>0</v>
       </c>
       <c r="G6" s="143">
-        <f>[2]EB1!G17</f>
+        <f>[3]EB1!G17</f>
         <v>0</v>
       </c>
       <c r="H6" s="143">
-        <f>[2]EB1!H17</f>
+        <f>[3]EB1!H17</f>
         <v>0</v>
       </c>
       <c r="I6" s="143">
-        <f>[2]EB1!I17</f>
+        <f>[3]EB1!I17</f>
         <v>5.3591040000000003</v>
       </c>
       <c r="J6" s="143">
-        <f>[2]EB1!J17</f>
+        <f>[3]EB1!J17</f>
         <v>0</v>
       </c>
       <c r="K6" s="144">
-        <f>[2]EB1!K17</f>
+        <f>[3]EB1!K17</f>
         <v>0</v>
       </c>
       <c r="L6" s="143">
-        <f>[2]EB1!L17</f>
+        <f>[3]EB1!L17</f>
         <v>0</v>
       </c>
       <c r="M6" s="143">
-        <f>[2]EB1!M17</f>
+        <f>[3]EB1!M17</f>
         <v>2.0264112000000001E-2</v>
       </c>
       <c r="N6" s="144">
-        <f>[2]EB1!N17</f>
+        <f>[3]EB1!N17</f>
         <v>0</v>
       </c>
       <c r="O6" s="143">
-        <f>[2]EB1!O17</f>
+        <f>[3]EB1!O17</f>
         <v>0</v>
       </c>
       <c r="P6" s="144">
-        <f>[2]EB1!P17</f>
+        <f>[3]EB1!P17</f>
         <v>0</v>
       </c>
       <c r="Q6" s="144">
-        <f>[2]EB1!Q17</f>
+        <f>[3]EB1!Q17</f>
         <v>0</v>
       </c>
       <c r="R6" s="143">
-        <f>[2]EB1!R17</f>
+        <f>[3]EB1!R17</f>
         <v>0</v>
       </c>
       <c r="S6" s="144">
-        <f>[2]EB1!S17</f>
+        <f>[3]EB1!S17</f>
         <v>0</v>
       </c>
       <c r="T6" s="144">
-        <f>[2]EB1!T17</f>
+        <f>[3]EB1!T17</f>
         <v>0</v>
       </c>
       <c r="U6" s="143">
-        <f>[2]EB1!U17</f>
+        <f>[3]EB1!U17</f>
         <v>11.973410640000001</v>
       </c>
       <c r="V6" s="79">
@@ -9684,75 +9652,75 @@
         <v>63</v>
       </c>
       <c r="D7" s="132">
-        <f>[2]EB1!D18</f>
+        <f>[3]EB1!D18</f>
         <v>20.32984476</v>
       </c>
       <c r="E7" s="78">
-        <f>[2]EB1!E18</f>
+        <f>[3]EB1!E18</f>
         <v>0</v>
       </c>
       <c r="F7" s="78">
-        <f>[2]EB1!F18</f>
+        <f>[3]EB1!F18</f>
         <v>0</v>
       </c>
       <c r="G7" s="133">
-        <f>[2]EB1!G18</f>
+        <f>[3]EB1!G18</f>
         <v>9.3960165599999996</v>
       </c>
       <c r="H7" s="78">
-        <f>[2]EB1!H18</f>
+        <f>[3]EB1!H18</f>
         <v>0</v>
       </c>
       <c r="I7" s="78">
-        <f>[2]EB1!I18</f>
+        <f>[3]EB1!I18</f>
         <v>2.8470240000000004E-2</v>
       </c>
       <c r="J7" s="78">
-        <f>[2]EB1!J18</f>
+        <f>[3]EB1!J18</f>
         <v>0</v>
       </c>
       <c r="K7" s="78">
-        <f>[2]EB1!K18</f>
+        <f>[3]EB1!K18</f>
         <v>0</v>
       </c>
       <c r="L7" s="78">
-        <f>[2]EB1!L18</f>
+        <f>[3]EB1!L18</f>
         <v>5.0660280000000002E-2</v>
       </c>
       <c r="M7" s="78">
-        <f>[2]EB1!M18</f>
+        <f>[3]EB1!M18</f>
         <v>0</v>
       </c>
       <c r="N7" s="78">
-        <f>[2]EB1!N18</f>
+        <f>[3]EB1!N18</f>
         <v>0</v>
       </c>
       <c r="O7" s="132">
-        <f>[2]EB1!O18</f>
+        <f>[3]EB1!O18</f>
         <v>60.016103280000003</v>
       </c>
       <c r="P7" s="78">
-        <f>[2]EB1!P18</f>
+        <f>[3]EB1!P18</f>
         <v>0</v>
       </c>
       <c r="Q7" s="78">
-        <f>[2]EB1!Q18</f>
+        <f>[3]EB1!Q18</f>
         <v>0</v>
       </c>
       <c r="R7" s="78">
-        <f>[2]EB1!R18</f>
+        <f>[3]EB1!R18</f>
         <v>0</v>
       </c>
       <c r="S7" s="78">
-        <f>[2]EB1!S18</f>
+        <f>[3]EB1!S18</f>
         <v>0</v>
       </c>
       <c r="T7" s="78">
-        <f>[2]EB1!T18</f>
+        <f>[3]EB1!T18</f>
         <v>0</v>
       </c>
       <c r="U7" s="78">
-        <f>[2]EB1!U18</f>
+        <f>[3]EB1!U18</f>
         <v>15.341691240000001</v>
       </c>
       <c r="V7" s="79">
@@ -9768,75 +9736,75 @@
         <v>65</v>
       </c>
       <c r="D8" s="147">
-        <f>[2]EB1!D19</f>
+        <f>[3]EB1!D19</f>
         <v>0</v>
       </c>
       <c r="E8" s="147">
-        <f>[2]EB1!E19</f>
+        <f>[3]EB1!E19</f>
         <v>0</v>
       </c>
       <c r="F8" s="147">
-        <f>[2]EB1!F19</f>
+        <f>[3]EB1!F19</f>
         <v>0</v>
       </c>
       <c r="G8" s="148">
-        <f>[2]EB1!G19</f>
+        <f>[3]EB1!G19</f>
         <v>8.9932464000000003</v>
       </c>
       <c r="H8" s="147">
-        <f>[2]EB1!H19</f>
+        <f>[3]EB1!H19</f>
         <v>0</v>
       </c>
       <c r="I8" s="147">
-        <f>[2]EB1!I19</f>
+        <f>[3]EB1!I19</f>
         <v>0</v>
       </c>
       <c r="J8" s="147">
-        <f>[2]EB1!J19</f>
+        <f>[3]EB1!J19</f>
         <v>0</v>
       </c>
       <c r="K8" s="147">
-        <f>[2]EB1!K19</f>
+        <f>[3]EB1!K19</f>
         <v>0</v>
       </c>
       <c r="L8" s="147">
-        <f>[2]EB1!L19</f>
+        <f>[3]EB1!L19</f>
         <v>0</v>
       </c>
       <c r="M8" s="147">
-        <f>[2]EB1!M19</f>
+        <f>[3]EB1!M19</f>
         <v>0</v>
       </c>
       <c r="N8" s="147">
-        <f>[2]EB1!N19</f>
+        <f>[3]EB1!N19</f>
         <v>0</v>
       </c>
       <c r="O8" s="147">
-        <f>[2]EB1!O19</f>
+        <f>[3]EB1!O19</f>
         <v>0</v>
       </c>
       <c r="P8" s="147">
-        <f>[2]EB1!P19</f>
+        <f>[3]EB1!P19</f>
         <v>0</v>
       </c>
       <c r="Q8" s="147">
-        <f>[2]EB1!Q19</f>
+        <f>[3]EB1!Q19</f>
         <v>0</v>
       </c>
       <c r="R8" s="147">
-        <f>[2]EB1!R19</f>
+        <f>[3]EB1!R19</f>
         <v>0</v>
       </c>
       <c r="S8" s="147">
-        <f>[2]EB1!S19</f>
+        <f>[3]EB1!S19</f>
         <v>4.1868000000000006E-5</v>
       </c>
       <c r="T8" s="147">
-        <f>[2]EB1!T19</f>
+        <f>[3]EB1!T19</f>
         <v>0</v>
       </c>
       <c r="U8" s="147">
-        <f>[2]EB1!U19</f>
+        <f>[3]EB1!U19</f>
         <v>0</v>
       </c>
       <c r="V8" s="42">
@@ -9852,75 +9820,75 @@
         <v>67</v>
       </c>
       <c r="D9" s="78">
-        <f>[2]EB1!D20</f>
+        <f>[3]EB1!D20</f>
         <v>0</v>
       </c>
       <c r="E9" s="78">
-        <f>[2]EB1!E20</f>
+        <f>[3]EB1!E20</f>
         <v>0</v>
       </c>
       <c r="F9" s="78">
-        <f>[2]EB1!F20</f>
+        <f>[3]EB1!F20</f>
         <v>0</v>
       </c>
       <c r="G9" s="134">
-        <f>[2]EB1!G20</f>
+        <f>[3]EB1!G20</f>
         <v>59.234009040000004</v>
       </c>
       <c r="H9" s="131">
-        <f>[2]EB1!H20</f>
+        <f>[3]EB1!H20</f>
         <v>2.9927246400000005</v>
       </c>
       <c r="I9" s="135">
-        <f>[2]EB1!I20</f>
+        <f>[3]EB1!I20</f>
         <v>1.2346873199999999</v>
       </c>
       <c r="J9" s="136">
-        <f>[2]EB1!J20</f>
+        <f>[3]EB1!J20</f>
         <v>28.510014600000005</v>
       </c>
       <c r="K9" s="78">
-        <f>[2]EB1!K20</f>
+        <f>[3]EB1!K20</f>
         <v>0</v>
       </c>
       <c r="L9" s="78">
-        <f>[2]EB1!L20</f>
+        <f>[3]EB1!L20</f>
         <v>1.2556213199999999</v>
       </c>
       <c r="M9" s="78">
-        <f>[2]EB1!M20</f>
+        <f>[3]EB1!M20</f>
         <v>8.1692841600000001</v>
       </c>
       <c r="N9" s="78">
-        <f>[2]EB1!N20</f>
+        <f>[3]EB1!N20</f>
         <v>0</v>
       </c>
       <c r="O9" s="78">
-        <f>[2]EB1!O20</f>
+        <f>[3]EB1!O20</f>
         <v>0</v>
       </c>
       <c r="P9" s="78">
-        <f>[2]EB1!P20</f>
+        <f>[3]EB1!P20</f>
         <v>0</v>
       </c>
       <c r="Q9" s="78">
-        <f>[2]EB1!Q20</f>
+        <f>[3]EB1!Q20</f>
         <v>0</v>
       </c>
       <c r="R9" s="78">
-        <f>[2]EB1!R20</f>
+        <f>[3]EB1!R20</f>
         <v>0</v>
       </c>
       <c r="S9" s="78">
-        <f>[2]EB1!S20</f>
+        <f>[3]EB1!S20</f>
         <v>0</v>
       </c>
       <c r="T9" s="78">
-        <f>[2]EB1!T20</f>
+        <f>[3]EB1!T20</f>
         <v>0</v>
       </c>
       <c r="U9" s="78">
-        <f>[2]EB1!U20</f>
+        <f>[3]EB1!U20</f>
         <v>0</v>
       </c>
       <c r="V9" s="79">
@@ -9936,75 +9904,75 @@
         <v>69</v>
       </c>
       <c r="D10" s="41">
-        <f>[2]EB1!D21</f>
+        <f>[3]EB1!D21</f>
         <v>0</v>
       </c>
       <c r="E10" s="41">
-        <f>[2]EB1!E21</f>
+        <f>[3]EB1!E21</f>
         <v>0</v>
       </c>
       <c r="F10" s="41">
-        <f>[2]EB1!F21</f>
+        <f>[3]EB1!F21</f>
         <v>0</v>
       </c>
       <c r="G10" s="41">
-        <f>[2]EB1!G21</f>
+        <f>[3]EB1!G21</f>
         <v>0</v>
       </c>
       <c r="H10" s="41">
-        <f>[2]EB1!H21</f>
+        <f>[3]EB1!H21</f>
         <v>0</v>
       </c>
       <c r="I10" s="41">
-        <f>[2]EB1!I21</f>
+        <f>[3]EB1!I21</f>
         <v>0</v>
       </c>
       <c r="J10" s="41">
-        <f>[2]EB1!J21</f>
+        <f>[3]EB1!J21</f>
         <v>0</v>
       </c>
       <c r="K10" s="41">
-        <f>[2]EB1!K21</f>
+        <f>[3]EB1!K21</f>
         <v>0</v>
       </c>
       <c r="L10" s="41">
-        <f>[2]EB1!L21</f>
+        <f>[3]EB1!L21</f>
         <v>0</v>
       </c>
       <c r="M10" s="41">
-        <f>[2]EB1!M21</f>
+        <f>[3]EB1!M21</f>
         <v>0</v>
       </c>
       <c r="N10" s="41">
-        <f>[2]EB1!N21</f>
+        <f>[3]EB1!N21</f>
         <v>0</v>
       </c>
       <c r="O10" s="41">
-        <f>[2]EB1!O21</f>
+        <f>[3]EB1!O21</f>
         <v>9.4575625199999998</v>
       </c>
       <c r="P10" s="41">
-        <f>[2]EB1!P21</f>
+        <f>[3]EB1!P21</f>
         <v>0</v>
       </c>
       <c r="Q10" s="41">
-        <f>[2]EB1!Q21</f>
+        <f>[3]EB1!Q21</f>
         <v>0</v>
       </c>
       <c r="R10" s="41">
-        <f>[2]EB1!R21</f>
+        <f>[3]EB1!R21</f>
         <v>0</v>
       </c>
       <c r="S10" s="41">
-        <f>[2]EB1!S21</f>
+        <f>[3]EB1!S21</f>
         <v>2.51208E-4</v>
       </c>
       <c r="T10" s="41">
-        <f>[2]EB1!T21</f>
+        <f>[3]EB1!T21</f>
         <v>1.0048319999999998E-3</v>
       </c>
       <c r="U10" s="41">
-        <f>[2]EB1!U21</f>
+        <f>[3]EB1!U21</f>
         <v>0</v>
       </c>
       <c r="V10" s="80">
@@ -10020,75 +9988,75 @@
         <v>70</v>
       </c>
       <c r="D11" s="78">
-        <f>[2]EB1!D22</f>
+        <f>[3]EB1!D22</f>
         <v>0</v>
       </c>
       <c r="E11" s="78">
-        <f>[2]EB1!E22</f>
+        <f>[3]EB1!E22</f>
         <v>0</v>
       </c>
       <c r="F11" s="78">
-        <f>[2]EB1!F22</f>
+        <f>[3]EB1!F22</f>
         <v>0</v>
       </c>
       <c r="G11" s="78">
-        <f>[2]EB1!G22</f>
+        <f>[3]EB1!G22</f>
         <v>0</v>
       </c>
       <c r="H11" s="78">
-        <f>[2]EB1!H22</f>
+        <f>[3]EB1!H22</f>
         <v>0</v>
       </c>
       <c r="I11" s="78">
-        <f>[2]EB1!I22</f>
+        <f>[3]EB1!I22</f>
         <v>0</v>
       </c>
       <c r="J11" s="78">
-        <f>[2]EB1!J22</f>
+        <f>[3]EB1!J22</f>
         <v>0</v>
       </c>
       <c r="K11" s="78">
-        <f>[2]EB1!K22</f>
+        <f>[3]EB1!K22</f>
         <v>0</v>
       </c>
       <c r="L11" s="78">
-        <f>[2]EB1!L22</f>
+        <f>[3]EB1!L22</f>
         <v>0</v>
       </c>
       <c r="M11" s="78">
-        <f>[2]EB1!M22</f>
+        <f>[3]EB1!M22</f>
         <v>0</v>
       </c>
       <c r="N11" s="78">
-        <f>[2]EB1!N22</f>
+        <f>[3]EB1!N22</f>
         <v>0</v>
       </c>
       <c r="O11" s="78">
-        <f>[2]EB1!O22</f>
+        <f>[3]EB1!O22</f>
         <v>0</v>
       </c>
       <c r="P11" s="78">
-        <f>[2]EB1!P22</f>
+        <f>[3]EB1!P22</f>
         <v>0</v>
       </c>
       <c r="Q11" s="78">
-        <f>[2]EB1!Q22</f>
+        <f>[3]EB1!Q22</f>
         <v>0</v>
       </c>
       <c r="R11" s="78">
-        <f>[2]EB1!R22</f>
+        <f>[3]EB1!R22</f>
         <v>0</v>
       </c>
       <c r="S11" s="78">
-        <f>[2]EB1!S22</f>
+        <f>[3]EB1!S22</f>
         <v>0</v>
       </c>
       <c r="T11" s="78">
-        <f>[2]EB1!T22</f>
+        <f>[3]EB1!T22</f>
         <v>0</v>
       </c>
       <c r="U11" s="78">
-        <f>[2]EB1!U22</f>
+        <f>[3]EB1!U22</f>
         <v>0</v>
       </c>
       <c r="V11" s="79">
@@ -10104,75 +10072,75 @@
         <v>71</v>
       </c>
       <c r="D12" s="78">
-        <f>[2]EB1!D23</f>
+        <f>[3]EB1!D23</f>
         <v>0</v>
       </c>
       <c r="E12" s="78">
-        <f>[2]EB1!E23</f>
+        <f>[3]EB1!E23</f>
         <v>0</v>
       </c>
       <c r="F12" s="78">
-        <f>[2]EB1!F23</f>
+        <f>[3]EB1!F23</f>
         <v>0</v>
       </c>
       <c r="G12" s="78">
-        <f>[2]EB1!G23</f>
+        <f>[3]EB1!G23</f>
         <v>0</v>
       </c>
       <c r="H12" s="78">
-        <f>[2]EB1!H23</f>
+        <f>[3]EB1!H23</f>
         <v>0</v>
       </c>
       <c r="I12" s="78">
-        <f>[2]EB1!I23</f>
+        <f>[3]EB1!I23</f>
         <v>0</v>
       </c>
       <c r="J12" s="78">
-        <f>[2]EB1!J23</f>
+        <f>[3]EB1!J23</f>
         <v>0</v>
       </c>
       <c r="K12" s="78">
-        <f>[2]EB1!K23</f>
+        <f>[3]EB1!K23</f>
         <v>0</v>
       </c>
       <c r="L12" s="78">
-        <f>[2]EB1!L23</f>
+        <f>[3]EB1!L23</f>
         <v>0</v>
       </c>
       <c r="M12" s="78">
-        <f>[2]EB1!M23</f>
+        <f>[3]EB1!M23</f>
         <v>0</v>
       </c>
       <c r="N12" s="78">
-        <f>[2]EB1!N23</f>
+        <f>[3]EB1!N23</f>
         <v>0</v>
       </c>
       <c r="O12" s="41">
-        <f>[2]EB1!O23</f>
+        <f>[3]EB1!O23</f>
         <v>0</v>
       </c>
       <c r="P12" s="41">
-        <f>[2]EB1!P23</f>
+        <f>[3]EB1!P23</f>
         <v>0</v>
       </c>
       <c r="Q12" s="41">
-        <f>[2]EB1!Q23</f>
+        <f>[3]EB1!Q23</f>
         <v>0</v>
       </c>
       <c r="R12" s="78">
-        <f>[2]EB1!R23</f>
+        <f>[3]EB1!R23</f>
         <v>0</v>
       </c>
       <c r="S12" s="78">
-        <f>[2]EB1!S23</f>
+        <f>[3]EB1!S23</f>
         <v>0</v>
       </c>
       <c r="T12" s="78">
-        <f>[2]EB1!T23</f>
+        <f>[3]EB1!T23</f>
         <v>0</v>
       </c>
       <c r="U12" s="78">
-        <f>[2]EB1!U23</f>
+        <f>[3]EB1!U23</f>
         <v>0</v>
       </c>
       <c r="V12" s="79">
@@ -11113,11 +11081,11 @@
       </c>
       <c r="K5" s="126"/>
       <c r="L5" s="126" t="str">
-        <f>$B$2&amp;[3]EB2!$D$2</f>
+        <f>$B$2&amp;[2]EB2!$D$2</f>
         <v>AGRCOA</v>
       </c>
       <c r="M5" s="127" t="str">
-        <f>$C$2&amp;" "&amp;[3]EB2!$D$3</f>
+        <f>$C$2&amp;" "&amp;[2]EB2!$D$3</f>
         <v>Agriculture Solid Fuels</v>
       </c>
       <c r="N5" s="126" t="str">
@@ -11137,11 +11105,11 @@
       <c r="J6" s="126"/>
       <c r="K6" s="126"/>
       <c r="L6" s="126" t="str">
-        <f>$B$2&amp;[3]EB2!$E$2</f>
+        <f>$B$2&amp;[2]EB2!$E$2</f>
         <v>AGRGAS</v>
       </c>
       <c r="M6" s="127" t="str">
-        <f>$C$2&amp;" "&amp;[3]EB2!$E$3</f>
+        <f>$C$2&amp;" "&amp;[2]EB2!$E$3</f>
         <v>Agriculture Natural Gas</v>
       </c>
       <c r="N6" s="126" t="str">
@@ -11161,11 +11129,11 @@
       <c r="J7" s="126"/>
       <c r="K7" s="126"/>
       <c r="L7" s="126" t="str">
-        <f>$B$2&amp;[3]EB2!$F$2</f>
+        <f>$B$2&amp;[2]EB2!$F$2</f>
         <v>AGROIL</v>
       </c>
       <c r="M7" s="127" t="str">
-        <f>$C$2&amp;" "&amp;RIGHT([3]EB2!$F$3,3)</f>
+        <f>$C$2&amp;" "&amp;RIGHT([2]EB2!$F$3,3)</f>
         <v>Agriculture oil</v>
       </c>
       <c r="N7" s="126" t="str">
@@ -11185,11 +11153,11 @@
       <c r="J8" s="126"/>
       <c r="K8" s="126"/>
       <c r="L8" s="126" t="str">
-        <f>$B$2&amp;[3]EB2!$O$2</f>
+        <f>$B$2&amp;[2]EB2!$O$2</f>
         <v>AGRBIO</v>
       </c>
       <c r="M8" s="127" t="str">
-        <f>$C$2&amp;" "&amp;[3]EB2!$O$3</f>
+        <f>$C$2&amp;" "&amp;[2]EB2!$O$3</f>
         <v>Agriculture Biomass</v>
       </c>
       <c r="N8" s="126" t="str">
@@ -11209,11 +11177,11 @@
       <c r="J9" s="126"/>
       <c r="K9" s="126"/>
       <c r="L9" s="126" t="str">
-        <f>$B$2&amp;[3]EB2!$U$2</f>
+        <f>$B$2&amp;[2]EB2!$U$2</f>
         <v>AGRELC</v>
       </c>
       <c r="M9" s="127" t="str">
-        <f>$C$2&amp;" "&amp;[3]EB2!$U$3</f>
+        <f>$C$2&amp;" "&amp;[2]EB2!$U$3</f>
         <v>Agriculture Electricity</v>
       </c>
       <c r="N9" s="126" t="str">
@@ -11477,7 +11445,7 @@
         <v>FTE-AGROIL</v>
       </c>
       <c r="C18" t="str">
-        <f>[3]EB2!$G$2</f>
+        <f>[2]EB2!$G$2</f>
         <v>DSL</v>
       </c>
       <c r="D18" t="str">
@@ -11515,7 +11483,7 @@
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C19" t="str">
-        <f>[3]EB2!$H$2</f>
+        <f>[2]EB2!$H$2</f>
         <v>KER</v>
       </c>
       <c r="E19" s="158"/>
@@ -11545,7 +11513,7 @@
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C20" t="str">
-        <f>[3]EB2!$I$2</f>
+        <f>[2]EB2!$I$2</f>
         <v>LPG</v>
       </c>
       <c r="E20" s="158"/>
@@ -11577,7 +11545,7 @@
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C21" t="str">
-        <f>[3]EB2!$J$2</f>
+        <f>[2]EB2!$J$2</f>
         <v>GSL</v>
       </c>
       <c r="E21" s="158"/>
@@ -11587,7 +11555,7 @@
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C22" t="str">
-        <f>[3]EB2!$L$2</f>
+        <f>[2]EB2!$L$2</f>
         <v>HFO</v>
       </c>
       <c r="E22" s="158"/>
@@ -11597,7 +11565,7 @@
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C23" t="str">
-        <f>[3]EB2!$M$2</f>
+        <f>[2]EB2!$M$2</f>
         <v>OPP</v>
       </c>
       <c r="E23" s="158"/>
@@ -11942,11 +11910,11 @@
       </c>
       <c r="M5" s="126"/>
       <c r="N5" s="157" t="str">
-        <f>LEFT($L$5,1)&amp;LEFT($B$2,1)&amp;[3]EB2!$C$20</f>
+        <f>LEFT($L$5,1)&amp;LEFT($B$2,1)&amp;[2]EB2!$C$20</f>
         <v>DAOT</v>
       </c>
       <c r="O5" s="157" t="str">
-        <f>LEFT($D$2,6)&amp;" "&amp;$C$2&amp; " Sector - "&amp;[3]EB2!$X$20</f>
+        <f>LEFT($D$2,6)&amp;" "&amp;$C$2&amp; " Sector - "&amp;[2]EB2!$X$20</f>
         <v>Demand Agriculture Sector - Demand</v>
       </c>
       <c r="P5" s="157" t="str">
@@ -11966,15 +11934,15 @@
       </c>
       <c r="M6" s="126"/>
       <c r="N6" s="126" t="str">
-        <f>$B$2&amp;[3]EB2!$C$29</f>
+        <f>$B$2&amp;[2]EB2!$C$29</f>
         <v>AGRCO2</v>
       </c>
       <c r="O6" s="126" t="str">
-        <f>$C$2&amp;" "&amp;[3]EB2!$C$30</f>
+        <f>$C$2&amp;" "&amp;[2]EB2!$C$30</f>
         <v>Agriculture Carbon dioxide</v>
       </c>
       <c r="P6" s="126" t="str">
-        <f>[3]EB2!$AA$2</f>
+        <f>[2]EB2!$AA$2</f>
         <v>kt</v>
       </c>
       <c r="Q6" s="126"/>
@@ -12170,7 +12138,7 @@
         <v>AOTETOT</v>
       </c>
       <c r="C12" t="str">
-        <f>[3]Sector_Fuels_AGR!L5</f>
+        <f>[2]Sector_Fuels_AGR!L5</f>
         <v>AGRCOA</v>
       </c>
       <c r="D12" t="str">
@@ -12179,12 +12147,12 @@
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="165">
-        <f>[3]EB2!$D$6/([3]EB2!$D$6+[3]EB2!$E$6+SUM([3]EB2!$G$6:$J$6,[3]EB2!$L$6:$M$6)+[3]EB2!$O$6+[3]EB2!$U$6)</f>
-        <v>7.179568674540544E-3</v>
+        <f>'EB1'!D8/('EB1'!$D$8+'EB1'!$E$8+SUM('EB1'!$G$8:$J$8,'EB1'!$M$8,'EB1'!$L$8)+'EB1'!$O$8+'EB1'!$U$8)</f>
+        <v>0</v>
       </c>
       <c r="G12" s="166">
         <f>IF(F12=0,20%,F12*(1+$G$8))</f>
-        <v>8.6154824094486528E-3</v>
+        <v>0.2</v>
       </c>
       <c r="H12" s="64">
         <v>1</v>
@@ -12200,11 +12168,11 @@
       </c>
       <c r="M12" s="126"/>
       <c r="N12" s="126" t="str">
-        <f>LEFT($B$2)&amp;[3]EB2!$C$20&amp;$J$2&amp;[3]EB2!$V$2</f>
+        <f>LEFT($B$2)&amp;[2]EB2!$C$20&amp;$J$2&amp;[2]EB2!$V$2</f>
         <v>AOTETOT</v>
       </c>
       <c r="O12" s="126" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$J$1&amp;" "&amp;[3]EB2!$X$20&amp;" - "&amp;[3]EB2!$V$2</f>
+        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$J$1&amp;" "&amp;[2]EB2!$X$20&amp;" - "&amp;[2]EB2!$V$2</f>
         <v>Demand Technologies Agriculture Sector - Existing Demand - TOT</v>
       </c>
       <c r="P12" s="126" t="str">
@@ -12227,17 +12195,17 @@
     </row>
     <row r="13" spans="2:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C13" t="str">
-        <f>[3]Sector_Fuels_AGR!L6</f>
+        <f>[2]Sector_Fuels_AGR!L6</f>
         <v>AGRGAS</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="165">
-        <f>[3]EB2!$E$6/([3]EB2!$D$6+[3]EB2!$E$6+SUM([3]EB2!$G$6:$J$6,[3]EB2!$L$6:$M$6)+[3]EB2!$O$6+[3]EB2!$U$6)</f>
-        <v>0.37874393628467257</v>
+        <f>'EB1'!E8/('EB1'!$D$8+'EB1'!$E$8+SUM('EB1'!$G$8:$J$8,'EB1'!$M$8,'EB1'!$L$8)+'EB1'!$O$8+'EB1'!$U$8)</f>
+        <v>0</v>
       </c>
       <c r="G13" s="166">
         <f>IF(F13=0,20%,F13*(1+$G$8))</f>
-        <v>0.45449272354160708</v>
+        <v>0.2</v>
       </c>
       <c r="H13" s="16"/>
       <c r="I13" s="16"/>
@@ -12246,17 +12214,17 @@
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C14" t="str">
-        <f>[3]Sector_Fuels_AGR!L7</f>
+        <f>[2]Sector_Fuels_AGR!L7</f>
         <v>AGROIL</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="165">
-        <f>SUM([3]EB2!$G$6:$J$6,[3]EB2!$L$6:$M$6)/([3]EB2!$D$6+[3]EB2!$E$6+SUM([3]EB2!$G$6:$J$6,[3]EB2!$L$6:$M$6)+[3]EB2!$O$6+[3]EB2!$U$6)</f>
-        <v>0.15401636485812167</v>
+        <f>SUM('EB1'!G8:J8,'EB1'!L8:M8)/('EB1'!$D$8+'EB1'!$E$8+SUM('EB1'!$G$8:$J$8,'EB1'!$M$8,'EB1'!$L$8)+'EB1'!$O$8+'EB1'!$U$8)</f>
+        <v>1</v>
       </c>
       <c r="G14" s="166">
         <f>IF(F14=0,20%,F14*(1+$G$8))</f>
-        <v>0.184819637829746</v>
+        <v>1.2</v>
       </c>
       <c r="H14" s="16"/>
       <c r="I14" s="16"/>
@@ -12264,17 +12232,17 @@
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C15" t="str">
-        <f>[3]Sector_Fuels_AGR!L8</f>
+        <f>[2]Sector_Fuels_AGR!L8</f>
         <v>AGRBIO</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="165">
-        <f>[3]EB2!$O$6/([3]EB2!$D$6+[3]EB2!$E$6+SUM([3]EB2!$G$6:$J$6,[3]EB2!$L$6:$M$6)+[3]EB2!$O$6+[3]EB2!$U$6)</f>
-        <v>4.6845795981693746E-3</v>
+        <f>'EB1'!O8/('EB1'!$D$8+'EB1'!$E$8+SUM('EB1'!$G$8:$J$8,'EB1'!$M$8,'EB1'!$L$8)+'EB1'!$O$8+'EB1'!$U$8)</f>
+        <v>0</v>
       </c>
       <c r="G15" s="166">
         <f>IF(F15=0,20%,F15*(1+$G$8))</f>
-        <v>5.6214955178032497E-3</v>
+        <v>0.2</v>
       </c>
       <c r="H15" s="16"/>
       <c r="I15" s="16"/>
@@ -12284,17 +12252,17 @@
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C16" t="str">
-        <f>[3]Sector_Fuels_AGR!L9</f>
+        <f>[2]Sector_Fuels_AGR!L9</f>
         <v>AGRELC</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="165">
-        <f>[3]EB2!$U$6/([3]EB2!$D$6+[3]EB2!$E$6+SUM([3]EB2!$G$6:$J$6,[3]EB2!$L$6:$M$6)+[3]EB2!$O$6+[3]EB2!$U$6)</f>
-        <v>0.45537555058449591</v>
+        <f>'EB1'!U8/('EB1'!$D$8+'EB1'!$E$8+SUM('EB1'!$G$8:$J$8,'EB1'!$M$8,'EB1'!$L$8)+'EB1'!$O$8+'EB1'!$U$8)</f>
+        <v>0</v>
       </c>
       <c r="G16" s="166">
         <f>IF(F16=0,20%,F16*(1+$G$8))</f>
-        <v>0.54645066070139503</v>
+        <v>0.2</v>
       </c>
       <c r="H16" s="16"/>
       <c r="I16" s="16"/>

--- a/VT_REG1_RCA_V12.xlsx
+++ b/VT_REG1_RCA_V12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261015\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EF296E0-DB84-4FA9-B34F-E3ABBF476D19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C5E1A70-91CA-450A-850A-A7593CD53A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="901" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="901" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB1" sheetId="133" r:id="rId1"/>
@@ -4657,7 +4657,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="183">
   <si>
     <t>CommName</t>
   </si>
@@ -12125,14 +12125,10 @@
       <c r="R11" s="125"/>
       <c r="S11" s="125"/>
       <c r="T11" s="125"/>
-      <c r="U11" s="123" t="s">
-        <v>19</v>
-      </c>
-      <c r="V11" s="123" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="2:22" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="U11" s="126"/>
+      <c r="V11" s="126"/>
+    </row>
+    <row r="12" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B12" t="str">
         <f>N12</f>
         <v>AOTETOT</v>
@@ -12186,14 +12182,10 @@
       <c r="R12" s="126"/>
       <c r="S12" s="126"/>
       <c r="T12" s="126"/>
-      <c r="U12" s="125" t="s">
-        <v>42</v>
-      </c>
-      <c r="V12" s="125" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="2:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="U12" s="126"/>
+      <c r="V12" s="126"/>
+    </row>
+    <row r="13" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C13" t="str">
         <f>[2]Sector_Fuels_AGR!L6</f>
         <v>AGRGAS</v>
@@ -12209,8 +12201,8 @@
       </c>
       <c r="H13" s="16"/>
       <c r="I13" s="16"/>
-      <c r="U13" s="125"/>
-      <c r="V13" s="125"/>
+      <c r="U13" s="126"/>
+      <c r="V13" s="126"/>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C14" t="str">
@@ -12229,6 +12221,8 @@
       <c r="H14" s="16"/>
       <c r="I14" s="16"/>
       <c r="O14" s="19"/>
+      <c r="U14" s="126"/>
+      <c r="V14" s="126"/>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C15" t="str">
@@ -12267,6 +12261,8 @@
       <c r="H16" s="16"/>
       <c r="I16" s="16"/>
       <c r="O16" s="19"/>
+      <c r="U16" s="126"/>
+      <c r="V16" s="126"/>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.2">
       <c r="J17" s="16"/>

--- a/VT_REG1_RCA_V12.xlsx
+++ b/VT_REG1_RCA_V12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261015\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C5E1A70-91CA-450A-850A-A7593CD53A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10473616-AD0E-4AF1-85DC-5B6442CB97F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="901" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="901" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB1" sheetId="133" r:id="rId1"/>
@@ -4657,7 +4657,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="183">
   <si>
     <t>CommName</t>
   </si>
@@ -11744,12 +11744,12 @@
     <col min="10" max="10" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="5.5703125" customWidth="1"/>
     <col min="12" max="12" width="8.140625" customWidth="1"/>
-    <col min="13" max="13" width="2" customWidth="1"/>
+    <col min="13" max="13" width="8.85546875" customWidth="1"/>
     <col min="14" max="14" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.140625" customWidth="1"/>
+    <col min="15" max="15" width="57.28515625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="77.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.7109375" customWidth="1"/>
+    <col min="18" max="18" width="16.28515625" customWidth="1"/>
     <col min="19" max="19" width="11.7109375" customWidth="1"/>
     <col min="20" max="20" width="13.42578125" customWidth="1"/>
     <col min="21" max="21" width="13.85546875" customWidth="1"/>
@@ -11841,23 +11841,13 @@
       <c r="Q3" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="R3" s="123" t="s">
-        <v>9</v>
-      </c>
-      <c r="S3" s="123" t="s">
-        <v>10</v>
-      </c>
-      <c r="T3" s="123" t="s">
-        <v>12</v>
-      </c>
-      <c r="U3" s="123" t="s">
-        <v>10</v>
-      </c>
-      <c r="V3" s="123" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="2:22" ht="114" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R3" s="122"/>
+      <c r="S3" s="122"/>
+      <c r="T3" s="122"/>
+      <c r="U3" s="122"/>
+      <c r="V3" s="122"/>
+    </row>
+    <row r="4" spans="2:22" ht="46.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -11882,21 +11872,11 @@
       <c r="Q4" s="125" t="s">
         <v>40</v>
       </c>
-      <c r="R4" s="125" t="s">
-        <v>41</v>
-      </c>
-      <c r="S4" s="125" t="s">
-        <v>28</v>
-      </c>
-      <c r="T4" s="125" t="s">
-        <v>29</v>
-      </c>
-      <c r="U4" s="125" t="s">
-        <v>28</v>
-      </c>
-      <c r="V4" s="125" t="s">
-        <v>29</v>
-      </c>
+      <c r="R4" s="122"/>
+      <c r="S4" s="122"/>
+      <c r="T4" s="122"/>
+      <c r="U4" s="122"/>
+      <c r="V4" s="122"/>
     </row>
     <row r="5" spans="2:22" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="8"/>
@@ -11922,9 +11902,9 @@
         <v>PJ</v>
       </c>
       <c r="Q5" s="157"/>
-      <c r="R5" s="157"/>
-      <c r="S5" s="157"/>
-      <c r="T5" s="157"/>
+      <c r="R5" s="122"/>
+      <c r="S5" s="122"/>
+      <c r="T5" s="122"/>
       <c r="U5" s="122"/>
       <c r="V5" s="122"/>
     </row>
@@ -11946,9 +11926,9 @@
         <v>kt</v>
       </c>
       <c r="Q6" s="126"/>
-      <c r="R6" s="126"/>
-      <c r="S6" s="126"/>
-      <c r="T6" s="126"/>
+      <c r="R6" s="122"/>
+      <c r="S6" s="122"/>
+      <c r="T6" s="122"/>
       <c r="U6" s="122"/>
       <c r="V6" s="122"/>
     </row>
@@ -11956,6 +11936,9 @@
       <c r="G7" s="163" t="s">
         <v>180</v>
       </c>
+      <c r="R7" s="122"/>
+      <c r="S7" s="122"/>
+      <c r="T7" s="122"/>
       <c r="U7" s="122"/>
       <c r="V7" s="122"/>
     </row>
@@ -11978,10 +11961,10 @@
       <c r="O8" s="126"/>
       <c r="P8" s="126"/>
       <c r="Q8" s="126"/>
-      <c r="R8" s="126"/>
-      <c r="S8" s="126"/>
-      <c r="T8" s="126"/>
-      <c r="U8" s="126"/>
+      <c r="R8" s="122"/>
+      <c r="S8" s="122"/>
+      <c r="T8" s="122"/>
+      <c r="U8" s="122"/>
       <c r="V8" s="126"/>
     </row>
     <row r="9" spans="2:22" ht="25.5" x14ac:dyDescent="0.2">
@@ -12030,17 +12013,12 @@
       <c r="Q9" s="123" t="s">
         <v>17</v>
       </c>
-      <c r="R9" s="123" t="s">
-        <v>18</v>
-      </c>
-      <c r="S9" s="123" t="s">
-        <v>19</v>
-      </c>
-      <c r="T9" s="123" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="2:22" ht="113.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="R9" s="122"/>
+      <c r="S9" s="122"/>
+      <c r="T9" s="122"/>
+      <c r="U9" s="122"/>
+    </row>
+    <row r="10" spans="2:22" ht="45.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="15" t="s">
         <v>39</v>
       </c>
@@ -12086,16 +12064,10 @@
       <c r="Q10" s="125" t="s">
         <v>24</v>
       </c>
-      <c r="R10" s="125" t="s">
-        <v>43</v>
-      </c>
-      <c r="S10" s="125" t="s">
-        <v>42</v>
-      </c>
-      <c r="T10" s="125" t="s">
-        <v>25</v>
-      </c>
-      <c r="U10" s="126"/>
+      <c r="R10" s="122"/>
+      <c r="S10" s="122"/>
+      <c r="T10" s="122"/>
+      <c r="U10" s="122"/>
       <c r="V10" s="126"/>
     </row>
     <row r="11" spans="2:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -12122,10 +12094,10 @@
       <c r="O11" s="125"/>
       <c r="P11" s="125"/>
       <c r="Q11" s="125"/>
-      <c r="R11" s="125"/>
-      <c r="S11" s="125"/>
-      <c r="T11" s="125"/>
-      <c r="U11" s="126"/>
+      <c r="R11" s="122"/>
+      <c r="S11" s="122"/>
+      <c r="T11" s="122"/>
+      <c r="U11" s="122"/>
       <c r="V11" s="126"/>
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.2">
@@ -12179,10 +12151,10 @@
         <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
-      <c r="R12" s="126"/>
-      <c r="S12" s="126"/>
-      <c r="T12" s="126"/>
-      <c r="U12" s="126"/>
+      <c r="R12" s="122"/>
+      <c r="S12" s="122"/>
+      <c r="T12" s="122"/>
+      <c r="U12" s="122"/>
       <c r="V12" s="126"/>
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.2">
@@ -12201,7 +12173,10 @@
       </c>
       <c r="H13" s="16"/>
       <c r="I13" s="16"/>
-      <c r="U13" s="126"/>
+      <c r="R13" s="122"/>
+      <c r="S13" s="122"/>
+      <c r="T13" s="122"/>
+      <c r="U13" s="122"/>
       <c r="V13" s="126"/>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.2">

--- a/VT_REG1_RCA_V12.xlsx
+++ b/VT_REG1_RCA_V12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261015\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10473616-AD0E-4AF1-85DC-5B6442CB97F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA4262C5-A6A8-427C-87B3-04E534B60D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="901" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="901" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB1" sheetId="133" r:id="rId1"/>
@@ -815,7 +815,7 @@
     <author>Maurizio Gargiulo</author>
   </authors>
   <commentList>
-    <comment ref="L3" authorId="0" shapeId="0" xr:uid="{5C0567BE-56F7-4695-9FF6-B4B4E14A4D4B}">
+    <comment ref="M3" authorId="0" shapeId="0" xr:uid="{5C0567BE-56F7-4695-9FF6-B4B4E14A4D4B}">
       <text>
         <r>
           <rPr>
@@ -929,7 +929,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q3" authorId="1" shapeId="0" xr:uid="{7713E87A-50E0-4DC4-896E-A24735B02FC8}">
+    <comment ref="R3" authorId="1" shapeId="0" xr:uid="{7713E87A-50E0-4DC4-896E-A24735B02FC8}">
       <text>
         <r>
           <rPr>
@@ -955,7 +955,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R3" authorId="2" shapeId="0" xr:uid="{F56F48DA-0D73-49B8-BF2E-4DDDD72835A7}">
+    <comment ref="S3" authorId="2" shapeId="0" xr:uid="{F56F48DA-0D73-49B8-BF2E-4DDDD72835A7}">
       <text>
         <r>
           <rPr>
@@ -1028,7 +1028,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="2" shapeId="0" xr:uid="{9889F8BB-2635-41C0-A4C3-783650D5B292}">
+    <comment ref="T3" authorId="2" shapeId="0" xr:uid="{9889F8BB-2635-41C0-A4C3-783650D5B292}">
       <text>
         <r>
           <rPr>
@@ -1081,7 +1081,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="2" shapeId="0" xr:uid="{AD9114B1-11E7-4E11-A8AD-6A93F18CBF16}">
+    <comment ref="U3" authorId="2" shapeId="0" xr:uid="{AD9114B1-11E7-4E11-A8AD-6A93F18CBF16}">
       <text>
         <r>
           <rPr>
@@ -1114,7 +1114,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
+    <comment ref="V3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
       <text>
         <r>
           <rPr>
@@ -1167,7 +1167,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
+    <comment ref="W3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
       <text>
         <r>
           <rPr>
@@ -1200,7 +1200,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R9" authorId="2" shapeId="0" xr:uid="{324BCA14-FC8D-4A62-BCD1-18785BA3D75D}">
+    <comment ref="S9" authorId="2" shapeId="0" xr:uid="{324BCA14-FC8D-4A62-BCD1-18785BA3D75D}">
       <text>
         <r>
           <rPr>
@@ -1293,7 +1293,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S9" authorId="1" shapeId="0" xr:uid="{2038C725-F30D-4EC6-B2FA-9206C192223D}">
+    <comment ref="T9" authorId="1" shapeId="0" xr:uid="{2038C725-F30D-4EC6-B2FA-9206C192223D}">
       <text>
         <r>
           <rPr>
@@ -1318,7 +1318,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T9" authorId="2" shapeId="0" xr:uid="{18A5E779-3F07-4FEC-9FC1-0C4FA21B02E2}">
+    <comment ref="U9" authorId="2" shapeId="0" xr:uid="{18A5E779-3F07-4FEC-9FC1-0C4FA21B02E2}">
       <text>
         <r>
           <rPr>
@@ -1381,7 +1381,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L10" authorId="2" shapeId="0" xr:uid="{B540F529-922B-45D8-BEB9-99D56FF3B931}">
+    <comment ref="M10" authorId="2" shapeId="0" xr:uid="{B540F529-922B-45D8-BEB9-99D56FF3B931}">
       <text>
         <r>
           <rPr>
@@ -1624,7 +1624,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U11" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000007000000}">
+    <comment ref="V11" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000007000000}">
       <text>
         <r>
           <rPr>
@@ -1649,7 +1649,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V11" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000008000000}">
+    <comment ref="W11" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000008000000}">
       <text>
         <r>
           <rPr>
@@ -4657,7 +4657,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="183">
   <si>
     <t>CommName</t>
   </si>
@@ -7142,13 +7142,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>123824</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>3811972</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
@@ -10826,7 +10826,7 @@
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B8">
-        <f>DemTechs_AGR!$P8</f>
+        <f>DemTechs_AGR!$Q8</f>
         <v>0</v>
       </c>
       <c r="C8" s="64">
@@ -11729,7 +11729,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B1:V31"/>
+  <dimension ref="B1:W31"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -11742,21 +11742,22 @@
     <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.140625" customWidth="1"/>
     <col min="10" max="10" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.5703125" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" customWidth="1"/>
-    <col min="13" max="13" width="8.85546875" customWidth="1"/>
-    <col min="14" max="14" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="57.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="77.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.28515625" customWidth="1"/>
-    <col min="19" max="19" width="11.7109375" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" customWidth="1"/>
-    <col min="21" max="21" width="13.85546875" customWidth="1"/>
-    <col min="22" max="22" width="8.42578125" customWidth="1"/>
+    <col min="11" max="11" width="12.28515625" customWidth="1"/>
+    <col min="12" max="12" width="5.5703125" customWidth="1"/>
+    <col min="13" max="13" width="8.140625" customWidth="1"/>
+    <col min="14" max="14" width="8.85546875" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="57.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="77.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.28515625" customWidth="1"/>
+    <col min="20" max="20" width="11.7109375" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" customWidth="1"/>
+    <col min="22" max="22" width="13.85546875" customWidth="1"/>
+    <col min="23" max="23" width="8.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:23" ht="15" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
         <v>73</v>
       </c>
@@ -11780,8 +11781,9 @@
       <c r="J1" s="7" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="2" spans="2:22" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="K1" s="7"/>
+    </row>
+    <row r="2" spans="2:23" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="str">
         <f>'EB1'!B8</f>
         <v>AGR</v>
@@ -11810,139 +11812,140 @@
       <c r="J2" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="N2" s="121" t="s">
+      <c r="K2" s="9"/>
+      <c r="O2" s="121" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="121"/>
-      <c r="P2" s="122"/>
+      <c r="P2" s="121"/>
       <c r="Q2" s="122"/>
       <c r="R2" s="122"/>
       <c r="S2" s="122"/>
       <c r="T2" s="122"/>
       <c r="U2" s="122"/>
       <c r="V2" s="122"/>
-    </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="L3" s="123" t="s">
+      <c r="W2" s="122"/>
+    </row>
+    <row r="3" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="M3" s="123" t="s">
         <v>7</v>
       </c>
-      <c r="M3" s="124" t="s">
+      <c r="N3" s="124" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="123" t="s">
-        <v>0</v>
-      </c>
       <c r="O3" s="123" t="s">
+        <v>0</v>
+      </c>
+      <c r="P3" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="P3" s="123" t="s">
+      <c r="Q3" s="123" t="s">
         <v>4</v>
       </c>
-      <c r="Q3" s="123" t="s">
+      <c r="R3" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="R3" s="122"/>
       <c r="S3" s="122"/>
       <c r="T3" s="122"/>
       <c r="U3" s="122"/>
       <c r="V3" s="122"/>
-    </row>
-    <row r="4" spans="2:22" ht="46.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="W3" s="122"/>
+    </row>
+    <row r="4" spans="2:23" ht="46.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
-      <c r="L4" s="125" t="s">
+      <c r="M4" s="125" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="125" t="s">
+      <c r="N4" s="125" t="s">
         <v>31</v>
       </c>
-      <c r="N4" s="125" t="s">
+      <c r="O4" s="125" t="s">
         <v>26</v>
       </c>
-      <c r="O4" s="125" t="s">
+      <c r="P4" s="125" t="s">
         <v>27</v>
       </c>
-      <c r="P4" s="125" t="s">
+      <c r="Q4" s="125" t="s">
         <v>4</v>
       </c>
-      <c r="Q4" s="125" t="s">
+      <c r="R4" s="125" t="s">
         <v>40</v>
       </c>
-      <c r="R4" s="122"/>
       <c r="S4" s="122"/>
       <c r="T4" s="122"/>
       <c r="U4" s="122"/>
       <c r="V4" s="122"/>
-    </row>
-    <row r="5" spans="2:22" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W4" s="122"/>
+    </row>
+    <row r="5" spans="2:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
-      <c r="L5" s="157" t="s">
+      <c r="M5" s="157" t="s">
         <v>83</v>
       </c>
-      <c r="M5" s="126"/>
-      <c r="N5" s="157" t="str">
-        <f>LEFT($L$5,1)&amp;LEFT($B$2,1)&amp;[2]EB2!$C$20</f>
+      <c r="N5" s="126"/>
+      <c r="O5" s="157" t="str">
+        <f>LEFT($M$5,1)&amp;LEFT($B$2,1)&amp;[2]EB2!$C$20</f>
         <v>DAOT</v>
       </c>
-      <c r="O5" s="157" t="str">
+      <c r="P5" s="157" t="str">
         <f>LEFT($D$2,6)&amp;" "&amp;$C$2&amp; " Sector - "&amp;[2]EB2!$X$20</f>
         <v>Demand Agriculture Sector - Demand</v>
       </c>
-      <c r="P5" s="157" t="str">
+      <c r="Q5" s="157" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="Q5" s="157"/>
-      <c r="R5" s="122"/>
+      <c r="R5" s="157"/>
       <c r="S5" s="122"/>
       <c r="T5" s="122"/>
       <c r="U5" s="122"/>
       <c r="V5" s="122"/>
-    </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="L6" s="126" t="s">
+      <c r="W5" s="122"/>
+    </row>
+    <row r="6" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="M6" s="126" t="s">
         <v>106</v>
       </c>
-      <c r="M6" s="126"/>
-      <c r="N6" s="126" t="str">
+      <c r="N6" s="126"/>
+      <c r="O6" s="126" t="str">
         <f>$B$2&amp;[2]EB2!$C$29</f>
         <v>AGRCO2</v>
       </c>
-      <c r="O6" s="126" t="str">
+      <c r="P6" s="126" t="str">
         <f>$C$2&amp;" "&amp;[2]EB2!$C$30</f>
         <v>Agriculture Carbon dioxide</v>
       </c>
-      <c r="P6" s="126" t="str">
+      <c r="Q6" s="126" t="str">
         <f>[2]EB2!$AA$2</f>
         <v>kt</v>
       </c>
-      <c r="Q6" s="126"/>
-      <c r="R6" s="122"/>
+      <c r="R6" s="126"/>
       <c r="S6" s="122"/>
       <c r="T6" s="122"/>
       <c r="U6" s="122"/>
       <c r="V6" s="122"/>
-    </row>
-    <row r="7" spans="2:22" ht="15" x14ac:dyDescent="0.25">
+      <c r="W6" s="122"/>
+    </row>
+    <row r="7" spans="2:23" ht="15" x14ac:dyDescent="0.25">
       <c r="G7" s="163" t="s">
         <v>180</v>
       </c>
-      <c r="R7" s="122"/>
       <c r="S7" s="122"/>
       <c r="T7" s="122"/>
       <c r="U7" s="122"/>
       <c r="V7" s="122"/>
-    </row>
-    <row r="8" spans="2:22" ht="15" x14ac:dyDescent="0.25">
+      <c r="W7" s="122"/>
+    </row>
+    <row r="8" spans="2:23" ht="15" x14ac:dyDescent="0.25">
       <c r="D8" s="4" t="s">
         <v>13</v>
       </c>
@@ -11953,21 +11956,22 @@
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
       <c r="J8" s="13"/>
-      <c r="L8" s="121" t="s">
+      <c r="K8" s="13"/>
+      <c r="M8" s="121" t="s">
         <v>15</v>
       </c>
-      <c r="M8" s="121"/>
-      <c r="N8" s="126"/>
+      <c r="N8" s="121"/>
       <c r="O8" s="126"/>
       <c r="P8" s="126"/>
       <c r="Q8" s="126"/>
-      <c r="R8" s="122"/>
+      <c r="R8" s="126"/>
       <c r="S8" s="122"/>
       <c r="T8" s="122"/>
       <c r="U8" s="122"/>
-      <c r="V8" s="126"/>
-    </row>
-    <row r="9" spans="2:22" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="V8" s="122"/>
+      <c r="W8" s="126"/>
+    </row>
+    <row r="9" spans="2:23" ht="25.5" x14ac:dyDescent="0.2">
       <c r="B9" s="17" t="s">
         <v>1</v>
       </c>
@@ -11995,30 +11999,33 @@
       <c r="J9" s="69" t="s">
         <v>79</v>
       </c>
-      <c r="L9" s="123" t="s">
+      <c r="K9" s="94" t="s">
+        <v>35</v>
+      </c>
+      <c r="M9" s="123" t="s">
         <v>11</v>
       </c>
-      <c r="M9" s="124" t="s">
+      <c r="N9" s="124" t="s">
         <v>30</v>
       </c>
-      <c r="N9" s="123" t="s">
+      <c r="O9" s="123" t="s">
         <v>1</v>
       </c>
-      <c r="O9" s="123" t="s">
+      <c r="P9" s="123" t="s">
         <v>2</v>
       </c>
-      <c r="P9" s="123" t="s">
+      <c r="Q9" s="123" t="s">
         <v>16</v>
       </c>
-      <c r="Q9" s="123" t="s">
+      <c r="R9" s="123" t="s">
         <v>17</v>
       </c>
-      <c r="R9" s="122"/>
       <c r="S9" s="122"/>
       <c r="T9" s="122"/>
       <c r="U9" s="122"/>
-    </row>
-    <row r="10" spans="2:22" ht="45.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="V9" s="122"/>
+    </row>
+    <row r="10" spans="2:23" ht="45.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="15" t="s">
         <v>39</v>
       </c>
@@ -12046,31 +12053,34 @@
       <c r="J10" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="L10" s="125" t="s">
+      <c r="K10" s="94" t="s">
+        <v>154</v>
+      </c>
+      <c r="M10" s="125" t="s">
         <v>38</v>
       </c>
-      <c r="M10" s="125" t="s">
+      <c r="N10" s="125" t="s">
         <v>31</v>
       </c>
-      <c r="N10" s="125" t="s">
+      <c r="O10" s="125" t="s">
         <v>21</v>
       </c>
-      <c r="O10" s="125" t="s">
+      <c r="P10" s="125" t="s">
         <v>22</v>
       </c>
-      <c r="P10" s="125" t="s">
+      <c r="Q10" s="125" t="s">
         <v>23</v>
       </c>
-      <c r="Q10" s="125" t="s">
+      <c r="R10" s="125" t="s">
         <v>24</v>
       </c>
-      <c r="R10" s="122"/>
       <c r="S10" s="122"/>
       <c r="T10" s="122"/>
       <c r="U10" s="122"/>
-      <c r="V10" s="126"/>
-    </row>
-    <row r="11" spans="2:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="V10" s="122"/>
+      <c r="W10" s="126"/>
+    </row>
+    <row r="11" spans="2:23" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B11" s="14" t="s">
         <v>90</v>
       </c>
@@ -12086,23 +12096,24 @@
       <c r="J11" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="L11" s="125" t="s">
+      <c r="K11" s="12"/>
+      <c r="M11" s="125" t="s">
         <v>81</v>
       </c>
-      <c r="M11" s="125"/>
       <c r="N11" s="125"/>
       <c r="O11" s="125"/>
       <c r="P11" s="125"/>
       <c r="Q11" s="125"/>
-      <c r="R11" s="122"/>
+      <c r="R11" s="125"/>
       <c r="S11" s="122"/>
       <c r="T11" s="122"/>
       <c r="U11" s="122"/>
-      <c r="V11" s="126"/>
-    </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="V11" s="122"/>
+      <c r="W11" s="126"/>
+    </row>
+    <row r="12" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B12" t="str">
-        <f>N12</f>
+        <f>O12</f>
         <v>AOTETOT</v>
       </c>
       <c r="C12" t="str">
@@ -12110,7 +12121,7 @@
         <v>AGRCOA</v>
       </c>
       <c r="D12" t="str">
-        <f>$N$5</f>
+        <f>$O$5</f>
         <v>DAOT</v>
       </c>
       <c r="E12" s="6"/>
@@ -12131,33 +12142,34 @@
       <c r="J12" s="39">
         <v>20</v>
       </c>
-      <c r="L12" s="157" t="s">
+      <c r="K12" s="39"/>
+      <c r="M12" s="157" t="s">
         <v>95</v>
       </c>
-      <c r="M12" s="126"/>
-      <c r="N12" s="126" t="str">
+      <c r="N12" s="126"/>
+      <c r="O12" s="126" t="str">
         <f>LEFT($B$2)&amp;[2]EB2!$C$20&amp;$J$2&amp;[2]EB2!$V$2</f>
         <v>AOTETOT</v>
       </c>
-      <c r="O12" s="126" t="str">
+      <c r="P12" s="126" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$J$1&amp;" "&amp;[2]EB2!$X$20&amp;" - "&amp;[2]EB2!$V$2</f>
         <v>Demand Technologies Agriculture Sector - Existing Demand - TOT</v>
       </c>
-      <c r="P12" s="126" t="str">
+      <c r="Q12" s="126" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="Q12" s="126" t="str">
+      <c r="R12" s="126" t="str">
         <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
-      <c r="R12" s="122"/>
       <c r="S12" s="122"/>
       <c r="T12" s="122"/>
       <c r="U12" s="122"/>
-      <c r="V12" s="126"/>
-    </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="V12" s="122"/>
+      <c r="W12" s="126"/>
+    </row>
+    <row r="13" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C13" t="str">
         <f>[2]Sector_Fuels_AGR!L6</f>
         <v>AGRGAS</v>
@@ -12173,13 +12185,14 @@
       </c>
       <c r="H13" s="16"/>
       <c r="I13" s="16"/>
-      <c r="R13" s="122"/>
+      <c r="K13" s="39"/>
       <c r="S13" s="122"/>
       <c r="T13" s="122"/>
       <c r="U13" s="122"/>
-      <c r="V13" s="126"/>
-    </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="V13" s="122"/>
+      <c r="W13" s="126"/>
+    </row>
+    <row r="14" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C14" t="str">
         <f>[2]Sector_Fuels_AGR!L7</f>
         <v>AGROIL</v>
@@ -12195,11 +12208,14 @@
       </c>
       <c r="H14" s="16"/>
       <c r="I14" s="16"/>
-      <c r="O14" s="19"/>
-      <c r="U14" s="126"/>
+      <c r="K14" s="39">
+        <v>8.9932882680000006</v>
+      </c>
+      <c r="P14" s="19"/>
       <c r="V14" s="126"/>
-    </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="126"/>
+    </row>
+    <row r="15" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C15" t="str">
         <f>[2]Sector_Fuels_AGR!L8</f>
         <v>AGRBIO</v>
@@ -12215,11 +12231,12 @@
       </c>
       <c r="H15" s="16"/>
       <c r="I15" s="16"/>
-      <c r="O15" s="19"/>
-      <c r="U15" s="126"/>
+      <c r="K15" s="39"/>
+      <c r="P15" s="19"/>
       <c r="V15" s="126"/>
-    </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="126"/>
+    </row>
+    <row r="16" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C16" t="str">
         <f>[2]Sector_Fuels_AGR!L9</f>
         <v>AGRELC</v>
@@ -12235,61 +12252,64 @@
       </c>
       <c r="H16" s="16"/>
       <c r="I16" s="16"/>
-      <c r="O16" s="19"/>
-      <c r="U16" s="126"/>
+      <c r="K16" s="39"/>
+      <c r="P16" s="19"/>
       <c r="V16" s="126"/>
-    </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="W16" s="126"/>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
       <c r="J17" s="16"/>
       <c r="K17" s="16"/>
-      <c r="Q17" s="19"/>
-    </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="L17" s="16"/>
+      <c r="R17" s="19"/>
+    </row>
+    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
       <c r="J18" s="16"/>
       <c r="K18" s="16"/>
-      <c r="Q18" s="19"/>
-    </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="L18" s="16"/>
+      <c r="R18" s="19"/>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
       <c r="F19" s="95"/>
       <c r="G19" s="95"/>
     </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
       <c r="F20" s="110"/>
       <c r="G20" s="110"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B26" s="39"/>
       <c r="C26" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B27" s="61"/>
       <c r="C27" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:18" x14ac:dyDescent="0.2">
       <c r="F28" s="11"/>
       <c r="G28" s="11"/>
-      <c r="M28" s="1"/>
-    </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="N28" s="1"/>
+    </row>
+    <row r="29" spans="2:18" x14ac:dyDescent="0.2">
       <c r="F29" s="11"/>
       <c r="G29" s="11"/>
-      <c r="M29" s="1"/>
-    </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="N29" s="1"/>
+    </row>
+    <row r="30" spans="2:18" x14ac:dyDescent="0.2">
       <c r="F30" s="11"/>
       <c r="G30" s="11"/>
-      <c r="M30" s="1"/>
-    </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="M31" s="1"/>
+      <c r="N30" s="1"/>
+    </row>
+    <row r="31" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="N31" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="29" type="noConversion"/>
@@ -15923,14 +15943,14 @@
         <v>35</v>
       </c>
       <c r="C15" s="26" t="str">
-        <f>DemTechs_AGR!P5</f>
+        <f>DemTechs_AGR!Q5</f>
         <v>PJ</v>
       </c>
       <c r="D15" s="26" t="s">
         <v>76</v>
       </c>
       <c r="E15" s="114">
-        <f>DemTechs_AGR!L15</f>
+        <f>DemTechs_AGR!M15</f>
         <v>0</v>
       </c>
       <c r="G15" s="1" t="s">
@@ -15953,14 +15973,14 @@
         <v>35</v>
       </c>
       <c r="C16" s="26" t="str">
-        <f>DemTechs_AGR!P6</f>
+        <f>DemTechs_AGR!Q6</f>
         <v>kt</v>
       </c>
       <c r="D16" s="26" t="s">
         <v>76</v>
       </c>
       <c r="E16" s="114">
-        <f>DemTechs_AGR!L14</f>
+        <f>DemTechs_AGR!M14</f>
         <v>0</v>
       </c>
       <c r="G16" s="26" t="s">
@@ -15982,14 +16002,14 @@
         <v>35</v>
       </c>
       <c r="C17" s="26">
-        <f>DemTechs_AGR!P7</f>
+        <f>DemTechs_AGR!Q7</f>
         <v>0</v>
       </c>
       <c r="D17" s="26" t="s">
         <v>76</v>
       </c>
       <c r="E17" s="107">
-        <f>DemTechs_AGR!L16</f>
+        <f>DemTechs_AGR!M16</f>
         <v>0</v>
       </c>
       <c r="G17" s="1" t="s">

--- a/VT_REG1_RCA_V12.xlsx
+++ b/VT_REG1_RCA_V12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261015\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA4262C5-A6A8-427C-87B3-04E534B60D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E92C3D-12FF-4140-B12D-673FD2A0D23A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="901" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="901" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB1" sheetId="133" r:id="rId1"/>
@@ -4657,7 +4657,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="184">
   <si>
     <t>CommName</t>
   </si>
@@ -5206,6 +5206,9 @@
   </si>
   <si>
     <t>Remaining Lifetime</t>
+  </si>
+  <si>
+    <t>AOTETOT</t>
   </si>
 </sst>
 </file>
@@ -8363,143 +8366,6 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="EB2"/>
-      <sheetName val="RES_RCA"/>
-      <sheetName val="Sector_Fuels_AGR"/>
-      <sheetName val="DemTechs_AGR"/>
-      <sheetName val="Sector_Fuels_COM"/>
-      <sheetName val="DemTechs_COM"/>
-      <sheetName val="Sector_Fuels_RSD"/>
-      <sheetName val="DemTechs_RSD"/>
-      <sheetName val="Demands"/>
-      <sheetName val="Emi"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="D2" t="str">
-            <v>COA</v>
-          </cell>
-          <cell r="E2" t="str">
-            <v>GAS</v>
-          </cell>
-          <cell r="F2" t="str">
-            <v>OIL</v>
-          </cell>
-          <cell r="G2" t="str">
-            <v>DSL</v>
-          </cell>
-          <cell r="H2" t="str">
-            <v>KER</v>
-          </cell>
-          <cell r="I2" t="str">
-            <v>LPG</v>
-          </cell>
-          <cell r="J2" t="str">
-            <v>GSL</v>
-          </cell>
-          <cell r="L2" t="str">
-            <v>HFO</v>
-          </cell>
-          <cell r="M2" t="str">
-            <v>OPP</v>
-          </cell>
-          <cell r="O2" t="str">
-            <v>BIO</v>
-          </cell>
-          <cell r="U2" t="str">
-            <v>ELC</v>
-          </cell>
-          <cell r="V2" t="str">
-            <v>TOT</v>
-          </cell>
-          <cell r="AA2" t="str">
-            <v>kt</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="D3" t="str">
-            <v>Solid Fuels</v>
-          </cell>
-          <cell r="E3" t="str">
-            <v>Natural Gas</v>
-          </cell>
-          <cell r="F3" t="str">
-            <v>Crude oil</v>
-          </cell>
-          <cell r="O3" t="str">
-            <v>Biomass</v>
-          </cell>
-          <cell r="U3" t="str">
-            <v>Electricity</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="C20" t="str">
-            <v>OT</v>
-          </cell>
-          <cell r="X20" t="str">
-            <v>Demand</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="C29" t="str">
-            <v>CO2</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="C30" t="str">
-            <v>Carbon dioxide</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2">
-        <row r="5">
-          <cell r="L5" t="str">
-            <v>AGRCOA</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="L6" t="str">
-            <v>AGRGAS</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="L7" t="str">
-            <v>AGROIL</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="L8" t="str">
-            <v>AGRBIO</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="L9" t="str">
-            <v>AGRELC</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
       <sheetName val="EnergyBalance"/>
       <sheetName val="EB1"/>
       <sheetName val="EB2"/>
@@ -8940,6 +8806,143 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="EB2"/>
+      <sheetName val="RES_RCA"/>
+      <sheetName val="Sector_Fuels_AGR"/>
+      <sheetName val="DemTechs_AGR"/>
+      <sheetName val="Sector_Fuels_COM"/>
+      <sheetName val="DemTechs_COM"/>
+      <sheetName val="Sector_Fuels_RSD"/>
+      <sheetName val="DemTechs_RSD"/>
+      <sheetName val="Demands"/>
+      <sheetName val="Emi"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="D2" t="str">
+            <v>COA</v>
+          </cell>
+          <cell r="E2" t="str">
+            <v>GAS</v>
+          </cell>
+          <cell r="F2" t="str">
+            <v>OIL</v>
+          </cell>
+          <cell r="G2" t="str">
+            <v>DSL</v>
+          </cell>
+          <cell r="H2" t="str">
+            <v>KER</v>
+          </cell>
+          <cell r="I2" t="str">
+            <v>LPG</v>
+          </cell>
+          <cell r="J2" t="str">
+            <v>GSL</v>
+          </cell>
+          <cell r="L2" t="str">
+            <v>HFO</v>
+          </cell>
+          <cell r="M2" t="str">
+            <v>OPP</v>
+          </cell>
+          <cell r="O2" t="str">
+            <v>BIO</v>
+          </cell>
+          <cell r="U2" t="str">
+            <v>ELC</v>
+          </cell>
+          <cell r="V2" t="str">
+            <v>TOT</v>
+          </cell>
+          <cell r="AA2" t="str">
+            <v>kt</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="D3" t="str">
+            <v>Solid Fuels</v>
+          </cell>
+          <cell r="E3" t="str">
+            <v>Natural Gas</v>
+          </cell>
+          <cell r="F3" t="str">
+            <v>Crude oil</v>
+          </cell>
+          <cell r="O3" t="str">
+            <v>Biomass</v>
+          </cell>
+          <cell r="U3" t="str">
+            <v>Electricity</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="C20" t="str">
+            <v>OT</v>
+          </cell>
+          <cell r="X20" t="str">
+            <v>Demand</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="C29" t="str">
+            <v>CO2</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="C30" t="str">
+            <v>Carbon dioxide</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2">
+        <row r="5">
+          <cell r="L5" t="str">
+            <v>AGRCOA</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="L6" t="str">
+            <v>AGRGAS</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="L7" t="str">
+            <v>AGROIL</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="L8" t="str">
+            <v>AGRBIO</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="L9" t="str">
+            <v>AGRELC</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -9484,75 +9487,75 @@
         <v>59</v>
       </c>
       <c r="D5" s="143">
-        <f>[3]EB1!D16</f>
+        <f>[2]EB1!D16</f>
         <v>0</v>
       </c>
       <c r="E5" s="143">
-        <f>[3]EB1!E16</f>
+        <f>[2]EB1!E16</f>
         <v>0</v>
       </c>
       <c r="F5" s="144">
-        <f>[3]EB1!F16</f>
+        <f>[2]EB1!F16</f>
         <v>0</v>
       </c>
       <c r="G5" s="143">
-        <f>[3]EB1!G16</f>
+        <f>[2]EB1!G16</f>
         <v>0</v>
       </c>
       <c r="H5" s="143">
-        <f>[3]EB1!H16</f>
+        <f>[2]EB1!H16</f>
         <v>0</v>
       </c>
       <c r="I5" s="143">
-        <f>[3]EB1!I16</f>
+        <f>[2]EB1!I16</f>
         <v>8.7784635600000005</v>
       </c>
       <c r="J5" s="143">
-        <f>[3]EB1!J16</f>
+        <f>[2]EB1!J16</f>
         <v>0</v>
       </c>
       <c r="K5" s="144">
-        <f>[3]EB1!K16</f>
+        <f>[2]EB1!K16</f>
         <v>0</v>
       </c>
       <c r="L5" s="143">
-        <f>[3]EB1!L16</f>
+        <f>[2]EB1!L16</f>
         <v>0</v>
       </c>
       <c r="M5" s="143">
-        <f>[3]EB1!M16</f>
+        <f>[2]EB1!M16</f>
         <v>0</v>
       </c>
       <c r="N5" s="144">
-        <f>[3]EB1!N16</f>
+        <f>[2]EB1!N16</f>
         <v>0</v>
       </c>
       <c r="O5" s="145">
-        <f>[3]EB1!O16</f>
+        <f>[2]EB1!O16</f>
         <v>29.606118840000001</v>
       </c>
       <c r="P5" s="144">
-        <f>[3]EB1!P16</f>
+        <f>[2]EB1!P16</f>
         <v>0</v>
       </c>
       <c r="Q5" s="144">
-        <f>[3]EB1!Q16</f>
+        <f>[2]EB1!Q16</f>
         <v>0</v>
       </c>
       <c r="R5" s="143">
-        <f>[3]EB1!R16</f>
+        <f>[2]EB1!R16</f>
         <v>0</v>
       </c>
       <c r="S5" s="144">
-        <f>[3]EB1!S16</f>
+        <f>[2]EB1!S16</f>
         <v>0</v>
       </c>
       <c r="T5" s="144">
-        <f>[3]EB1!T16</f>
+        <f>[2]EB1!T16</f>
         <v>0</v>
       </c>
       <c r="U5" s="143">
-        <f>[3]EB1!U16</f>
+        <f>[2]EB1!U16</f>
         <v>15.231997080000001</v>
       </c>
       <c r="V5" s="79">
@@ -9568,75 +9571,75 @@
         <v>61</v>
       </c>
       <c r="D6" s="146">
-        <f>[3]EB1!D17</f>
+        <f>[2]EB1!D17</f>
         <v>0</v>
       </c>
       <c r="E6" s="143">
-        <f>[3]EB1!E17</f>
+        <f>[2]EB1!E17</f>
         <v>0</v>
       </c>
       <c r="F6" s="144">
-        <f>[3]EB1!F17</f>
+        <f>[2]EB1!F17</f>
         <v>0</v>
       </c>
       <c r="G6" s="143">
-        <f>[3]EB1!G17</f>
+        <f>[2]EB1!G17</f>
         <v>0</v>
       </c>
       <c r="H6" s="143">
-        <f>[3]EB1!H17</f>
+        <f>[2]EB1!H17</f>
         <v>0</v>
       </c>
       <c r="I6" s="143">
-        <f>[3]EB1!I17</f>
+        <f>[2]EB1!I17</f>
         <v>5.3591040000000003</v>
       </c>
       <c r="J6" s="143">
-        <f>[3]EB1!J17</f>
+        <f>[2]EB1!J17</f>
         <v>0</v>
       </c>
       <c r="K6" s="144">
-        <f>[3]EB1!K17</f>
+        <f>[2]EB1!K17</f>
         <v>0</v>
       </c>
       <c r="L6" s="143">
-        <f>[3]EB1!L17</f>
+        <f>[2]EB1!L17</f>
         <v>0</v>
       </c>
       <c r="M6" s="143">
-        <f>[3]EB1!M17</f>
+        <f>[2]EB1!M17</f>
         <v>2.0264112000000001E-2</v>
       </c>
       <c r="N6" s="144">
-        <f>[3]EB1!N17</f>
+        <f>[2]EB1!N17</f>
         <v>0</v>
       </c>
       <c r="O6" s="143">
-        <f>[3]EB1!O17</f>
+        <f>[2]EB1!O17</f>
         <v>0</v>
       </c>
       <c r="P6" s="144">
-        <f>[3]EB1!P17</f>
+        <f>[2]EB1!P17</f>
         <v>0</v>
       </c>
       <c r="Q6" s="144">
-        <f>[3]EB1!Q17</f>
+        <f>[2]EB1!Q17</f>
         <v>0</v>
       </c>
       <c r="R6" s="143">
-        <f>[3]EB1!R17</f>
+        <f>[2]EB1!R17</f>
         <v>0</v>
       </c>
       <c r="S6" s="144">
-        <f>[3]EB1!S17</f>
+        <f>[2]EB1!S17</f>
         <v>0</v>
       </c>
       <c r="T6" s="144">
-        <f>[3]EB1!T17</f>
+        <f>[2]EB1!T17</f>
         <v>0</v>
       </c>
       <c r="U6" s="143">
-        <f>[3]EB1!U17</f>
+        <f>[2]EB1!U17</f>
         <v>11.973410640000001</v>
       </c>
       <c r="V6" s="79">
@@ -9652,75 +9655,75 @@
         <v>63</v>
       </c>
       <c r="D7" s="132">
-        <f>[3]EB1!D18</f>
+        <f>[2]EB1!D18</f>
         <v>20.32984476</v>
       </c>
       <c r="E7" s="78">
-        <f>[3]EB1!E18</f>
+        <f>[2]EB1!E18</f>
         <v>0</v>
       </c>
       <c r="F7" s="78">
-        <f>[3]EB1!F18</f>
+        <f>[2]EB1!F18</f>
         <v>0</v>
       </c>
       <c r="G7" s="133">
-        <f>[3]EB1!G18</f>
+        <f>[2]EB1!G18</f>
         <v>9.3960165599999996</v>
       </c>
       <c r="H7" s="78">
-        <f>[3]EB1!H18</f>
+        <f>[2]EB1!H18</f>
         <v>0</v>
       </c>
       <c r="I7" s="78">
-        <f>[3]EB1!I18</f>
+        <f>[2]EB1!I18</f>
         <v>2.8470240000000004E-2</v>
       </c>
       <c r="J7" s="78">
-        <f>[3]EB1!J18</f>
+        <f>[2]EB1!J18</f>
         <v>0</v>
       </c>
       <c r="K7" s="78">
-        <f>[3]EB1!K18</f>
+        <f>[2]EB1!K18</f>
         <v>0</v>
       </c>
       <c r="L7" s="78">
-        <f>[3]EB1!L18</f>
+        <f>[2]EB1!L18</f>
         <v>5.0660280000000002E-2</v>
       </c>
       <c r="M7" s="78">
-        <f>[3]EB1!M18</f>
+        <f>[2]EB1!M18</f>
         <v>0</v>
       </c>
       <c r="N7" s="78">
-        <f>[3]EB1!N18</f>
+        <f>[2]EB1!N18</f>
         <v>0</v>
       </c>
       <c r="O7" s="132">
-        <f>[3]EB1!O18</f>
+        <f>[2]EB1!O18</f>
         <v>60.016103280000003</v>
       </c>
       <c r="P7" s="78">
-        <f>[3]EB1!P18</f>
+        <f>[2]EB1!P18</f>
         <v>0</v>
       </c>
       <c r="Q7" s="78">
-        <f>[3]EB1!Q18</f>
+        <f>[2]EB1!Q18</f>
         <v>0</v>
       </c>
       <c r="R7" s="78">
-        <f>[3]EB1!R18</f>
+        <f>[2]EB1!R18</f>
         <v>0</v>
       </c>
       <c r="S7" s="78">
-        <f>[3]EB1!S18</f>
+        <f>[2]EB1!S18</f>
         <v>0</v>
       </c>
       <c r="T7" s="78">
-        <f>[3]EB1!T18</f>
+        <f>[2]EB1!T18</f>
         <v>0</v>
       </c>
       <c r="U7" s="78">
-        <f>[3]EB1!U18</f>
+        <f>[2]EB1!U18</f>
         <v>15.341691240000001</v>
       </c>
       <c r="V7" s="79">
@@ -9736,75 +9739,75 @@
         <v>65</v>
       </c>
       <c r="D8" s="147">
-        <f>[3]EB1!D19</f>
+        <f>[2]EB1!D19</f>
         <v>0</v>
       </c>
       <c r="E8" s="147">
-        <f>[3]EB1!E19</f>
+        <f>[2]EB1!E19</f>
         <v>0</v>
       </c>
       <c r="F8" s="147">
-        <f>[3]EB1!F19</f>
+        <f>[2]EB1!F19</f>
         <v>0</v>
       </c>
       <c r="G8" s="148">
-        <f>[3]EB1!G19</f>
+        <f>[2]EB1!G19</f>
         <v>8.9932464000000003</v>
       </c>
       <c r="H8" s="147">
-        <f>[3]EB1!H19</f>
+        <f>[2]EB1!H19</f>
         <v>0</v>
       </c>
       <c r="I8" s="147">
-        <f>[3]EB1!I19</f>
+        <f>[2]EB1!I19</f>
         <v>0</v>
       </c>
       <c r="J8" s="147">
-        <f>[3]EB1!J19</f>
+        <f>[2]EB1!J19</f>
         <v>0</v>
       </c>
       <c r="K8" s="147">
-        <f>[3]EB1!K19</f>
+        <f>[2]EB1!K19</f>
         <v>0</v>
       </c>
       <c r="L8" s="147">
-        <f>[3]EB1!L19</f>
+        <f>[2]EB1!L19</f>
         <v>0</v>
       </c>
       <c r="M8" s="147">
-        <f>[3]EB1!M19</f>
+        <f>[2]EB1!M19</f>
         <v>0</v>
       </c>
       <c r="N8" s="147">
-        <f>[3]EB1!N19</f>
+        <f>[2]EB1!N19</f>
         <v>0</v>
       </c>
       <c r="O8" s="147">
-        <f>[3]EB1!O19</f>
+        <f>[2]EB1!O19</f>
         <v>0</v>
       </c>
       <c r="P8" s="147">
-        <f>[3]EB1!P19</f>
+        <f>[2]EB1!P19</f>
         <v>0</v>
       </c>
       <c r="Q8" s="147">
-        <f>[3]EB1!Q19</f>
+        <f>[2]EB1!Q19</f>
         <v>0</v>
       </c>
       <c r="R8" s="147">
-        <f>[3]EB1!R19</f>
+        <f>[2]EB1!R19</f>
         <v>0</v>
       </c>
       <c r="S8" s="147">
-        <f>[3]EB1!S19</f>
+        <f>[2]EB1!S19</f>
         <v>4.1868000000000006E-5</v>
       </c>
       <c r="T8" s="147">
-        <f>[3]EB1!T19</f>
+        <f>[2]EB1!T19</f>
         <v>0</v>
       </c>
       <c r="U8" s="147">
-        <f>[3]EB1!U19</f>
+        <f>[2]EB1!U19</f>
         <v>0</v>
       </c>
       <c r="V8" s="42">
@@ -9820,75 +9823,75 @@
         <v>67</v>
       </c>
       <c r="D9" s="78">
-        <f>[3]EB1!D20</f>
+        <f>[2]EB1!D20</f>
         <v>0</v>
       </c>
       <c r="E9" s="78">
-        <f>[3]EB1!E20</f>
+        <f>[2]EB1!E20</f>
         <v>0</v>
       </c>
       <c r="F9" s="78">
-        <f>[3]EB1!F20</f>
+        <f>[2]EB1!F20</f>
         <v>0</v>
       </c>
       <c r="G9" s="134">
-        <f>[3]EB1!G20</f>
+        <f>[2]EB1!G20</f>
         <v>59.234009040000004</v>
       </c>
       <c r="H9" s="131">
-        <f>[3]EB1!H20</f>
+        <f>[2]EB1!H20</f>
         <v>2.9927246400000005</v>
       </c>
       <c r="I9" s="135">
-        <f>[3]EB1!I20</f>
+        <f>[2]EB1!I20</f>
         <v>1.2346873199999999</v>
       </c>
       <c r="J9" s="136">
-        <f>[3]EB1!J20</f>
+        <f>[2]EB1!J20</f>
         <v>28.510014600000005</v>
       </c>
       <c r="K9" s="78">
-        <f>[3]EB1!K20</f>
+        <f>[2]EB1!K20</f>
         <v>0</v>
       </c>
       <c r="L9" s="78">
-        <f>[3]EB1!L20</f>
+        <f>[2]EB1!L20</f>
         <v>1.2556213199999999</v>
       </c>
       <c r="M9" s="78">
-        <f>[3]EB1!M20</f>
+        <f>[2]EB1!M20</f>
         <v>8.1692841600000001</v>
       </c>
       <c r="N9" s="78">
-        <f>[3]EB1!N20</f>
+        <f>[2]EB1!N20</f>
         <v>0</v>
       </c>
       <c r="O9" s="78">
-        <f>[3]EB1!O20</f>
+        <f>[2]EB1!O20</f>
         <v>0</v>
       </c>
       <c r="P9" s="78">
-        <f>[3]EB1!P20</f>
+        <f>[2]EB1!P20</f>
         <v>0</v>
       </c>
       <c r="Q9" s="78">
-        <f>[3]EB1!Q20</f>
+        <f>[2]EB1!Q20</f>
         <v>0</v>
       </c>
       <c r="R9" s="78">
-        <f>[3]EB1!R20</f>
+        <f>[2]EB1!R20</f>
         <v>0</v>
       </c>
       <c r="S9" s="78">
-        <f>[3]EB1!S20</f>
+        <f>[2]EB1!S20</f>
         <v>0</v>
       </c>
       <c r="T9" s="78">
-        <f>[3]EB1!T20</f>
+        <f>[2]EB1!T20</f>
         <v>0</v>
       </c>
       <c r="U9" s="78">
-        <f>[3]EB1!U20</f>
+        <f>[2]EB1!U20</f>
         <v>0</v>
       </c>
       <c r="V9" s="79">
@@ -9904,75 +9907,75 @@
         <v>69</v>
       </c>
       <c r="D10" s="41">
-        <f>[3]EB1!D21</f>
+        <f>[2]EB1!D21</f>
         <v>0</v>
       </c>
       <c r="E10" s="41">
-        <f>[3]EB1!E21</f>
+        <f>[2]EB1!E21</f>
         <v>0</v>
       </c>
       <c r="F10" s="41">
-        <f>[3]EB1!F21</f>
+        <f>[2]EB1!F21</f>
         <v>0</v>
       </c>
       <c r="G10" s="41">
-        <f>[3]EB1!G21</f>
+        <f>[2]EB1!G21</f>
         <v>0</v>
       </c>
       <c r="H10" s="41">
-        <f>[3]EB1!H21</f>
+        <f>[2]EB1!H21</f>
         <v>0</v>
       </c>
       <c r="I10" s="41">
-        <f>[3]EB1!I21</f>
+        <f>[2]EB1!I21</f>
         <v>0</v>
       </c>
       <c r="J10" s="41">
-        <f>[3]EB1!J21</f>
+        <f>[2]EB1!J21</f>
         <v>0</v>
       </c>
       <c r="K10" s="41">
-        <f>[3]EB1!K21</f>
+        <f>[2]EB1!K21</f>
         <v>0</v>
       </c>
       <c r="L10" s="41">
-        <f>[3]EB1!L21</f>
+        <f>[2]EB1!L21</f>
         <v>0</v>
       </c>
       <c r="M10" s="41">
-        <f>[3]EB1!M21</f>
+        <f>[2]EB1!M21</f>
         <v>0</v>
       </c>
       <c r="N10" s="41">
-        <f>[3]EB1!N21</f>
+        <f>[2]EB1!N21</f>
         <v>0</v>
       </c>
       <c r="O10" s="41">
-        <f>[3]EB1!O21</f>
+        <f>[2]EB1!O21</f>
         <v>9.4575625199999998</v>
       </c>
       <c r="P10" s="41">
-        <f>[3]EB1!P21</f>
+        <f>[2]EB1!P21</f>
         <v>0</v>
       </c>
       <c r="Q10" s="41">
-        <f>[3]EB1!Q21</f>
+        <f>[2]EB1!Q21</f>
         <v>0</v>
       </c>
       <c r="R10" s="41">
-        <f>[3]EB1!R21</f>
+        <f>[2]EB1!R21</f>
         <v>0</v>
       </c>
       <c r="S10" s="41">
-        <f>[3]EB1!S21</f>
+        <f>[2]EB1!S21</f>
         <v>2.51208E-4</v>
       </c>
       <c r="T10" s="41">
-        <f>[3]EB1!T21</f>
+        <f>[2]EB1!T21</f>
         <v>1.0048319999999998E-3</v>
       </c>
       <c r="U10" s="41">
-        <f>[3]EB1!U21</f>
+        <f>[2]EB1!U21</f>
         <v>0</v>
       </c>
       <c r="V10" s="80">
@@ -9988,75 +9991,75 @@
         <v>70</v>
       </c>
       <c r="D11" s="78">
-        <f>[3]EB1!D22</f>
+        <f>[2]EB1!D22</f>
         <v>0</v>
       </c>
       <c r="E11" s="78">
-        <f>[3]EB1!E22</f>
+        <f>[2]EB1!E22</f>
         <v>0</v>
       </c>
       <c r="F11" s="78">
-        <f>[3]EB1!F22</f>
+        <f>[2]EB1!F22</f>
         <v>0</v>
       </c>
       <c r="G11" s="78">
-        <f>[3]EB1!G22</f>
+        <f>[2]EB1!G22</f>
         <v>0</v>
       </c>
       <c r="H11" s="78">
-        <f>[3]EB1!H22</f>
+        <f>[2]EB1!H22</f>
         <v>0</v>
       </c>
       <c r="I11" s="78">
-        <f>[3]EB1!I22</f>
+        <f>[2]EB1!I22</f>
         <v>0</v>
       </c>
       <c r="J11" s="78">
-        <f>[3]EB1!J22</f>
+        <f>[2]EB1!J22</f>
         <v>0</v>
       </c>
       <c r="K11" s="78">
-        <f>[3]EB1!K22</f>
+        <f>[2]EB1!K22</f>
         <v>0</v>
       </c>
       <c r="L11" s="78">
-        <f>[3]EB1!L22</f>
+        <f>[2]EB1!L22</f>
         <v>0</v>
       </c>
       <c r="M11" s="78">
-        <f>[3]EB1!M22</f>
+        <f>[2]EB1!M22</f>
         <v>0</v>
       </c>
       <c r="N11" s="78">
-        <f>[3]EB1!N22</f>
+        <f>[2]EB1!N22</f>
         <v>0</v>
       </c>
       <c r="O11" s="78">
-        <f>[3]EB1!O22</f>
+        <f>[2]EB1!O22</f>
         <v>0</v>
       </c>
       <c r="P11" s="78">
-        <f>[3]EB1!P22</f>
+        <f>[2]EB1!P22</f>
         <v>0</v>
       </c>
       <c r="Q11" s="78">
-        <f>[3]EB1!Q22</f>
+        <f>[2]EB1!Q22</f>
         <v>0</v>
       </c>
       <c r="R11" s="78">
-        <f>[3]EB1!R22</f>
+        <f>[2]EB1!R22</f>
         <v>0</v>
       </c>
       <c r="S11" s="78">
-        <f>[3]EB1!S22</f>
+        <f>[2]EB1!S22</f>
         <v>0</v>
       </c>
       <c r="T11" s="78">
-        <f>[3]EB1!T22</f>
+        <f>[2]EB1!T22</f>
         <v>0</v>
       </c>
       <c r="U11" s="78">
-        <f>[3]EB1!U22</f>
+        <f>[2]EB1!U22</f>
         <v>0</v>
       </c>
       <c r="V11" s="79">
@@ -10072,75 +10075,75 @@
         <v>71</v>
       </c>
       <c r="D12" s="78">
-        <f>[3]EB1!D23</f>
+        <f>[2]EB1!D23</f>
         <v>0</v>
       </c>
       <c r="E12" s="78">
-        <f>[3]EB1!E23</f>
+        <f>[2]EB1!E23</f>
         <v>0</v>
       </c>
       <c r="F12" s="78">
-        <f>[3]EB1!F23</f>
+        <f>[2]EB1!F23</f>
         <v>0</v>
       </c>
       <c r="G12" s="78">
-        <f>[3]EB1!G23</f>
+        <f>[2]EB1!G23</f>
         <v>0</v>
       </c>
       <c r="H12" s="78">
-        <f>[3]EB1!H23</f>
+        <f>[2]EB1!H23</f>
         <v>0</v>
       </c>
       <c r="I12" s="78">
-        <f>[3]EB1!I23</f>
+        <f>[2]EB1!I23</f>
         <v>0</v>
       </c>
       <c r="J12" s="78">
-        <f>[3]EB1!J23</f>
+        <f>[2]EB1!J23</f>
         <v>0</v>
       </c>
       <c r="K12" s="78">
-        <f>[3]EB1!K23</f>
+        <f>[2]EB1!K23</f>
         <v>0</v>
       </c>
       <c r="L12" s="78">
-        <f>[3]EB1!L23</f>
+        <f>[2]EB1!L23</f>
         <v>0</v>
       </c>
       <c r="M12" s="78">
-        <f>[3]EB1!M23</f>
+        <f>[2]EB1!M23</f>
         <v>0</v>
       </c>
       <c r="N12" s="78">
-        <f>[3]EB1!N23</f>
+        <f>[2]EB1!N23</f>
         <v>0</v>
       </c>
       <c r="O12" s="41">
-        <f>[3]EB1!O23</f>
+        <f>[2]EB1!O23</f>
         <v>0</v>
       </c>
       <c r="P12" s="41">
-        <f>[3]EB1!P23</f>
+        <f>[2]EB1!P23</f>
         <v>0</v>
       </c>
       <c r="Q12" s="41">
-        <f>[3]EB1!Q23</f>
+        <f>[2]EB1!Q23</f>
         <v>0</v>
       </c>
       <c r="R12" s="78">
-        <f>[3]EB1!R23</f>
+        <f>[2]EB1!R23</f>
         <v>0</v>
       </c>
       <c r="S12" s="78">
-        <f>[3]EB1!S23</f>
+        <f>[2]EB1!S23</f>
         <v>0</v>
       </c>
       <c r="T12" s="78">
-        <f>[3]EB1!T23</f>
+        <f>[2]EB1!T23</f>
         <v>0</v>
       </c>
       <c r="U12" s="78">
-        <f>[3]EB1!U23</f>
+        <f>[2]EB1!U23</f>
         <v>0</v>
       </c>
       <c r="V12" s="79">
@@ -11081,11 +11084,11 @@
       </c>
       <c r="K5" s="126"/>
       <c r="L5" s="126" t="str">
-        <f>$B$2&amp;[2]EB2!$D$2</f>
+        <f>$B$2&amp;[3]EB2!$D$2</f>
         <v>AGRCOA</v>
       </c>
       <c r="M5" s="127" t="str">
-        <f>$C$2&amp;" "&amp;[2]EB2!$D$3</f>
+        <f>$C$2&amp;" "&amp;[3]EB2!$D$3</f>
         <v>Agriculture Solid Fuels</v>
       </c>
       <c r="N5" s="126" t="str">
@@ -11105,11 +11108,11 @@
       <c r="J6" s="126"/>
       <c r="K6" s="126"/>
       <c r="L6" s="126" t="str">
-        <f>$B$2&amp;[2]EB2!$E$2</f>
+        <f>$B$2&amp;[3]EB2!$E$2</f>
         <v>AGRGAS</v>
       </c>
       <c r="M6" s="127" t="str">
-        <f>$C$2&amp;" "&amp;[2]EB2!$E$3</f>
+        <f>$C$2&amp;" "&amp;[3]EB2!$E$3</f>
         <v>Agriculture Natural Gas</v>
       </c>
       <c r="N6" s="126" t="str">
@@ -11129,11 +11132,11 @@
       <c r="J7" s="126"/>
       <c r="K7" s="126"/>
       <c r="L7" s="126" t="str">
-        <f>$B$2&amp;[2]EB2!$F$2</f>
+        <f>$B$2&amp;[3]EB2!$F$2</f>
         <v>AGROIL</v>
       </c>
       <c r="M7" s="127" t="str">
-        <f>$C$2&amp;" "&amp;RIGHT([2]EB2!$F$3,3)</f>
+        <f>$C$2&amp;" "&amp;RIGHT([3]EB2!$F$3,3)</f>
         <v>Agriculture oil</v>
       </c>
       <c r="N7" s="126" t="str">
@@ -11153,11 +11156,11 @@
       <c r="J8" s="126"/>
       <c r="K8" s="126"/>
       <c r="L8" s="126" t="str">
-        <f>$B$2&amp;[2]EB2!$O$2</f>
+        <f>$B$2&amp;[3]EB2!$O$2</f>
         <v>AGRBIO</v>
       </c>
       <c r="M8" s="127" t="str">
-        <f>$C$2&amp;" "&amp;[2]EB2!$O$3</f>
+        <f>$C$2&amp;" "&amp;[3]EB2!$O$3</f>
         <v>Agriculture Biomass</v>
       </c>
       <c r="N8" s="126" t="str">
@@ -11177,11 +11180,11 @@
       <c r="J9" s="126"/>
       <c r="K9" s="126"/>
       <c r="L9" s="126" t="str">
-        <f>$B$2&amp;[2]EB2!$U$2</f>
+        <f>$B$2&amp;[3]EB2!$U$2</f>
         <v>AGRELC</v>
       </c>
       <c r="M9" s="127" t="str">
-        <f>$C$2&amp;" "&amp;[2]EB2!$U$3</f>
+        <f>$C$2&amp;" "&amp;[3]EB2!$U$3</f>
         <v>Agriculture Electricity</v>
       </c>
       <c r="N9" s="126" t="str">
@@ -11445,7 +11448,7 @@
         <v>FTE-AGROIL</v>
       </c>
       <c r="C18" t="str">
-        <f>[2]EB2!$G$2</f>
+        <f>[3]EB2!$G$2</f>
         <v>DSL</v>
       </c>
       <c r="D18" t="str">
@@ -11483,7 +11486,7 @@
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C19" t="str">
-        <f>[2]EB2!$H$2</f>
+        <f>[3]EB2!$H$2</f>
         <v>KER</v>
       </c>
       <c r="E19" s="158"/>
@@ -11513,7 +11516,7 @@
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C20" t="str">
-        <f>[2]EB2!$I$2</f>
+        <f>[3]EB2!$I$2</f>
         <v>LPG</v>
       </c>
       <c r="E20" s="158"/>
@@ -11545,7 +11548,7 @@
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C21" t="str">
-        <f>[2]EB2!$J$2</f>
+        <f>[3]EB2!$J$2</f>
         <v>GSL</v>
       </c>
       <c r="E21" s="158"/>
@@ -11555,7 +11558,7 @@
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C22" t="str">
-        <f>[2]EB2!$L$2</f>
+        <f>[3]EB2!$L$2</f>
         <v>HFO</v>
       </c>
       <c r="E22" s="158"/>
@@ -11565,7 +11568,7 @@
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C23" t="str">
-        <f>[2]EB2!$M$2</f>
+        <f>[3]EB2!$M$2</f>
         <v>OPP</v>
       </c>
       <c r="E23" s="158"/>
@@ -11893,11 +11896,11 @@
       </c>
       <c r="N5" s="126"/>
       <c r="O5" s="157" t="str">
-        <f>LEFT($M$5,1)&amp;LEFT($B$2,1)&amp;[2]EB2!$C$20</f>
+        <f>LEFT($M$5,1)&amp;LEFT($B$2,1)&amp;[3]EB2!$C$20</f>
         <v>DAOT</v>
       </c>
       <c r="P5" s="157" t="str">
-        <f>LEFT($D$2,6)&amp;" "&amp;$C$2&amp; " Sector - "&amp;[2]EB2!$X$20</f>
+        <f>LEFT($D$2,6)&amp;" "&amp;$C$2&amp; " Sector - "&amp;[3]EB2!$X$20</f>
         <v>Demand Agriculture Sector - Demand</v>
       </c>
       <c r="Q5" s="157" t="str">
@@ -11917,15 +11920,15 @@
       </c>
       <c r="N6" s="126"/>
       <c r="O6" s="126" t="str">
-        <f>$B$2&amp;[2]EB2!$C$29</f>
+        <f>$B$2&amp;[3]EB2!$C$29</f>
         <v>AGRCO2</v>
       </c>
       <c r="P6" s="126" t="str">
-        <f>$C$2&amp;" "&amp;[2]EB2!$C$30</f>
+        <f>$C$2&amp;" "&amp;[3]EB2!$C$30</f>
         <v>Agriculture Carbon dioxide</v>
       </c>
       <c r="Q6" s="126" t="str">
-        <f>[2]EB2!$AA$2</f>
+        <f>[3]EB2!$AA$2</f>
         <v>kt</v>
       </c>
       <c r="R6" s="126"/>
@@ -12117,7 +12120,7 @@
         <v>AOTETOT</v>
       </c>
       <c r="C12" t="str">
-        <f>[2]Sector_Fuels_AGR!L5</f>
+        <f>[3]Sector_Fuels_AGR!L5</f>
         <v>AGRCOA</v>
       </c>
       <c r="D12" t="str">
@@ -12148,11 +12151,11 @@
       </c>
       <c r="N12" s="126"/>
       <c r="O12" s="126" t="str">
-        <f>LEFT($B$2)&amp;[2]EB2!$C$20&amp;$J$2&amp;[2]EB2!$V$2</f>
+        <f>LEFT($B$2)&amp;[3]EB2!$C$20&amp;$J$2&amp;[3]EB2!$V$2</f>
         <v>AOTETOT</v>
       </c>
       <c r="P12" s="126" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$J$1&amp;" "&amp;[2]EB2!$X$20&amp;" - "&amp;[2]EB2!$V$2</f>
+        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$J$1&amp;" "&amp;[3]EB2!$X$20&amp;" - "&amp;[3]EB2!$V$2</f>
         <v>Demand Technologies Agriculture Sector - Existing Demand - TOT</v>
       </c>
       <c r="Q12" s="126" t="str">
@@ -12170,9 +12173,16 @@
       <c r="W12" s="126"/>
     </row>
     <row r="13" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
+        <v>183</v>
+      </c>
       <c r="C13" t="str">
-        <f>[2]Sector_Fuels_AGR!L6</f>
+        <f>[3]Sector_Fuels_AGR!L6</f>
         <v>AGRGAS</v>
+      </c>
+      <c r="D13" t="str">
+        <f t="shared" ref="D13:D16" si="0">$O$5</f>
+        <v>DAOT</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="165">
@@ -12183,8 +12193,15 @@
         <f>IF(F13=0,20%,F13*(1+$G$8))</f>
         <v>0.2</v>
       </c>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
+      <c r="H13" s="64">
+        <v>1</v>
+      </c>
+      <c r="I13" s="64">
+        <v>1</v>
+      </c>
+      <c r="J13" s="39">
+        <v>20</v>
+      </c>
       <c r="K13" s="39"/>
       <c r="S13" s="122"/>
       <c r="T13" s="122"/>
@@ -12193,9 +12210,16 @@
       <c r="W13" s="126"/>
     </row>
     <row r="14" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>183</v>
+      </c>
       <c r="C14" t="str">
-        <f>[2]Sector_Fuels_AGR!L7</f>
+        <f>[3]Sector_Fuels_AGR!L7</f>
         <v>AGROIL</v>
+      </c>
+      <c r="D14" t="str">
+        <f t="shared" si="0"/>
+        <v>DAOT</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="165">
@@ -12206,8 +12230,15 @@
         <f>IF(F14=0,20%,F14*(1+$G$8))</f>
         <v>1.2</v>
       </c>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
+      <c r="H14" s="64">
+        <v>1</v>
+      </c>
+      <c r="I14" s="64">
+        <v>1</v>
+      </c>
+      <c r="J14" s="39">
+        <v>20</v>
+      </c>
       <c r="K14" s="39">
         <v>8.9932882680000006</v>
       </c>
@@ -12216,9 +12247,16 @@
       <c r="W14" s="126"/>
     </row>
     <row r="15" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>183</v>
+      </c>
       <c r="C15" t="str">
-        <f>[2]Sector_Fuels_AGR!L8</f>
+        <f>[3]Sector_Fuels_AGR!L8</f>
         <v>AGRBIO</v>
+      </c>
+      <c r="D15" t="str">
+        <f t="shared" si="0"/>
+        <v>DAOT</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="165">
@@ -12229,17 +12267,31 @@
         <f>IF(F15=0,20%,F15*(1+$G$8))</f>
         <v>0.2</v>
       </c>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
+      <c r="H15" s="64">
+        <v>1</v>
+      </c>
+      <c r="I15" s="64">
+        <v>1</v>
+      </c>
+      <c r="J15" s="39">
+        <v>20</v>
+      </c>
       <c r="K15" s="39"/>
       <c r="P15" s="19"/>
       <c r="V15" s="126"/>
       <c r="W15" s="126"/>
     </row>
     <row r="16" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>183</v>
+      </c>
       <c r="C16" t="str">
-        <f>[2]Sector_Fuels_AGR!L9</f>
+        <f>[3]Sector_Fuels_AGR!L9</f>
         <v>AGRELC</v>
+      </c>
+      <c r="D16" t="str">
+        <f t="shared" si="0"/>
+        <v>DAOT</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="165">
@@ -12250,8 +12302,15 @@
         <f>IF(F16=0,20%,F16*(1+$G$8))</f>
         <v>0.2</v>
       </c>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
+      <c r="H16" s="64">
+        <v>1</v>
+      </c>
+      <c r="I16" s="64">
+        <v>1</v>
+      </c>
+      <c r="J16" s="39">
+        <v>20</v>
+      </c>
       <c r="K16" s="39"/>
       <c r="P16" s="19"/>
       <c r="V16" s="126"/>
@@ -13241,7 +13300,7 @@
     <col min="21" max="21" width="8.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:21" ht="15" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
         <v>73</v>
       </c>
@@ -13264,7 +13323,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="str">
         <f>'EB1'!B6</f>
         <v>COM</v>
@@ -13542,7 +13601,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="2:21" ht="34.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:21" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B12" s="15" t="s">
         <v>39</v>
       </c>

--- a/VT_REG1_RCA_V12.xlsx
+++ b/VT_REG1_RCA_V12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261015\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E92C3D-12FF-4140-B12D-673FD2A0D23A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82621706-8F0E-4C6C-BCEC-C66667DA6692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="901" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="901" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB1" sheetId="133" r:id="rId1"/>
@@ -5411,6 +5411,7 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="20">
@@ -8366,6 +8367,143 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
+      <sheetName val="EB2"/>
+      <sheetName val="RES_RCA"/>
+      <sheetName val="Sector_Fuels_AGR"/>
+      <sheetName val="DemTechs_AGR"/>
+      <sheetName val="Sector_Fuels_COM"/>
+      <sheetName val="DemTechs_COM"/>
+      <sheetName val="Sector_Fuels_RSD"/>
+      <sheetName val="DemTechs_RSD"/>
+      <sheetName val="Demands"/>
+      <sheetName val="Emi"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="D2" t="str">
+            <v>COA</v>
+          </cell>
+          <cell r="E2" t="str">
+            <v>GAS</v>
+          </cell>
+          <cell r="F2" t="str">
+            <v>OIL</v>
+          </cell>
+          <cell r="G2" t="str">
+            <v>DSL</v>
+          </cell>
+          <cell r="H2" t="str">
+            <v>KER</v>
+          </cell>
+          <cell r="I2" t="str">
+            <v>LPG</v>
+          </cell>
+          <cell r="J2" t="str">
+            <v>GSL</v>
+          </cell>
+          <cell r="L2" t="str">
+            <v>HFO</v>
+          </cell>
+          <cell r="M2" t="str">
+            <v>OPP</v>
+          </cell>
+          <cell r="O2" t="str">
+            <v>BIO</v>
+          </cell>
+          <cell r="U2" t="str">
+            <v>ELC</v>
+          </cell>
+          <cell r="V2" t="str">
+            <v>TOT</v>
+          </cell>
+          <cell r="AA2" t="str">
+            <v>kt</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="D3" t="str">
+            <v>Solid Fuels</v>
+          </cell>
+          <cell r="E3" t="str">
+            <v>Natural Gas</v>
+          </cell>
+          <cell r="F3" t="str">
+            <v>Crude oil</v>
+          </cell>
+          <cell r="O3" t="str">
+            <v>Biomass</v>
+          </cell>
+          <cell r="U3" t="str">
+            <v>Electricity</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="C20" t="str">
+            <v>OT</v>
+          </cell>
+          <cell r="X20" t="str">
+            <v>Demand</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="C29" t="str">
+            <v>CO2</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="C30" t="str">
+            <v>Carbon dioxide</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2">
+        <row r="5">
+          <cell r="L5" t="str">
+            <v>AGRCOA</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="L6" t="str">
+            <v>AGRGAS</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="L7" t="str">
+            <v>AGROIL</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="L8" t="str">
+            <v>AGRBIO</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="L9" t="str">
+            <v>AGRELC</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
       <sheetName val="EnergyBalance"/>
       <sheetName val="EB1"/>
       <sheetName val="EB2"/>
@@ -8806,143 +8944,6 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="EB2"/>
-      <sheetName val="RES_RCA"/>
-      <sheetName val="Sector_Fuels_AGR"/>
-      <sheetName val="DemTechs_AGR"/>
-      <sheetName val="Sector_Fuels_COM"/>
-      <sheetName val="DemTechs_COM"/>
-      <sheetName val="Sector_Fuels_RSD"/>
-      <sheetName val="DemTechs_RSD"/>
-      <sheetName val="Demands"/>
-      <sheetName val="Emi"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="D2" t="str">
-            <v>COA</v>
-          </cell>
-          <cell r="E2" t="str">
-            <v>GAS</v>
-          </cell>
-          <cell r="F2" t="str">
-            <v>OIL</v>
-          </cell>
-          <cell r="G2" t="str">
-            <v>DSL</v>
-          </cell>
-          <cell r="H2" t="str">
-            <v>KER</v>
-          </cell>
-          <cell r="I2" t="str">
-            <v>LPG</v>
-          </cell>
-          <cell r="J2" t="str">
-            <v>GSL</v>
-          </cell>
-          <cell r="L2" t="str">
-            <v>HFO</v>
-          </cell>
-          <cell r="M2" t="str">
-            <v>OPP</v>
-          </cell>
-          <cell r="O2" t="str">
-            <v>BIO</v>
-          </cell>
-          <cell r="U2" t="str">
-            <v>ELC</v>
-          </cell>
-          <cell r="V2" t="str">
-            <v>TOT</v>
-          </cell>
-          <cell r="AA2" t="str">
-            <v>kt</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="D3" t="str">
-            <v>Solid Fuels</v>
-          </cell>
-          <cell r="E3" t="str">
-            <v>Natural Gas</v>
-          </cell>
-          <cell r="F3" t="str">
-            <v>Crude oil</v>
-          </cell>
-          <cell r="O3" t="str">
-            <v>Biomass</v>
-          </cell>
-          <cell r="U3" t="str">
-            <v>Electricity</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="C20" t="str">
-            <v>OT</v>
-          </cell>
-          <cell r="X20" t="str">
-            <v>Demand</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="C29" t="str">
-            <v>CO2</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="C30" t="str">
-            <v>Carbon dioxide</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2">
-        <row r="5">
-          <cell r="L5" t="str">
-            <v>AGRCOA</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="L6" t="str">
-            <v>AGRGAS</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="L7" t="str">
-            <v>AGROIL</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="L8" t="str">
-            <v>AGRBIO</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="L9" t="str">
-            <v>AGRELC</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -9487,75 +9488,75 @@
         <v>59</v>
       </c>
       <c r="D5" s="143">
-        <f>[2]EB1!D16</f>
+        <f>[3]EB1!D16</f>
         <v>0</v>
       </c>
       <c r="E5" s="143">
-        <f>[2]EB1!E16</f>
+        <f>[3]EB1!E16</f>
         <v>0</v>
       </c>
       <c r="F5" s="144">
-        <f>[2]EB1!F16</f>
+        <f>[3]EB1!F16</f>
         <v>0</v>
       </c>
       <c r="G5" s="143">
-        <f>[2]EB1!G16</f>
+        <f>[3]EB1!G16</f>
         <v>0</v>
       </c>
       <c r="H5" s="143">
-        <f>[2]EB1!H16</f>
+        <f>[3]EB1!H16</f>
         <v>0</v>
       </c>
       <c r="I5" s="143">
-        <f>[2]EB1!I16</f>
+        <f>[3]EB1!I16</f>
         <v>8.7784635600000005</v>
       </c>
       <c r="J5" s="143">
-        <f>[2]EB1!J16</f>
+        <f>[3]EB1!J16</f>
         <v>0</v>
       </c>
       <c r="K5" s="144">
-        <f>[2]EB1!K16</f>
+        <f>[3]EB1!K16</f>
         <v>0</v>
       </c>
       <c r="L5" s="143">
-        <f>[2]EB1!L16</f>
+        <f>[3]EB1!L16</f>
         <v>0</v>
       </c>
       <c r="M5" s="143">
-        <f>[2]EB1!M16</f>
+        <f>[3]EB1!M16</f>
         <v>0</v>
       </c>
       <c r="N5" s="144">
-        <f>[2]EB1!N16</f>
+        <f>[3]EB1!N16</f>
         <v>0</v>
       </c>
       <c r="O5" s="145">
-        <f>[2]EB1!O16</f>
+        <f>[3]EB1!O16</f>
         <v>29.606118840000001</v>
       </c>
       <c r="P5" s="144">
-        <f>[2]EB1!P16</f>
+        <f>[3]EB1!P16</f>
         <v>0</v>
       </c>
       <c r="Q5" s="144">
-        <f>[2]EB1!Q16</f>
+        <f>[3]EB1!Q16</f>
         <v>0</v>
       </c>
       <c r="R5" s="143">
-        <f>[2]EB1!R16</f>
+        <f>[3]EB1!R16</f>
         <v>0</v>
       </c>
       <c r="S5" s="144">
-        <f>[2]EB1!S16</f>
+        <f>[3]EB1!S16</f>
         <v>0</v>
       </c>
       <c r="T5" s="144">
-        <f>[2]EB1!T16</f>
+        <f>[3]EB1!T16</f>
         <v>0</v>
       </c>
       <c r="U5" s="143">
-        <f>[2]EB1!U16</f>
+        <f>[3]EB1!U16</f>
         <v>15.231997080000001</v>
       </c>
       <c r="V5" s="79">
@@ -9571,75 +9572,75 @@
         <v>61</v>
       </c>
       <c r="D6" s="146">
-        <f>[2]EB1!D17</f>
+        <f>[3]EB1!D17</f>
         <v>0</v>
       </c>
       <c r="E6" s="143">
-        <f>[2]EB1!E17</f>
+        <f>[3]EB1!E17</f>
         <v>0</v>
       </c>
       <c r="F6" s="144">
-        <f>[2]EB1!F17</f>
+        <f>[3]EB1!F17</f>
         <v>0</v>
       </c>
       <c r="G6" s="143">
-        <f>[2]EB1!G17</f>
+        <f>[3]EB1!G17</f>
         <v>0</v>
       </c>
       <c r="H6" s="143">
-        <f>[2]EB1!H17</f>
+        <f>[3]EB1!H17</f>
         <v>0</v>
       </c>
       <c r="I6" s="143">
-        <f>[2]EB1!I17</f>
+        <f>[3]EB1!I17</f>
         <v>5.3591040000000003</v>
       </c>
       <c r="J6" s="143">
-        <f>[2]EB1!J17</f>
+        <f>[3]EB1!J17</f>
         <v>0</v>
       </c>
       <c r="K6" s="144">
-        <f>[2]EB1!K17</f>
+        <f>[3]EB1!K17</f>
         <v>0</v>
       </c>
       <c r="L6" s="143">
-        <f>[2]EB1!L17</f>
+        <f>[3]EB1!L17</f>
         <v>0</v>
       </c>
       <c r="M6" s="143">
-        <f>[2]EB1!M17</f>
+        <f>[3]EB1!M17</f>
         <v>2.0264112000000001E-2</v>
       </c>
       <c r="N6" s="144">
-        <f>[2]EB1!N17</f>
+        <f>[3]EB1!N17</f>
         <v>0</v>
       </c>
       <c r="O6" s="143">
-        <f>[2]EB1!O17</f>
+        <f>[3]EB1!O17</f>
         <v>0</v>
       </c>
       <c r="P6" s="144">
-        <f>[2]EB1!P17</f>
+        <f>[3]EB1!P17</f>
         <v>0</v>
       </c>
       <c r="Q6" s="144">
-        <f>[2]EB1!Q17</f>
+        <f>[3]EB1!Q17</f>
         <v>0</v>
       </c>
       <c r="R6" s="143">
-        <f>[2]EB1!R17</f>
+        <f>[3]EB1!R17</f>
         <v>0</v>
       </c>
       <c r="S6" s="144">
-        <f>[2]EB1!S17</f>
+        <f>[3]EB1!S17</f>
         <v>0</v>
       </c>
       <c r="T6" s="144">
-        <f>[2]EB1!T17</f>
+        <f>[3]EB1!T17</f>
         <v>0</v>
       </c>
       <c r="U6" s="143">
-        <f>[2]EB1!U17</f>
+        <f>[3]EB1!U17</f>
         <v>11.973410640000001</v>
       </c>
       <c r="V6" s="79">
@@ -9655,75 +9656,75 @@
         <v>63</v>
       </c>
       <c r="D7" s="132">
-        <f>[2]EB1!D18</f>
+        <f>[3]EB1!D18</f>
         <v>20.32984476</v>
       </c>
       <c r="E7" s="78">
-        <f>[2]EB1!E18</f>
+        <f>[3]EB1!E18</f>
         <v>0</v>
       </c>
       <c r="F7" s="78">
-        <f>[2]EB1!F18</f>
+        <f>[3]EB1!F18</f>
         <v>0</v>
       </c>
       <c r="G7" s="133">
-        <f>[2]EB1!G18</f>
+        <f>[3]EB1!G18</f>
         <v>9.3960165599999996</v>
       </c>
       <c r="H7" s="78">
-        <f>[2]EB1!H18</f>
+        <f>[3]EB1!H18</f>
         <v>0</v>
       </c>
       <c r="I7" s="78">
-        <f>[2]EB1!I18</f>
+        <f>[3]EB1!I18</f>
         <v>2.8470240000000004E-2</v>
       </c>
       <c r="J7" s="78">
-        <f>[2]EB1!J18</f>
+        <f>[3]EB1!J18</f>
         <v>0</v>
       </c>
       <c r="K7" s="78">
-        <f>[2]EB1!K18</f>
+        <f>[3]EB1!K18</f>
         <v>0</v>
       </c>
       <c r="L7" s="78">
-        <f>[2]EB1!L18</f>
+        <f>[3]EB1!L18</f>
         <v>5.0660280000000002E-2</v>
       </c>
       <c r="M7" s="78">
-        <f>[2]EB1!M18</f>
+        <f>[3]EB1!M18</f>
         <v>0</v>
       </c>
       <c r="N7" s="78">
-        <f>[2]EB1!N18</f>
+        <f>[3]EB1!N18</f>
         <v>0</v>
       </c>
       <c r="O7" s="132">
-        <f>[2]EB1!O18</f>
+        <f>[3]EB1!O18</f>
         <v>60.016103280000003</v>
       </c>
       <c r="P7" s="78">
-        <f>[2]EB1!P18</f>
+        <f>[3]EB1!P18</f>
         <v>0</v>
       </c>
       <c r="Q7" s="78">
-        <f>[2]EB1!Q18</f>
+        <f>[3]EB1!Q18</f>
         <v>0</v>
       </c>
       <c r="R7" s="78">
-        <f>[2]EB1!R18</f>
+        <f>[3]EB1!R18</f>
         <v>0</v>
       </c>
       <c r="S7" s="78">
-        <f>[2]EB1!S18</f>
+        <f>[3]EB1!S18</f>
         <v>0</v>
       </c>
       <c r="T7" s="78">
-        <f>[2]EB1!T18</f>
+        <f>[3]EB1!T18</f>
         <v>0</v>
       </c>
       <c r="U7" s="78">
-        <f>[2]EB1!U18</f>
+        <f>[3]EB1!U18</f>
         <v>15.341691240000001</v>
       </c>
       <c r="V7" s="79">
@@ -9739,75 +9740,75 @@
         <v>65</v>
       </c>
       <c r="D8" s="147">
-        <f>[2]EB1!D19</f>
+        <f>[3]EB1!D19</f>
         <v>0</v>
       </c>
       <c r="E8" s="147">
-        <f>[2]EB1!E19</f>
+        <f>[3]EB1!E19</f>
         <v>0</v>
       </c>
       <c r="F8" s="147">
-        <f>[2]EB1!F19</f>
+        <f>[3]EB1!F19</f>
         <v>0</v>
       </c>
       <c r="G8" s="148">
-        <f>[2]EB1!G19</f>
+        <f>[3]EB1!G19</f>
         <v>8.9932464000000003</v>
       </c>
       <c r="H8" s="147">
-        <f>[2]EB1!H19</f>
+        <f>[3]EB1!H19</f>
         <v>0</v>
       </c>
       <c r="I8" s="147">
-        <f>[2]EB1!I19</f>
+        <f>[3]EB1!I19</f>
         <v>0</v>
       </c>
       <c r="J8" s="147">
-        <f>[2]EB1!J19</f>
+        <f>[3]EB1!J19</f>
         <v>0</v>
       </c>
       <c r="K8" s="147">
-        <f>[2]EB1!K19</f>
+        <f>[3]EB1!K19</f>
         <v>0</v>
       </c>
       <c r="L8" s="147">
-        <f>[2]EB1!L19</f>
+        <f>[3]EB1!L19</f>
         <v>0</v>
       </c>
       <c r="M8" s="147">
-        <f>[2]EB1!M19</f>
+        <f>[3]EB1!M19</f>
         <v>0</v>
       </c>
       <c r="N8" s="147">
-        <f>[2]EB1!N19</f>
+        <f>[3]EB1!N19</f>
         <v>0</v>
       </c>
       <c r="O8" s="147">
-        <f>[2]EB1!O19</f>
+        <f>[3]EB1!O19</f>
         <v>0</v>
       </c>
       <c r="P8" s="147">
-        <f>[2]EB1!P19</f>
+        <f>[3]EB1!P19</f>
         <v>0</v>
       </c>
       <c r="Q8" s="147">
-        <f>[2]EB1!Q19</f>
+        <f>[3]EB1!Q19</f>
         <v>0</v>
       </c>
       <c r="R8" s="147">
-        <f>[2]EB1!R19</f>
+        <f>[3]EB1!R19</f>
         <v>0</v>
       </c>
       <c r="S8" s="147">
-        <f>[2]EB1!S19</f>
+        <f>[3]EB1!S19</f>
         <v>4.1868000000000006E-5</v>
       </c>
       <c r="T8" s="147">
-        <f>[2]EB1!T19</f>
+        <f>[3]EB1!T19</f>
         <v>0</v>
       </c>
       <c r="U8" s="147">
-        <f>[2]EB1!U19</f>
+        <f>[3]EB1!U19</f>
         <v>0</v>
       </c>
       <c r="V8" s="42">
@@ -9823,75 +9824,75 @@
         <v>67</v>
       </c>
       <c r="D9" s="78">
-        <f>[2]EB1!D20</f>
+        <f>[3]EB1!D20</f>
         <v>0</v>
       </c>
       <c r="E9" s="78">
-        <f>[2]EB1!E20</f>
+        <f>[3]EB1!E20</f>
         <v>0</v>
       </c>
       <c r="F9" s="78">
-        <f>[2]EB1!F20</f>
+        <f>[3]EB1!F20</f>
         <v>0</v>
       </c>
       <c r="G9" s="134">
-        <f>[2]EB1!G20</f>
+        <f>[3]EB1!G20</f>
         <v>59.234009040000004</v>
       </c>
       <c r="H9" s="131">
-        <f>[2]EB1!H20</f>
+        <f>[3]EB1!H20</f>
         <v>2.9927246400000005</v>
       </c>
       <c r="I9" s="135">
-        <f>[2]EB1!I20</f>
+        <f>[3]EB1!I20</f>
         <v>1.2346873199999999</v>
       </c>
       <c r="J9" s="136">
-        <f>[2]EB1!J20</f>
+        <f>[3]EB1!J20</f>
         <v>28.510014600000005</v>
       </c>
       <c r="K9" s="78">
-        <f>[2]EB1!K20</f>
+        <f>[3]EB1!K20</f>
         <v>0</v>
       </c>
       <c r="L9" s="78">
-        <f>[2]EB1!L20</f>
+        <f>[3]EB1!L20</f>
         <v>1.2556213199999999</v>
       </c>
       <c r="M9" s="78">
-        <f>[2]EB1!M20</f>
+        <f>[3]EB1!M20</f>
         <v>8.1692841600000001</v>
       </c>
       <c r="N9" s="78">
-        <f>[2]EB1!N20</f>
+        <f>[3]EB1!N20</f>
         <v>0</v>
       </c>
       <c r="O9" s="78">
-        <f>[2]EB1!O20</f>
+        <f>[3]EB1!O20</f>
         <v>0</v>
       </c>
       <c r="P9" s="78">
-        <f>[2]EB1!P20</f>
+        <f>[3]EB1!P20</f>
         <v>0</v>
       </c>
       <c r="Q9" s="78">
-        <f>[2]EB1!Q20</f>
+        <f>[3]EB1!Q20</f>
         <v>0</v>
       </c>
       <c r="R9" s="78">
-        <f>[2]EB1!R20</f>
+        <f>[3]EB1!R20</f>
         <v>0</v>
       </c>
       <c r="S9" s="78">
-        <f>[2]EB1!S20</f>
+        <f>[3]EB1!S20</f>
         <v>0</v>
       </c>
       <c r="T9" s="78">
-        <f>[2]EB1!T20</f>
+        <f>[3]EB1!T20</f>
         <v>0</v>
       </c>
       <c r="U9" s="78">
-        <f>[2]EB1!U20</f>
+        <f>[3]EB1!U20</f>
         <v>0</v>
       </c>
       <c r="V9" s="79">
@@ -9907,75 +9908,75 @@
         <v>69</v>
       </c>
       <c r="D10" s="41">
-        <f>[2]EB1!D21</f>
+        <f>[3]EB1!D21</f>
         <v>0</v>
       </c>
       <c r="E10" s="41">
-        <f>[2]EB1!E21</f>
+        <f>[3]EB1!E21</f>
         <v>0</v>
       </c>
       <c r="F10" s="41">
-        <f>[2]EB1!F21</f>
+        <f>[3]EB1!F21</f>
         <v>0</v>
       </c>
       <c r="G10" s="41">
-        <f>[2]EB1!G21</f>
+        <f>[3]EB1!G21</f>
         <v>0</v>
       </c>
       <c r="H10" s="41">
-        <f>[2]EB1!H21</f>
+        <f>[3]EB1!H21</f>
         <v>0</v>
       </c>
       <c r="I10" s="41">
-        <f>[2]EB1!I21</f>
+        <f>[3]EB1!I21</f>
         <v>0</v>
       </c>
       <c r="J10" s="41">
-        <f>[2]EB1!J21</f>
+        <f>[3]EB1!J21</f>
         <v>0</v>
       </c>
       <c r="K10" s="41">
-        <f>[2]EB1!K21</f>
+        <f>[3]EB1!K21</f>
         <v>0</v>
       </c>
       <c r="L10" s="41">
-        <f>[2]EB1!L21</f>
+        <f>[3]EB1!L21</f>
         <v>0</v>
       </c>
       <c r="M10" s="41">
-        <f>[2]EB1!M21</f>
+        <f>[3]EB1!M21</f>
         <v>0</v>
       </c>
       <c r="N10" s="41">
-        <f>[2]EB1!N21</f>
+        <f>[3]EB1!N21</f>
         <v>0</v>
       </c>
       <c r="O10" s="41">
-        <f>[2]EB1!O21</f>
+        <f>[3]EB1!O21</f>
         <v>9.4575625199999998</v>
       </c>
       <c r="P10" s="41">
-        <f>[2]EB1!P21</f>
+        <f>[3]EB1!P21</f>
         <v>0</v>
       </c>
       <c r="Q10" s="41">
-        <f>[2]EB1!Q21</f>
+        <f>[3]EB1!Q21</f>
         <v>0</v>
       </c>
       <c r="R10" s="41">
-        <f>[2]EB1!R21</f>
+        <f>[3]EB1!R21</f>
         <v>0</v>
       </c>
       <c r="S10" s="41">
-        <f>[2]EB1!S21</f>
+        <f>[3]EB1!S21</f>
         <v>2.51208E-4</v>
       </c>
       <c r="T10" s="41">
-        <f>[2]EB1!T21</f>
+        <f>[3]EB1!T21</f>
         <v>1.0048319999999998E-3</v>
       </c>
       <c r="U10" s="41">
-        <f>[2]EB1!U21</f>
+        <f>[3]EB1!U21</f>
         <v>0</v>
       </c>
       <c r="V10" s="80">
@@ -9991,75 +9992,75 @@
         <v>70</v>
       </c>
       <c r="D11" s="78">
-        <f>[2]EB1!D22</f>
+        <f>[3]EB1!D22</f>
         <v>0</v>
       </c>
       <c r="E11" s="78">
-        <f>[2]EB1!E22</f>
+        <f>[3]EB1!E22</f>
         <v>0</v>
       </c>
       <c r="F11" s="78">
-        <f>[2]EB1!F22</f>
+        <f>[3]EB1!F22</f>
         <v>0</v>
       </c>
       <c r="G11" s="78">
-        <f>[2]EB1!G22</f>
+        <f>[3]EB1!G22</f>
         <v>0</v>
       </c>
       <c r="H11" s="78">
-        <f>[2]EB1!H22</f>
+        <f>[3]EB1!H22</f>
         <v>0</v>
       </c>
       <c r="I11" s="78">
-        <f>[2]EB1!I22</f>
+        <f>[3]EB1!I22</f>
         <v>0</v>
       </c>
       <c r="J11" s="78">
-        <f>[2]EB1!J22</f>
+        <f>[3]EB1!J22</f>
         <v>0</v>
       </c>
       <c r="K11" s="78">
-        <f>[2]EB1!K22</f>
+        <f>[3]EB1!K22</f>
         <v>0</v>
       </c>
       <c r="L11" s="78">
-        <f>[2]EB1!L22</f>
+        <f>[3]EB1!L22</f>
         <v>0</v>
       </c>
       <c r="M11" s="78">
-        <f>[2]EB1!M22</f>
+        <f>[3]EB1!M22</f>
         <v>0</v>
       </c>
       <c r="N11" s="78">
-        <f>[2]EB1!N22</f>
+        <f>[3]EB1!N22</f>
         <v>0</v>
       </c>
       <c r="O11" s="78">
-        <f>[2]EB1!O22</f>
+        <f>[3]EB1!O22</f>
         <v>0</v>
       </c>
       <c r="P11" s="78">
-        <f>[2]EB1!P22</f>
+        <f>[3]EB1!P22</f>
         <v>0</v>
       </c>
       <c r="Q11" s="78">
-        <f>[2]EB1!Q22</f>
+        <f>[3]EB1!Q22</f>
         <v>0</v>
       </c>
       <c r="R11" s="78">
-        <f>[2]EB1!R22</f>
+        <f>[3]EB1!R22</f>
         <v>0</v>
       </c>
       <c r="S11" s="78">
-        <f>[2]EB1!S22</f>
+        <f>[3]EB1!S22</f>
         <v>0</v>
       </c>
       <c r="T11" s="78">
-        <f>[2]EB1!T22</f>
+        <f>[3]EB1!T22</f>
         <v>0</v>
       </c>
       <c r="U11" s="78">
-        <f>[2]EB1!U22</f>
+        <f>[3]EB1!U22</f>
         <v>0</v>
       </c>
       <c r="V11" s="79">
@@ -10075,75 +10076,75 @@
         <v>71</v>
       </c>
       <c r="D12" s="78">
-        <f>[2]EB1!D23</f>
+        <f>[3]EB1!D23</f>
         <v>0</v>
       </c>
       <c r="E12" s="78">
-        <f>[2]EB1!E23</f>
+        <f>[3]EB1!E23</f>
         <v>0</v>
       </c>
       <c r="F12" s="78">
-        <f>[2]EB1!F23</f>
+        <f>[3]EB1!F23</f>
         <v>0</v>
       </c>
       <c r="G12" s="78">
-        <f>[2]EB1!G23</f>
+        <f>[3]EB1!G23</f>
         <v>0</v>
       </c>
       <c r="H12" s="78">
-        <f>[2]EB1!H23</f>
+        <f>[3]EB1!H23</f>
         <v>0</v>
       </c>
       <c r="I12" s="78">
-        <f>[2]EB1!I23</f>
+        <f>[3]EB1!I23</f>
         <v>0</v>
       </c>
       <c r="J12" s="78">
-        <f>[2]EB1!J23</f>
+        <f>[3]EB1!J23</f>
         <v>0</v>
       </c>
       <c r="K12" s="78">
-        <f>[2]EB1!K23</f>
+        <f>[3]EB1!K23</f>
         <v>0</v>
       </c>
       <c r="L12" s="78">
-        <f>[2]EB1!L23</f>
+        <f>[3]EB1!L23</f>
         <v>0</v>
       </c>
       <c r="M12" s="78">
-        <f>[2]EB1!M23</f>
+        <f>[3]EB1!M23</f>
         <v>0</v>
       </c>
       <c r="N12" s="78">
-        <f>[2]EB1!N23</f>
+        <f>[3]EB1!N23</f>
         <v>0</v>
       </c>
       <c r="O12" s="41">
-        <f>[2]EB1!O23</f>
+        <f>[3]EB1!O23</f>
         <v>0</v>
       </c>
       <c r="P12" s="41">
-        <f>[2]EB1!P23</f>
+        <f>[3]EB1!P23</f>
         <v>0</v>
       </c>
       <c r="Q12" s="41">
-        <f>[2]EB1!Q23</f>
+        <f>[3]EB1!Q23</f>
         <v>0</v>
       </c>
       <c r="R12" s="78">
-        <f>[2]EB1!R23</f>
+        <f>[3]EB1!R23</f>
         <v>0</v>
       </c>
       <c r="S12" s="78">
-        <f>[2]EB1!S23</f>
+        <f>[3]EB1!S23</f>
         <v>0</v>
       </c>
       <c r="T12" s="78">
-        <f>[2]EB1!T23</f>
+        <f>[3]EB1!T23</f>
         <v>0</v>
       </c>
       <c r="U12" s="78">
-        <f>[2]EB1!U23</f>
+        <f>[3]EB1!U23</f>
         <v>0</v>
       </c>
       <c r="V12" s="79">
@@ -11084,11 +11085,11 @@
       </c>
       <c r="K5" s="126"/>
       <c r="L5" s="126" t="str">
-        <f>$B$2&amp;[3]EB2!$D$2</f>
+        <f>$B$2&amp;[2]EB2!$D$2</f>
         <v>AGRCOA</v>
       </c>
       <c r="M5" s="127" t="str">
-        <f>$C$2&amp;" "&amp;[3]EB2!$D$3</f>
+        <f>$C$2&amp;" "&amp;[2]EB2!$D$3</f>
         <v>Agriculture Solid Fuels</v>
       </c>
       <c r="N5" s="126" t="str">
@@ -11108,11 +11109,11 @@
       <c r="J6" s="126"/>
       <c r="K6" s="126"/>
       <c r="L6" s="126" t="str">
-        <f>$B$2&amp;[3]EB2!$E$2</f>
+        <f>$B$2&amp;[2]EB2!$E$2</f>
         <v>AGRGAS</v>
       </c>
       <c r="M6" s="127" t="str">
-        <f>$C$2&amp;" "&amp;[3]EB2!$E$3</f>
+        <f>$C$2&amp;" "&amp;[2]EB2!$E$3</f>
         <v>Agriculture Natural Gas</v>
       </c>
       <c r="N6" s="126" t="str">
@@ -11132,11 +11133,11 @@
       <c r="J7" s="126"/>
       <c r="K7" s="126"/>
       <c r="L7" s="126" t="str">
-        <f>$B$2&amp;[3]EB2!$F$2</f>
+        <f>$B$2&amp;[2]EB2!$F$2</f>
         <v>AGROIL</v>
       </c>
       <c r="M7" s="127" t="str">
-        <f>$C$2&amp;" "&amp;RIGHT([3]EB2!$F$3,3)</f>
+        <f>$C$2&amp;" "&amp;RIGHT([2]EB2!$F$3,3)</f>
         <v>Agriculture oil</v>
       </c>
       <c r="N7" s="126" t="str">
@@ -11156,11 +11157,11 @@
       <c r="J8" s="126"/>
       <c r="K8" s="126"/>
       <c r="L8" s="126" t="str">
-        <f>$B$2&amp;[3]EB2!$O$2</f>
+        <f>$B$2&amp;[2]EB2!$O$2</f>
         <v>AGRBIO</v>
       </c>
       <c r="M8" s="127" t="str">
-        <f>$C$2&amp;" "&amp;[3]EB2!$O$3</f>
+        <f>$C$2&amp;" "&amp;[2]EB2!$O$3</f>
         <v>Agriculture Biomass</v>
       </c>
       <c r="N8" s="126" t="str">
@@ -11180,11 +11181,11 @@
       <c r="J9" s="126"/>
       <c r="K9" s="126"/>
       <c r="L9" s="126" t="str">
-        <f>$B$2&amp;[3]EB2!$U$2</f>
+        <f>$B$2&amp;[2]EB2!$U$2</f>
         <v>AGRELC</v>
       </c>
       <c r="M9" s="127" t="str">
-        <f>$C$2&amp;" "&amp;[3]EB2!$U$3</f>
+        <f>$C$2&amp;" "&amp;[2]EB2!$U$3</f>
         <v>Agriculture Electricity</v>
       </c>
       <c r="N9" s="126" t="str">
@@ -11448,7 +11449,7 @@
         <v>FTE-AGROIL</v>
       </c>
       <c r="C18" t="str">
-        <f>[3]EB2!$G$2</f>
+        <f>[2]EB2!$G$2</f>
         <v>DSL</v>
       </c>
       <c r="D18" t="str">
@@ -11486,7 +11487,7 @@
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C19" t="str">
-        <f>[3]EB2!$H$2</f>
+        <f>[2]EB2!$H$2</f>
         <v>KER</v>
       </c>
       <c r="E19" s="158"/>
@@ -11516,7 +11517,7 @@
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C20" t="str">
-        <f>[3]EB2!$I$2</f>
+        <f>[2]EB2!$I$2</f>
         <v>LPG</v>
       </c>
       <c r="E20" s="158"/>
@@ -11548,7 +11549,7 @@
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C21" t="str">
-        <f>[3]EB2!$J$2</f>
+        <f>[2]EB2!$J$2</f>
         <v>GSL</v>
       </c>
       <c r="E21" s="158"/>
@@ -11558,7 +11559,7 @@
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C22" t="str">
-        <f>[3]EB2!$L$2</f>
+        <f>[2]EB2!$L$2</f>
         <v>HFO</v>
       </c>
       <c r="E22" s="158"/>
@@ -11568,7 +11569,7 @@
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C23" t="str">
-        <f>[3]EB2!$M$2</f>
+        <f>[2]EB2!$M$2</f>
         <v>OPP</v>
       </c>
       <c r="E23" s="158"/>
@@ -11896,11 +11897,11 @@
       </c>
       <c r="N5" s="126"/>
       <c r="O5" s="157" t="str">
-        <f>LEFT($M$5,1)&amp;LEFT($B$2,1)&amp;[3]EB2!$C$20</f>
+        <f>LEFT($M$5,1)&amp;LEFT($B$2,1)&amp;[2]EB2!$C$20</f>
         <v>DAOT</v>
       </c>
       <c r="P5" s="157" t="str">
-        <f>LEFT($D$2,6)&amp;" "&amp;$C$2&amp; " Sector - "&amp;[3]EB2!$X$20</f>
+        <f>LEFT($D$2,6)&amp;" "&amp;$C$2&amp; " Sector - "&amp;[2]EB2!$X$20</f>
         <v>Demand Agriculture Sector - Demand</v>
       </c>
       <c r="Q5" s="157" t="str">
@@ -11920,15 +11921,15 @@
       </c>
       <c r="N6" s="126"/>
       <c r="O6" s="126" t="str">
-        <f>$B$2&amp;[3]EB2!$C$29</f>
+        <f>$B$2&amp;[2]EB2!$C$29</f>
         <v>AGRCO2</v>
       </c>
       <c r="P6" s="126" t="str">
-        <f>$C$2&amp;" "&amp;[3]EB2!$C$30</f>
+        <f>$C$2&amp;" "&amp;[2]EB2!$C$30</f>
         <v>Agriculture Carbon dioxide</v>
       </c>
       <c r="Q6" s="126" t="str">
-        <f>[3]EB2!$AA$2</f>
+        <f>[2]EB2!$AA$2</f>
         <v>kt</v>
       </c>
       <c r="R6" s="126"/>
@@ -12120,7 +12121,7 @@
         <v>AOTETOT</v>
       </c>
       <c r="C12" t="str">
-        <f>[3]Sector_Fuels_AGR!L5</f>
+        <f>[2]Sector_Fuels_AGR!L5</f>
         <v>AGRCOA</v>
       </c>
       <c r="D12" t="str">
@@ -12151,11 +12152,11 @@
       </c>
       <c r="N12" s="126"/>
       <c r="O12" s="126" t="str">
-        <f>LEFT($B$2)&amp;[3]EB2!$C$20&amp;$J$2&amp;[3]EB2!$V$2</f>
+        <f>LEFT($B$2)&amp;[2]EB2!$C$20&amp;$J$2&amp;[2]EB2!$V$2</f>
         <v>AOTETOT</v>
       </c>
       <c r="P12" s="126" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$J$1&amp;" "&amp;[3]EB2!$X$20&amp;" - "&amp;[3]EB2!$V$2</f>
+        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$J$1&amp;" "&amp;[2]EB2!$X$20&amp;" - "&amp;[2]EB2!$V$2</f>
         <v>Demand Technologies Agriculture Sector - Existing Demand - TOT</v>
       </c>
       <c r="Q12" s="126" t="str">
@@ -12177,7 +12178,7 @@
         <v>183</v>
       </c>
       <c r="C13" t="str">
-        <f>[3]Sector_Fuels_AGR!L6</f>
+        <f>[2]Sector_Fuels_AGR!L6</f>
         <v>AGRGAS</v>
       </c>
       <c r="D13" t="str">
@@ -12214,7 +12215,7 @@
         <v>183</v>
       </c>
       <c r="C14" t="str">
-        <f>[3]Sector_Fuels_AGR!L7</f>
+        <f>[2]Sector_Fuels_AGR!L7</f>
         <v>AGROIL</v>
       </c>
       <c r="D14" t="str">
@@ -12251,7 +12252,7 @@
         <v>183</v>
       </c>
       <c r="C15" t="str">
-        <f>[3]Sector_Fuels_AGR!L8</f>
+        <f>[2]Sector_Fuels_AGR!L8</f>
         <v>AGRBIO</v>
       </c>
       <c r="D15" t="str">
@@ -12286,7 +12287,7 @@
         <v>183</v>
       </c>
       <c r="C16" t="str">
-        <f>[3]Sector_Fuels_AGR!L9</f>
+        <f>[2]Sector_Fuels_AGR!L9</f>
         <v>AGRELC</v>
       </c>
       <c r="D16" t="str">

--- a/VT_REG1_RCA_V12.xlsx
+++ b/VT_REG1_RCA_V12.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr showObjects="placeholders" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261015\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261016\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82621706-8F0E-4C6C-BCEC-C66667DA6692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C086E9-3122-4A90-B308-6A5E825AD4B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="901" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="901" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB1" sheetId="133" r:id="rId1"/>
@@ -33,19 +33,6 @@
     <definedName name="FID_1">[1]AGR_Fuels!$A$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -6158,8 +6145,6 @@
     <xf numFmtId="2" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="18" fillId="10" borderId="23" xfId="8" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="2" fontId="18" fillId="10" borderId="20" xfId="8" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="19" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="24" fillId="13" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -6196,6 +6181,8 @@
     </xf>
     <xf numFmtId="9" fontId="1" fillId="17" borderId="0" xfId="17" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="30" fillId="16" borderId="0" xfId="25" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="19" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="26">
     <cellStyle name="20% - Accent5" xfId="1" builtinId="46"/>
@@ -9293,26 +9280,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:AA33"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.85546875" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="10.85546875" customWidth="1"/>
-    <col min="13" max="13" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="10.85546875" customWidth="1"/>
-    <col min="22" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.88671875" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="10.88671875" customWidth="1"/>
+    <col min="13" max="13" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="10.88671875" customWidth="1"/>
+    <col min="22" max="22" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:27" x14ac:dyDescent="0.25">
       <c r="X1" s="20" t="s">
         <v>92</v>
       </c>
@@ -9326,7 +9313,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="2:27" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:27" ht="15.6" x14ac:dyDescent="0.3">
       <c r="D2" s="35" t="s">
         <v>44</v>
       </c>
@@ -9394,7 +9381,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="3" spans="2:27" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:27" ht="26.4" x14ac:dyDescent="0.25">
       <c r="C3" s="59" t="s">
         <v>125</v>
       </c>
@@ -9456,7 +9443,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B4" s="33"/>
       <c r="C4" s="76" t="s">
         <v>57</v>
@@ -9480,7 +9467,7 @@
       <c r="U4" s="5"/>
       <c r="V4" s="77"/>
     </row>
-    <row r="5" spans="2:27" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:27" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B5" s="37" t="s">
         <v>58</v>
       </c>
@@ -9564,7 +9551,7 @@
         <v>53.616579479999999</v>
       </c>
     </row>
-    <row r="6" spans="2:27" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:27" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B6" s="37" t="s">
         <v>60</v>
       </c>
@@ -9648,7 +9635,7 @@
         <v>17.352778751999999</v>
       </c>
     </row>
-    <row r="7" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B7" s="37" t="s">
         <v>62</v>
       </c>
@@ -9732,82 +9719,82 @@
         <v>105.16278636</v>
       </c>
     </row>
-    <row r="8" spans="2:27" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:27" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B8" s="37" t="s">
         <v>64</v>
       </c>
       <c r="C8" s="47" t="s">
         <v>65</v>
       </c>
-      <c r="D8" s="147">
+      <c r="D8" s="165">
         <f>[3]EB1!D19</f>
         <v>0</v>
       </c>
-      <c r="E8" s="147">
+      <c r="E8" s="165">
         <f>[3]EB1!E19</f>
         <v>0</v>
       </c>
-      <c r="F8" s="147">
+      <c r="F8" s="165">
         <f>[3]EB1!F19</f>
         <v>0</v>
       </c>
-      <c r="G8" s="148">
+      <c r="G8" s="166">
         <f>[3]EB1!G19</f>
         <v>8.9932464000000003</v>
       </c>
-      <c r="H8" s="147">
+      <c r="H8" s="165">
         <f>[3]EB1!H19</f>
         <v>0</v>
       </c>
-      <c r="I8" s="147">
+      <c r="I8" s="165">
         <f>[3]EB1!I19</f>
         <v>0</v>
       </c>
-      <c r="J8" s="147">
+      <c r="J8" s="165">
         <f>[3]EB1!J19</f>
         <v>0</v>
       </c>
-      <c r="K8" s="147">
+      <c r="K8" s="165">
         <f>[3]EB1!K19</f>
         <v>0</v>
       </c>
-      <c r="L8" s="147">
+      <c r="L8" s="165">
         <f>[3]EB1!L19</f>
         <v>0</v>
       </c>
-      <c r="M8" s="147">
+      <c r="M8" s="165">
         <f>[3]EB1!M19</f>
         <v>0</v>
       </c>
-      <c r="N8" s="147">
+      <c r="N8" s="165">
         <f>[3]EB1!N19</f>
         <v>0</v>
       </c>
-      <c r="O8" s="147">
+      <c r="O8" s="165">
         <f>[3]EB1!O19</f>
         <v>0</v>
       </c>
-      <c r="P8" s="147">
+      <c r="P8" s="165">
         <f>[3]EB1!P19</f>
         <v>0</v>
       </c>
-      <c r="Q8" s="147">
+      <c r="Q8" s="165">
         <f>[3]EB1!Q19</f>
         <v>0</v>
       </c>
-      <c r="R8" s="147">
+      <c r="R8" s="165">
         <f>[3]EB1!R19</f>
         <v>0</v>
       </c>
-      <c r="S8" s="147">
+      <c r="S8" s="165">
         <f>[3]EB1!S19</f>
         <v>4.1868000000000006E-5</v>
       </c>
-      <c r="T8" s="147">
+      <c r="T8" s="165">
         <f>[3]EB1!T19</f>
         <v>0</v>
       </c>
-      <c r="U8" s="147">
+      <c r="U8" s="165">
         <f>[3]EB1!U19</f>
         <v>0</v>
       </c>
@@ -9816,7 +9803,7 @@
         <v>8.9932882680000006</v>
       </c>
     </row>
-    <row r="9" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B9" s="37" t="s">
         <v>66</v>
       </c>
@@ -9900,7 +9887,7 @@
         <v>101.39634108000001</v>
       </c>
     </row>
-    <row r="10" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B10" s="37" t="s">
         <v>68</v>
       </c>
@@ -9984,7 +9971,7 @@
         <v>9.4588185599999992</v>
       </c>
     </row>
-    <row r="11" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B11" s="37" t="s">
         <v>85</v>
       </c>
@@ -10068,7 +10055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B12" s="37" t="s">
         <v>86</v>
       </c>
@@ -10152,7 +10139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:27" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:27" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B13" s="75" t="s">
         <v>88</v>
       </c>
@@ -10236,7 +10223,7 @@
         <v>295.9805925</v>
       </c>
     </row>
-    <row r="14" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:27" x14ac:dyDescent="0.25">
       <c r="D14" s="6"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
@@ -10247,7 +10234,7 @@
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
     </row>
-    <row r="15" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:27" x14ac:dyDescent="0.25">
       <c r="D15" s="6"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
@@ -10258,7 +10245,7 @@
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
     </row>
-    <row r="16" spans="2:27" ht="15" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:27" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C16" s="42" t="s">
         <v>147</v>
       </c>
@@ -10273,7 +10260,7 @@
       <c r="L16" s="6"/>
       <c r="M16" s="6"/>
     </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:24" x14ac:dyDescent="0.25">
       <c r="D17" s="6"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
@@ -10284,7 +10271,7 @@
       <c r="L17" s="6"/>
       <c r="M17" s="6"/>
     </row>
-    <row r="18" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:24" x14ac:dyDescent="0.25">
       <c r="D18" s="6"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
@@ -10295,76 +10282,76 @@
       <c r="L18" s="6"/>
       <c r="M18" s="6"/>
     </row>
-    <row r="19" spans="2:24" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:24" ht="26.4" x14ac:dyDescent="0.25">
       <c r="B19" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="C19" s="152" t="s">
+      <c r="C19" s="150" t="s">
         <v>116</v>
       </c>
       <c r="D19" s="84" t="s">
         <v>51</v>
       </c>
-      <c r="E19" s="153" t="s">
+      <c r="E19" s="151" t="s">
         <v>52</v>
       </c>
-      <c r="F19" s="153" t="s">
+      <c r="F19" s="151" t="s">
         <v>127</v>
       </c>
-      <c r="G19" s="153" t="s">
+      <c r="G19" s="151" t="s">
         <v>141</v>
       </c>
-      <c r="H19" s="153" t="s">
+      <c r="H19" s="151" t="s">
         <v>137</v>
       </c>
-      <c r="I19" s="153" t="s">
+      <c r="I19" s="151" t="s">
         <v>130</v>
       </c>
-      <c r="J19" s="153" t="s">
+      <c r="J19" s="151" t="s">
         <v>138</v>
       </c>
-      <c r="K19" s="153" t="s">
+      <c r="K19" s="151" t="s">
         <v>139</v>
       </c>
-      <c r="L19" s="153" t="s">
+      <c r="L19" s="151" t="s">
         <v>135</v>
       </c>
-      <c r="M19" s="153" t="s">
+      <c r="M19" s="151" t="s">
         <v>136</v>
       </c>
-      <c r="N19" s="153" t="s">
+      <c r="N19" s="151" t="s">
         <v>53</v>
       </c>
-      <c r="O19" s="153" t="s">
+      <c r="O19" s="151" t="s">
         <v>163</v>
       </c>
-      <c r="P19" s="153" t="s">
+      <c r="P19" s="151" t="s">
         <v>164</v>
       </c>
-      <c r="Q19" s="153" t="s">
+      <c r="Q19" s="151" t="s">
         <v>165</v>
       </c>
-      <c r="R19" s="153" t="s">
+      <c r="R19" s="151" t="s">
         <v>166</v>
       </c>
-      <c r="S19" s="153" t="s">
+      <c r="S19" s="151" t="s">
         <v>54</v>
       </c>
-      <c r="T19" s="153" t="s">
+      <c r="T19" s="151" t="s">
         <v>55</v>
       </c>
-      <c r="U19" s="154" t="s">
+      <c r="U19" s="152" t="s">
         <v>87</v>
       </c>
-      <c r="V19" s="156" t="s">
+      <c r="V19" s="154" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B20" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="155" t="s">
+      <c r="C20" s="153" t="s">
         <v>68</v>
       </c>
       <c r="D20" s="96"/>
@@ -10391,7 +10378,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="2:24" ht="15" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B21" s="82" t="s">
         <v>58</v>
       </c>
@@ -10428,7 +10415,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="22" spans="2:24" ht="15" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B22" s="82" t="s">
         <v>58</v>
       </c>
@@ -10461,7 +10448,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="23" spans="2:24" ht="15" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B23" s="82" t="s">
         <v>58</v>
       </c>
@@ -10501,7 +10488,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="2:24" ht="15" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B24" s="82" t="s">
         <v>60</v>
       </c>
@@ -10536,7 +10523,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="25" spans="2:24" ht="15" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B25" s="82" t="s">
         <v>60</v>
       </c>
@@ -10569,7 +10556,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="26" spans="2:24" ht="15" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B26" s="82" t="s">
         <v>60</v>
       </c>
@@ -10609,7 +10596,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:24" x14ac:dyDescent="0.25">
       <c r="C29" s="55" t="s">
         <v>107</v>
       </c>
@@ -10620,7 +10607,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="30" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B30" s="20" t="s">
         <v>117</v>
       </c>
@@ -10634,7 +10621,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="31" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B31" s="37" t="s">
         <v>64</v>
       </c>
@@ -10644,7 +10631,7 @@
       <c r="D31" s="87"/>
       <c r="E31" s="88"/>
     </row>
-    <row r="32" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B32" s="37" t="s">
         <v>58</v>
       </c>
@@ -10654,7 +10641,7 @@
       <c r="D32" s="53"/>
       <c r="E32" s="90"/>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B33" s="37" t="s">
         <v>60</v>
       </c>
@@ -10673,20 +10660,20 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="B3:R24"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.42578125" customWidth="1"/>
-    <col min="4" max="4" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.42578125" customWidth="1"/>
-    <col min="14" max="14" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.44140625" customWidth="1"/>
+    <col min="14" max="14" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="15" max="16" width="9" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:18" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="29" t="s">
         <v>155</v>
       </c>
@@ -10703,7 +10690,7 @@
       <c r="M3" s="29"/>
       <c r="N3" s="29"/>
     </row>
-    <row r="4" spans="2:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:18" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="30"/>
       <c r="C4" s="30"/>
       <c r="D4" s="30"/>
@@ -10712,7 +10699,7 @@
       <c r="G4" s="30"/>
       <c r="H4" s="30"/>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5" s="28" t="s">
         <v>142</v>
       </c>
@@ -10723,7 +10710,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="6" spans="2:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="31" t="s">
         <v>0</v>
       </c>
@@ -10780,7 +10767,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="7" spans="2:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="14" t="s">
         <v>90</v>
       </c>
@@ -10828,7 +10815,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B8">
         <f>DemTechs_AGR!$Q8</f>
         <v>0</v>
@@ -10879,13 +10866,13 @@
         <v>112</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="39"/>
       <c r="C23" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="61"/>
       <c r="C24" s="1" t="s">
         <v>150</v>
@@ -10900,20 +10887,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B3:J5"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.85546875" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" customWidth="1"/>
-    <col min="3" max="3" width="6.85546875" customWidth="1"/>
-    <col min="4" max="4" width="5.42578125" customWidth="1"/>
+    <col min="1" max="1" width="1.88671875" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" customWidth="1"/>
+    <col min="3" max="3" width="6.88671875" customWidth="1"/>
+    <col min="4" max="4" width="5.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B3" s="67" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E5" s="68" t="s">
         <v>158</v>
       </c>
@@ -10933,29 +10920,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:R41"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="2.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" customWidth="1"/>
-    <col min="11" max="11" width="7.140625" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.44140625" customWidth="1"/>
+    <col min="11" max="11" width="7.109375" customWidth="1"/>
+    <col min="12" max="12" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="63" customWidth="1"/>
-    <col min="14" max="14" width="6.140625" customWidth="1"/>
-    <col min="15" max="15" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.140625" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="15" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="7" t="s">
         <v>73</v>
       </c>
@@ -10976,7 +10963,7 @@
       </c>
       <c r="H1" s="27"/>
     </row>
-    <row r="2" spans="2:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="9" t="str">
         <f>'EB1'!B8</f>
         <v>AGR</v>
@@ -11012,7 +10999,7 @@
       <c r="Q2" s="122"/>
       <c r="R2" s="122"/>
     </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:18" x14ac:dyDescent="0.25">
       <c r="J3" s="123" t="s">
         <v>7</v>
       </c>
@@ -11041,7 +11028,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:18" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -11075,11 +11062,11 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="E5" s="158"/>
-      <c r="F5" s="158"/>
-      <c r="G5" s="159"/>
-      <c r="H5" s="160"/>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="E5" s="156"/>
+      <c r="F5" s="156"/>
+      <c r="G5" s="157"/>
+      <c r="H5" s="158"/>
       <c r="J5" s="126" t="s">
         <v>72</v>
       </c>
@@ -11101,11 +11088,11 @@
       <c r="Q5" s="126"/>
       <c r="R5" s="126"/>
     </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="E6" s="158"/>
-      <c r="F6" s="158"/>
-      <c r="G6" s="159"/>
-      <c r="H6" s="160"/>
+    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="E6" s="156"/>
+      <c r="F6" s="156"/>
+      <c r="G6" s="157"/>
+      <c r="H6" s="158"/>
       <c r="J6" s="126"/>
       <c r="K6" s="126"/>
       <c r="L6" s="126" t="str">
@@ -11125,11 +11112,11 @@
       <c r="Q6" s="126"/>
       <c r="R6" s="126"/>
     </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="E7" s="158"/>
-      <c r="F7" s="158"/>
-      <c r="G7" s="159"/>
-      <c r="H7" s="160"/>
+    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="E7" s="156"/>
+      <c r="F7" s="156"/>
+      <c r="G7" s="157"/>
+      <c r="H7" s="158"/>
       <c r="J7" s="126"/>
       <c r="K7" s="126"/>
       <c r="L7" s="126" t="str">
@@ -11149,11 +11136,11 @@
       <c r="Q7" s="126"/>
       <c r="R7" s="126"/>
     </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="E8" s="158"/>
-      <c r="F8" s="158"/>
-      <c r="G8" s="159"/>
-      <c r="H8" s="160"/>
+    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="E8" s="156"/>
+      <c r="F8" s="156"/>
+      <c r="G8" s="157"/>
+      <c r="H8" s="158"/>
       <c r="J8" s="126"/>
       <c r="K8" s="126"/>
       <c r="L8" s="126" t="str">
@@ -11173,11 +11160,11 @@
       <c r="Q8" s="126"/>
       <c r="R8" s="126"/>
     </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="E9" s="158"/>
-      <c r="F9" s="158"/>
-      <c r="G9" s="159"/>
-      <c r="H9" s="160"/>
+    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="E9" s="156"/>
+      <c r="F9" s="156"/>
+      <c r="G9" s="157"/>
+      <c r="H9" s="158"/>
       <c r="J9" s="126"/>
       <c r="K9" s="126"/>
       <c r="L9" s="126" t="str">
@@ -11201,18 +11188,18 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="E10" s="158"/>
-      <c r="F10" s="158"/>
-      <c r="G10" s="159"/>
-      <c r="H10" s="160"/>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="E10" s="156"/>
+      <c r="F10" s="156"/>
+      <c r="G10" s="157"/>
+      <c r="H10" s="158"/>
       <c r="M10" s="19"/>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="L11" s="23"/>
       <c r="M11" s="24"/>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D12" s="4" t="s">
         <v>13</v>
       </c>
@@ -11230,7 +11217,7 @@
       <c r="Q12" s="126"/>
       <c r="R12" s="126"/>
     </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="17" t="s">
         <v>1</v>
       </c>
@@ -11280,7 +11267,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="2:18" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="15" t="s">
         <v>39</v>
       </c>
@@ -11330,7 +11317,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="2:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="14" t="s">
         <v>90</v>
       </c>
@@ -11357,7 +11344,7 @@
       <c r="Q15" s="128"/>
       <c r="R15" s="128"/>
     </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" t="str">
         <f>L16</f>
         <v>FTE-AGRCOA</v>
@@ -11370,14 +11357,14 @@
         <f>L5</f>
         <v>AGRCOA</v>
       </c>
-      <c r="E16" s="158"/>
-      <c r="G16" s="161">
+      <c r="E16" s="156"/>
+      <c r="G16" s="159">
         <v>1</v>
       </c>
-      <c r="H16" s="162">
+      <c r="H16" s="160">
         <v>30</v>
       </c>
-      <c r="J16" s="157" t="s">
+      <c r="J16" s="155" t="s">
         <v>113</v>
       </c>
       <c r="K16" s="126"/>
@@ -11401,7 +11388,7 @@
       <c r="Q16" s="126"/>
       <c r="R16" s="126"/>
     </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" t="str">
         <f>L17</f>
         <v>FTE-AGRGAS</v>
@@ -11414,11 +11401,11 @@
         <f>L6</f>
         <v>AGRGAS</v>
       </c>
-      <c r="E17" s="158"/>
-      <c r="G17" s="161">
+      <c r="E17" s="156"/>
+      <c r="G17" s="159">
         <v>1</v>
       </c>
-      <c r="H17" s="162">
+      <c r="H17" s="160">
         <v>30</v>
       </c>
       <c r="J17" s="126"/>
@@ -11443,7 +11430,7 @@
       <c r="Q17" s="126"/>
       <c r="R17" s="126"/>
     </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" t="str">
         <f>L18</f>
         <v>FTE-AGROIL</v>
@@ -11456,11 +11443,11 @@
         <f>L7</f>
         <v>AGROIL</v>
       </c>
-      <c r="E18" s="158"/>
-      <c r="G18" s="161">
+      <c r="E18" s="156"/>
+      <c r="G18" s="159">
         <v>1</v>
       </c>
-      <c r="H18" s="162">
+      <c r="H18" s="160">
         <v>30</v>
       </c>
       <c r="J18" s="126"/>
@@ -11485,14 +11472,14 @@
       <c r="Q18" s="126"/>
       <c r="R18" s="126"/>
     </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C19" t="str">
         <f>[2]EB2!$H$2</f>
         <v>KER</v>
       </c>
-      <c r="E19" s="158"/>
-      <c r="G19" s="159"/>
-      <c r="H19" s="160"/>
+      <c r="E19" s="156"/>
+      <c r="G19" s="157"/>
+      <c r="H19" s="158"/>
       <c r="J19" s="126"/>
       <c r="K19" s="126"/>
       <c r="L19" s="126" t="str">
@@ -11515,14 +11502,14 @@
       <c r="Q19" s="126"/>
       <c r="R19" s="126"/>
     </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C20" t="str">
         <f>[2]EB2!$I$2</f>
         <v>LPG</v>
       </c>
-      <c r="E20" s="158"/>
-      <c r="G20" s="159"/>
-      <c r="H20" s="160"/>
+      <c r="E20" s="156"/>
+      <c r="G20" s="157"/>
+      <c r="H20" s="158"/>
       <c r="J20" s="126"/>
       <c r="K20" s="126"/>
       <c r="L20" s="126" t="str">
@@ -11547,37 +11534,37 @@
       <c r="Q20" s="126"/>
       <c r="R20" s="126"/>
     </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C21" t="str">
         <f>[2]EB2!$J$2</f>
         <v>GSL</v>
       </c>
-      <c r="E21" s="158"/>
-      <c r="G21" s="159"/>
-      <c r="H21" s="160"/>
+      <c r="E21" s="156"/>
+      <c r="G21" s="157"/>
+      <c r="H21" s="158"/>
       <c r="M21" s="19"/>
     </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C22" t="str">
         <f>[2]EB2!$L$2</f>
         <v>HFO</v>
       </c>
-      <c r="E22" s="158"/>
-      <c r="G22" s="159"/>
-      <c r="H22" s="160"/>
+      <c r="E22" s="156"/>
+      <c r="G22" s="157"/>
+      <c r="H22" s="158"/>
       <c r="M22" s="19"/>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C23" t="str">
         <f>[2]EB2!$M$2</f>
         <v>OPP</v>
       </c>
-      <c r="E23" s="158"/>
-      <c r="G23" s="159"/>
-      <c r="H23" s="160"/>
+      <c r="E23" s="156"/>
+      <c r="G23" s="157"/>
+      <c r="H23" s="158"/>
       <c r="M23" s="19"/>
     </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B24" t="str">
         <f>L19</f>
         <v>FTE-AGRBIO</v>
@@ -11590,18 +11577,18 @@
         <f>L8</f>
         <v>AGRBIO</v>
       </c>
-      <c r="E24" s="158"/>
-      <c r="G24" s="161">
+      <c r="E24" s="156"/>
+      <c r="G24" s="159">
         <v>1</v>
       </c>
-      <c r="H24" s="162">
+      <c r="H24" s="160">
         <v>30</v>
       </c>
       <c r="J24" s="23"/>
       <c r="K24" s="23"/>
       <c r="M24" s="19"/>
     </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B25" t="str">
         <f>L20</f>
         <v>FTE-AGRELC</v>
@@ -11614,18 +11601,18 @@
         <f>L9</f>
         <v>AGRELC</v>
       </c>
-      <c r="E25" s="158"/>
-      <c r="G25" s="161">
+      <c r="E25" s="156"/>
+      <c r="G25" s="159">
         <v>1</v>
       </c>
-      <c r="H25" s="162">
+      <c r="H25" s="160">
         <v>30</v>
       </c>
       <c r="J25" s="23"/>
       <c r="K25" s="23"/>
       <c r="M25" s="19"/>
     </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
       <c r="G26" s="66"/>
@@ -11634,20 +11621,20 @@
       <c r="K26" s="23"/>
       <c r="M26" s="19"/>
     </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
       <c r="G27" s="66"/>
       <c r="H27" s="10"/>
       <c r="M27" s="19"/>
     </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
       <c r="G28" s="66"/>
       <c r="H28" s="10"/>
     </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B29" s="23"/>
       <c r="D29" s="23"/>
       <c r="E29" s="11"/>
@@ -11655,7 +11642,7 @@
       <c r="G29" s="66"/>
       <c r="H29" s="10"/>
     </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B30" s="23"/>
       <c r="D30" s="23"/>
       <c r="E30" s="11"/>
@@ -11663,7 +11650,7 @@
       <c r="G30" s="66"/>
       <c r="H30" s="10"/>
     </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B31" s="23"/>
       <c r="D31" s="23"/>
       <c r="E31" s="95"/>
@@ -11671,7 +11658,7 @@
       <c r="G31" s="66"/>
       <c r="H31" s="10"/>
     </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B32" s="23"/>
       <c r="D32" s="23"/>
       <c r="E32" s="95"/>
@@ -11679,7 +11666,7 @@
       <c r="G32" s="66"/>
       <c r="H32" s="10"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B33" s="23"/>
       <c r="D33" s="23"/>
       <c r="E33" s="95"/>
@@ -11687,7 +11674,7 @@
       <c r="G33" s="66"/>
       <c r="H33" s="10"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="23"/>
       <c r="D34" s="23"/>
       <c r="E34" s="95"/>
@@ -11695,7 +11682,7 @@
       <c r="G34" s="66"/>
       <c r="H34" s="10"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="23"/>
       <c r="D35" s="23"/>
       <c r="E35" s="11"/>
@@ -11703,7 +11690,7 @@
       <c r="G35" s="66"/>
       <c r="H35" s="10"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="23"/>
       <c r="D36" s="23"/>
       <c r="E36" s="11"/>
@@ -11711,13 +11698,13 @@
       <c r="G36" s="66"/>
       <c r="H36" s="10"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B40" s="39"/>
       <c r="C40" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B41" s="61"/>
       <c r="C41" s="1" t="s">
         <v>150</v>
@@ -11734,34 +11721,34 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:W31"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" customWidth="1"/>
-    <col min="12" max="12" width="5.5703125" customWidth="1"/>
-    <col min="13" max="13" width="8.140625" customWidth="1"/>
-    <col min="14" max="14" width="8.85546875" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="57.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="77.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.28515625" customWidth="1"/>
-    <col min="20" max="20" width="11.7109375" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" customWidth="1"/>
-    <col min="22" max="22" width="13.85546875" customWidth="1"/>
-    <col min="23" max="23" width="8.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.109375" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" customWidth="1"/>
+    <col min="12" max="12" width="5.5546875" customWidth="1"/>
+    <col min="13" max="13" width="8.109375" customWidth="1"/>
+    <col min="14" max="14" width="8.88671875" customWidth="1"/>
+    <col min="15" max="15" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="57.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="77.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.33203125" customWidth="1"/>
+    <col min="20" max="20" width="11.6640625" customWidth="1"/>
+    <col min="21" max="21" width="13.44140625" customWidth="1"/>
+    <col min="22" max="22" width="13.88671875" customWidth="1"/>
+    <col min="23" max="23" width="8.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:23" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="7" t="s">
         <v>73</v>
       </c>
@@ -11787,7 +11774,7 @@
       </c>
       <c r="K1" s="7"/>
     </row>
-    <row r="2" spans="2:23" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:23" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B2" s="9" t="str">
         <f>'EB1'!B8</f>
         <v>AGR</v>
@@ -11829,7 +11816,7 @@
       <c r="V2" s="122"/>
       <c r="W2" s="122"/>
     </row>
-    <row r="3" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:23" x14ac:dyDescent="0.25">
       <c r="M3" s="123" t="s">
         <v>7</v>
       </c>
@@ -11854,7 +11841,7 @@
       <c r="V3" s="122"/>
       <c r="W3" s="122"/>
     </row>
-    <row r="4" spans="2:23" ht="46.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:23" ht="42.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -11885,37 +11872,37 @@
       <c r="V4" s="122"/>
       <c r="W4" s="122"/>
     </row>
-    <row r="5" spans="2:23" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
-      <c r="M5" s="157" t="s">
+      <c r="M5" s="155" t="s">
         <v>83</v>
       </c>
       <c r="N5" s="126"/>
-      <c r="O5" s="157" t="str">
+      <c r="O5" s="155" t="str">
         <f>LEFT($M$5,1)&amp;LEFT($B$2,1)&amp;[2]EB2!$C$20</f>
         <v>DAOT</v>
       </c>
-      <c r="P5" s="157" t="str">
+      <c r="P5" s="155" t="str">
         <f>LEFT($D$2,6)&amp;" "&amp;$C$2&amp; " Sector - "&amp;[2]EB2!$X$20</f>
         <v>Demand Agriculture Sector - Demand</v>
       </c>
-      <c r="Q5" s="157" t="str">
+      <c r="Q5" s="155" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="R5" s="157"/>
+      <c r="R5" s="155"/>
       <c r="S5" s="122"/>
       <c r="T5" s="122"/>
       <c r="U5" s="122"/>
       <c r="V5" s="122"/>
       <c r="W5" s="122"/>
     </row>
-    <row r="6" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:23" x14ac:dyDescent="0.25">
       <c r="M6" s="126" t="s">
         <v>106</v>
       </c>
@@ -11939,8 +11926,8 @@
       <c r="V6" s="122"/>
       <c r="W6" s="122"/>
     </row>
-    <row r="7" spans="2:23" ht="15" x14ac:dyDescent="0.25">
-      <c r="G7" s="163" t="s">
+    <row r="7" spans="2:23" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="G7" s="161" t="s">
         <v>180</v>
       </c>
       <c r="S7" s="122"/>
@@ -11949,12 +11936,12 @@
       <c r="V7" s="122"/>
       <c r="W7" s="122"/>
     </row>
-    <row r="8" spans="2:23" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:23" ht="14.4" x14ac:dyDescent="0.3">
       <c r="D8" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E8" s="4"/>
-      <c r="G8" s="164">
+      <c r="G8" s="162">
         <v>0.2</v>
       </c>
       <c r="H8" s="4"/>
@@ -11975,7 +11962,7 @@
       <c r="V8" s="122"/>
       <c r="W8" s="126"/>
     </row>
-    <row r="9" spans="2:23" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:23" ht="26.4" x14ac:dyDescent="0.25">
       <c r="B9" s="17" t="s">
         <v>1</v>
       </c>
@@ -12029,7 +12016,7 @@
       <c r="U9" s="122"/>
       <c r="V9" s="122"/>
     </row>
-    <row r="10" spans="2:23" ht="45.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:23" ht="42" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="15" t="s">
         <v>39</v>
       </c>
@@ -12084,7 +12071,7 @@
       <c r="V10" s="122"/>
       <c r="W10" s="126"/>
     </row>
-    <row r="11" spans="2:23" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:23" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="14" t="s">
         <v>90</v>
       </c>
@@ -12115,7 +12102,7 @@
       <c r="V11" s="122"/>
       <c r="W11" s="126"/>
     </row>
-    <row r="12" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B12" t="str">
         <f>O12</f>
         <v>AOTETOT</v>
@@ -12129,13 +12116,12 @@
         <v>DAOT</v>
       </c>
       <c r="E12" s="6"/>
-      <c r="F12" s="165">
+      <c r="F12" s="163">
         <f>'EB1'!D8/('EB1'!$D$8+'EB1'!$E$8+SUM('EB1'!$G$8:$J$8,'EB1'!$M$8,'EB1'!$L$8)+'EB1'!$O$8+'EB1'!$U$8)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="166">
-        <f>IF(F12=0,20%,F12*(1+$G$8))</f>
-        <v>0.2</v>
+      <c r="G12" s="164">
+        <v>0</v>
       </c>
       <c r="H12" s="64">
         <v>1</v>
@@ -12147,7 +12133,7 @@
         <v>20</v>
       </c>
       <c r="K12" s="39"/>
-      <c r="M12" s="157" t="s">
+      <c r="M12" s="155" t="s">
         <v>95</v>
       </c>
       <c r="N12" s="126"/>
@@ -12173,7 +12159,7 @@
       <c r="V12" s="122"/>
       <c r="W12" s="126"/>
     </row>
-    <row r="13" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>183</v>
       </c>
@@ -12186,13 +12172,12 @@
         <v>DAOT</v>
       </c>
       <c r="E13" s="6"/>
-      <c r="F13" s="165">
+      <c r="F13" s="163">
         <f>'EB1'!E8/('EB1'!$D$8+'EB1'!$E$8+SUM('EB1'!$G$8:$J$8,'EB1'!$M$8,'EB1'!$L$8)+'EB1'!$O$8+'EB1'!$U$8)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="166">
-        <f>IF(F13=0,20%,F13*(1+$G$8))</f>
-        <v>0.2</v>
+      <c r="G13" s="164">
+        <v>0</v>
       </c>
       <c r="H13" s="64">
         <v>1</v>
@@ -12210,7 +12195,7 @@
       <c r="V13" s="122"/>
       <c r="W13" s="126"/>
     </row>
-    <row r="14" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>183</v>
       </c>
@@ -12223,11 +12208,11 @@
         <v>DAOT</v>
       </c>
       <c r="E14" s="6"/>
-      <c r="F14" s="165">
+      <c r="F14" s="163">
         <f>SUM('EB1'!G8:J8,'EB1'!L8:M8)/('EB1'!$D$8+'EB1'!$E$8+SUM('EB1'!$G$8:$J$8,'EB1'!$M$8,'EB1'!$L$8)+'EB1'!$O$8+'EB1'!$U$8)</f>
         <v>1</v>
       </c>
-      <c r="G14" s="166">
+      <c r="G14" s="164">
         <f>IF(F14=0,20%,F14*(1+$G$8))</f>
         <v>1.2</v>
       </c>
@@ -12247,7 +12232,7 @@
       <c r="V14" s="126"/>
       <c r="W14" s="126"/>
     </row>
-    <row r="15" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>183</v>
       </c>
@@ -12260,13 +12245,12 @@
         <v>DAOT</v>
       </c>
       <c r="E15" s="6"/>
-      <c r="F15" s="165">
+      <c r="F15" s="163">
         <f>'EB1'!O8/('EB1'!$D$8+'EB1'!$E$8+SUM('EB1'!$G$8:$J$8,'EB1'!$M$8,'EB1'!$L$8)+'EB1'!$O$8+'EB1'!$U$8)</f>
         <v>0</v>
       </c>
-      <c r="G15" s="166">
-        <f>IF(F15=0,20%,F15*(1+$G$8))</f>
-        <v>0.2</v>
+      <c r="G15" s="164">
+        <v>0</v>
       </c>
       <c r="H15" s="64">
         <v>1</v>
@@ -12282,7 +12266,7 @@
       <c r="V15" s="126"/>
       <c r="W15" s="126"/>
     </row>
-    <row r="16" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>183</v>
       </c>
@@ -12295,13 +12279,12 @@
         <v>DAOT</v>
       </c>
       <c r="E16" s="6"/>
-      <c r="F16" s="165">
+      <c r="F16" s="163">
         <f>'EB1'!U8/('EB1'!$D$8+'EB1'!$E$8+SUM('EB1'!$G$8:$J$8,'EB1'!$M$8,'EB1'!$L$8)+'EB1'!$O$8+'EB1'!$U$8)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="166">
-        <f>IF(F16=0,20%,F16*(1+$G$8))</f>
-        <v>0.2</v>
+      <c r="G16" s="164">
+        <v>0</v>
       </c>
       <c r="H16" s="64">
         <v>1</v>
@@ -12317,58 +12300,58 @@
       <c r="V16" s="126"/>
       <c r="W16" s="126"/>
     </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="J17" s="16"/>
       <c r="K17" s="16"/>
       <c r="L17" s="16"/>
       <c r="R17" s="19"/>
     </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="J18" s="16"/>
       <c r="K18" s="16"/>
       <c r="L18" s="16"/>
       <c r="R18" s="19"/>
     </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="F19" s="95"/>
       <c r="G19" s="95"/>
     </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="F20" s="110"/>
       <c r="G20" s="110"/>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
     </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B26" s="39"/>
       <c r="C26" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B27" s="61"/>
       <c r="C27" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
       <c r="F28" s="11"/>
       <c r="G28" s="11"/>
       <c r="N28" s="1"/>
     </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
       <c r="F29" s="11"/>
       <c r="G29" s="11"/>
       <c r="N29" s="1"/>
     </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:18" x14ac:dyDescent="0.25">
       <c r="F30" s="11"/>
       <c r="G30" s="11"/>
       <c r="N30" s="1"/>
     </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="N31" s="1"/>
     </row>
   </sheetData>
@@ -12383,29 +12366,29 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:R42"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="2.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" customWidth="1"/>
-    <col min="11" max="11" width="7.140625" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.44140625" customWidth="1"/>
+    <col min="11" max="11" width="7.109375" customWidth="1"/>
+    <col min="12" max="12" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="63" customWidth="1"/>
-    <col min="14" max="14" width="6.140625" customWidth="1"/>
-    <col min="15" max="15" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.140625" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="15" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="7" t="s">
         <v>73</v>
       </c>
@@ -12426,7 +12409,7 @@
       </c>
       <c r="H1" s="27"/>
     </row>
-    <row r="2" spans="2:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="9" t="str">
         <f>'EB1'!B6</f>
         <v>COM</v>
@@ -12462,7 +12445,7 @@
       <c r="Q2" s="122"/>
       <c r="R2" s="122"/>
     </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:18" x14ac:dyDescent="0.25">
       <c r="J3" s="123" t="s">
         <v>7</v>
       </c>
@@ -12491,7 +12474,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:18" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -12525,7 +12508,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="66"/>
@@ -12551,7 +12534,7 @@
       <c r="Q5" s="126"/>
       <c r="R5" s="126"/>
     </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="66"/>
@@ -12575,7 +12558,7 @@
       <c r="Q6" s="126"/>
       <c r="R6" s="126"/>
     </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="66"/>
@@ -12599,7 +12582,7 @@
       <c r="Q7" s="126"/>
       <c r="R7" s="126"/>
     </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="66"/>
@@ -12623,7 +12606,7 @@
       <c r="Q8" s="126"/>
       <c r="R8" s="126"/>
     </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="66"/>
@@ -12647,7 +12630,7 @@
       <c r="Q9" s="126"/>
       <c r="R9" s="126"/>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="66"/>
@@ -12675,11 +12658,11 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="L11" s="23"/>
       <c r="M11" s="24"/>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D12" s="4" t="s">
         <v>13</v>
       </c>
@@ -12697,7 +12680,7 @@
       <c r="Q12" s="126"/>
       <c r="R12" s="126"/>
     </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="17" t="s">
         <v>1</v>
       </c>
@@ -12747,7 +12730,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="2:18" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="15" t="s">
         <v>39</v>
       </c>
@@ -12797,7 +12780,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="2:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="14" t="s">
         <v>90</v>
       </c>
@@ -12824,7 +12807,7 @@
       <c r="Q15" s="128"/>
       <c r="R15" s="128"/>
     </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" t="str">
         <f>L16</f>
         <v>FTE-COMCOA</v>
@@ -12869,7 +12852,7 @@
       <c r="Q16" s="126"/>
       <c r="R16" s="126"/>
     </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" t="str">
         <f>L17</f>
         <v>FTE-COMGAS</v>
@@ -12912,7 +12895,7 @@
       <c r="Q17" s="126"/>
       <c r="R17" s="126"/>
     </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" t="str">
         <f>L18</f>
         <v>FTE-COMOIL</v>
@@ -12958,7 +12941,7 @@
       <c r="Q18" s="126"/>
       <c r="R18" s="126"/>
     </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C19" t="str">
         <f>'EB1'!$H$2</f>
         <v>KER</v>
@@ -12992,7 +12975,7 @@
       <c r="Q19" s="126"/>
       <c r="R19" s="126"/>
     </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C20" t="str">
         <f>'EB1'!$I$2</f>
         <v>LPG</v>
@@ -13026,7 +13009,7 @@
       <c r="Q20" s="126"/>
       <c r="R20" s="126"/>
     </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C21" t="str">
         <f>'EB1'!$J$2</f>
         <v>GSL</v>
@@ -13062,7 +13045,7 @@
       <c r="Q21" s="126"/>
       <c r="R21" s="126"/>
     </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C22" t="str">
         <f>'EB1'!$L$2</f>
         <v>HFO</v>
@@ -13076,7 +13059,7 @@
       <c r="H22" s="10"/>
       <c r="M22" s="19"/>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C23" t="str">
         <f>'EB1'!$M$2</f>
         <v>OPP</v>
@@ -13090,7 +13073,7 @@
       <c r="H23" s="10"/>
       <c r="M23" s="19"/>
     </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B24" t="str">
         <f>L19</f>
         <v>FTE-COMBIO</v>
@@ -13115,7 +13098,7 @@
       <c r="K24" s="23"/>
       <c r="M24" s="19"/>
     </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B25" t="str">
         <f>L20</f>
         <v>FTE-COMSOL</v>
@@ -13140,7 +13123,7 @@
       <c r="K25" s="23"/>
       <c r="M25" s="19"/>
     </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B26" s="5" t="str">
         <f>L21</f>
         <v>FTE-COMELC</v>
@@ -13167,7 +13150,7 @@
       <c r="K26" s="23"/>
       <c r="M26" s="19"/>
     </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
       <c r="G27" s="66"/>
@@ -13176,20 +13159,20 @@
       <c r="K27" s="23"/>
       <c r="M27" s="19"/>
     </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
       <c r="G28" s="66"/>
       <c r="H28" s="10"/>
       <c r="M28" s="19"/>
     </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
       <c r="G29" s="66"/>
       <c r="H29" s="10"/>
     </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B30" s="23"/>
       <c r="D30" s="23"/>
       <c r="E30" s="11"/>
@@ -13197,7 +13180,7 @@
       <c r="G30" s="66"/>
       <c r="H30" s="10"/>
     </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B31" s="23"/>
       <c r="D31" s="23"/>
       <c r="E31" s="11"/>
@@ -13205,7 +13188,7 @@
       <c r="G31" s="66"/>
       <c r="H31" s="10"/>
     </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B32" s="23"/>
       <c r="D32" s="23"/>
       <c r="E32" s="95"/>
@@ -13213,7 +13196,7 @@
       <c r="G32" s="66"/>
       <c r="H32" s="10"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B33" s="23"/>
       <c r="D33" s="23"/>
       <c r="E33" s="95"/>
@@ -13221,7 +13204,7 @@
       <c r="G33" s="66"/>
       <c r="H33" s="10"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="23"/>
       <c r="D34" s="23"/>
       <c r="E34" s="95"/>
@@ -13229,7 +13212,7 @@
       <c r="G34" s="66"/>
       <c r="H34" s="10"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="23"/>
       <c r="D35" s="23"/>
       <c r="E35" s="95"/>
@@ -13237,7 +13220,7 @@
       <c r="G35" s="66"/>
       <c r="H35" s="10"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="23"/>
       <c r="D36" s="23"/>
       <c r="E36" s="11"/>
@@ -13245,7 +13228,7 @@
       <c r="G36" s="66"/>
       <c r="H36" s="10"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B37" s="23"/>
       <c r="D37" s="23"/>
       <c r="E37" s="11"/>
@@ -13253,13 +13236,13 @@
       <c r="G37" s="66"/>
       <c r="H37" s="10"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B41" s="39"/>
       <c r="C41" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B42" s="61"/>
       <c r="C42" s="1" t="s">
         <v>150</v>
@@ -13276,32 +13259,32 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B1:U35"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.140625" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.109375" customWidth="1"/>
     <col min="10" max="10" width="2" customWidth="1"/>
-    <col min="11" max="11" width="11.5703125" customWidth="1"/>
+    <col min="11" max="11" width="11.5546875" customWidth="1"/>
     <col min="12" max="12" width="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.140625" customWidth="1"/>
-    <col min="15" max="15" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="77.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.7109375" customWidth="1"/>
-    <col min="18" max="18" width="11.7109375" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" customWidth="1"/>
-    <col min="20" max="20" width="13.85546875" customWidth="1"/>
-    <col min="21" max="21" width="8.42578125" customWidth="1"/>
+    <col min="13" max="13" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.109375" customWidth="1"/>
+    <col min="15" max="15" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="77.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.6640625" customWidth="1"/>
+    <col min="18" max="18" width="11.6640625" customWidth="1"/>
+    <col min="19" max="19" width="13.44140625" customWidth="1"/>
+    <col min="20" max="20" width="13.88671875" customWidth="1"/>
+    <col min="21" max="21" width="8.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:21" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="7" t="s">
         <v>73</v>
       </c>
@@ -13324,7 +13307,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:21" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B2" s="9" t="str">
         <f>'EB1'!B6</f>
         <v>COM</v>
@@ -13363,7 +13346,7 @@
       <c r="T2" s="122"/>
       <c r="U2" s="122"/>
     </row>
-    <row r="3" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:21" x14ac:dyDescent="0.25">
       <c r="M3" s="123" t="s">
         <v>7</v>
       </c>
@@ -13392,7 +13375,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:21" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -13426,7 +13409,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -13453,7 +13436,7 @@
       <c r="T5" s="122"/>
       <c r="U5" s="122"/>
     </row>
-    <row r="6" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
@@ -13478,7 +13461,7 @@
       <c r="T6" s="122"/>
       <c r="U6" s="122"/>
     </row>
-    <row r="7" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -13503,7 +13486,7 @@
       <c r="T7" s="122"/>
       <c r="U7" s="122"/>
     </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
       <c r="M8" s="126" t="s">
         <v>106</v>
       </c>
@@ -13525,7 +13508,7 @@
       <c r="T8" s="126"/>
       <c r="U8" s="126"/>
     </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:21" x14ac:dyDescent="0.25">
       <c r="D10" s="4" t="s">
         <v>13</v>
       </c>
@@ -13545,7 +13528,7 @@
       <c r="T10" s="126"/>
       <c r="U10" s="126"/>
     </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B11" s="17" t="s">
         <v>1</v>
       </c>
@@ -13602,7 +13585,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="2:21" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:21" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="15" t="s">
         <v>39</v>
       </c>
@@ -13659,7 +13642,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="2:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:21" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="14" t="s">
         <v>90</v>
       </c>
@@ -13689,7 +13672,7 @@
       <c r="T13" s="125"/>
       <c r="U13" s="125"/>
     </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B14" t="str">
         <f>O14</f>
         <v>CSCESOL</v>
@@ -13718,7 +13701,7 @@
       <c r="I14" s="39">
         <v>15</v>
       </c>
-      <c r="K14" s="149">
+      <c r="K14" s="147">
         <f>E14*G14*H14</f>
         <v>0</v>
       </c>
@@ -13741,11 +13724,11 @@
       <c r="R14" s="126" t="s">
         <v>119</v>
       </c>
-      <c r="S14" s="157"/>
+      <c r="S14" s="155"/>
       <c r="T14" s="126"/>
       <c r="U14" s="126"/>
     </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="str">
         <f t="shared" ref="B15:B18" si="2">O15</f>
         <v>CSCEELC</v>
@@ -13775,7 +13758,7 @@
         <v>15</v>
       </c>
       <c r="J15" s="5"/>
-      <c r="K15" s="150">
+      <c r="K15" s="148">
         <f>E15*G15*H15</f>
         <v>6.6512296105200015</v>
       </c>
@@ -13802,7 +13785,7 @@
       <c r="T15" s="126"/>
       <c r="U15" s="126"/>
     </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B16" s="105" t="str">
         <f t="shared" si="2"/>
         <v>CAPEELC</v>
@@ -13832,7 +13815,7 @@
         <v>5</v>
       </c>
       <c r="J16" s="105"/>
-      <c r="K16" s="151">
+      <c r="K16" s="149">
         <f t="shared" ref="K16:K18" si="4">E16*G16*H16</f>
         <v>3.0232861866000005</v>
       </c>
@@ -13860,7 +13843,7 @@
       <c r="T16" s="129"/>
       <c r="U16" s="129"/>
     </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B17" t="str">
         <f t="shared" si="2"/>
         <v>COTEOIL</v>
@@ -13889,7 +13872,7 @@
       <c r="I17" s="39">
         <v>10</v>
       </c>
-      <c r="K17" s="149">
+      <c r="K17" s="147">
         <f t="shared" si="4"/>
         <v>5.43316179312</v>
       </c>
@@ -13917,7 +13900,7 @@
       <c r="T17" s="126"/>
       <c r="U17" s="126"/>
     </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B18" t="str">
         <f t="shared" si="2"/>
         <v>COTEELC</v>
@@ -13946,7 +13929,7 @@
       <c r="I18" s="39">
         <v>10</v>
       </c>
-      <c r="K18" s="149">
+      <c r="K18" s="147">
         <f t="shared" si="4"/>
         <v>2.4186289492799995</v>
       </c>
@@ -13974,61 +13957,61 @@
       <c r="T18" s="126"/>
       <c r="U18" s="126"/>
     </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
       <c r="E19" s="6"/>
       <c r="F19" s="16"/>
       <c r="G19" s="16"/>
       <c r="H19" s="16"/>
     </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
       <c r="E20" s="6"/>
       <c r="F20" s="16"/>
       <c r="G20" s="16"/>
       <c r="H20" s="16"/>
       <c r="P20" s="19"/>
     </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
       <c r="E21" s="6"/>
       <c r="F21" s="16"/>
       <c r="G21" s="16"/>
       <c r="H21" s="16"/>
       <c r="P21" s="19"/>
     </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
       <c r="E22" s="6"/>
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
       <c r="H22" s="16"/>
       <c r="P22" s="19"/>
     </row>
-    <row r="30" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B30" s="39"/>
       <c r="C30" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="31" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B31" s="61"/>
       <c r="C31" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="32" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:21" x14ac:dyDescent="0.25">
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
     </row>
-    <row r="33" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
     </row>
-    <row r="34" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
     </row>
-    <row r="35" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="35" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
@@ -14044,29 +14027,29 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B1:R38"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="2.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" customWidth="1"/>
-    <col min="11" max="11" width="7.140625" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.44140625" customWidth="1"/>
+    <col min="11" max="11" width="7.109375" customWidth="1"/>
+    <col min="12" max="12" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="63" customWidth="1"/>
-    <col min="14" max="14" width="6.140625" customWidth="1"/>
-    <col min="15" max="15" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.140625" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="15" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="7" t="s">
         <v>73</v>
       </c>
@@ -14087,7 +14070,7 @@
       </c>
       <c r="H1" s="27"/>
     </row>
-    <row r="2" spans="2:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="9" t="str">
         <f>'EB1'!B5</f>
         <v>RSD</v>
@@ -14123,7 +14106,7 @@
       <c r="Q2" s="122"/>
       <c r="R2" s="122"/>
     </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:18" x14ac:dyDescent="0.25">
       <c r="J3" s="123" t="s">
         <v>7</v>
       </c>
@@ -14152,7 +14135,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:18" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -14186,7 +14169,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="66"/>
@@ -14212,7 +14195,7 @@
       <c r="Q5" s="126"/>
       <c r="R5" s="126"/>
     </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="66"/>
@@ -14236,7 +14219,7 @@
       <c r="Q6" s="126"/>
       <c r="R6" s="126"/>
     </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="66"/>
@@ -14260,7 +14243,7 @@
       <c r="Q7" s="126"/>
       <c r="R7" s="126"/>
     </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="66"/>
@@ -14284,7 +14267,7 @@
       <c r="Q8" s="126"/>
       <c r="R8" s="126"/>
     </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="66"/>
@@ -14308,7 +14291,7 @@
       <c r="Q9" s="126"/>
       <c r="R9" s="126"/>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="66"/>
@@ -14336,18 +14319,18 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="66"/>
       <c r="H11" s="10"/>
       <c r="M11" s="19"/>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="L12" s="23"/>
       <c r="M12" s="24"/>
     </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D13" s="4" t="s">
         <v>13</v>
       </c>
@@ -14365,7 +14348,7 @@
       <c r="Q13" s="126"/>
       <c r="R13" s="126"/>
     </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14" s="17" t="s">
         <v>1</v>
       </c>
@@ -14415,7 +14398,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="2:18" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="15" t="s">
         <v>39</v>
       </c>
@@ -14465,7 +14448,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="2:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="14" t="s">
         <v>90</v>
       </c>
@@ -14492,7 +14475,7 @@
       <c r="Q16" s="128"/>
       <c r="R16" s="128"/>
     </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" t="str">
         <f>L17</f>
         <v>FTE-RSDCOA</v>
@@ -14537,7 +14520,7 @@
       <c r="Q17" s="126"/>
       <c r="R17" s="126"/>
     </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" t="str">
         <f>L18</f>
         <v>FTE-RSDGAS</v>
@@ -14580,7 +14563,7 @@
       <c r="Q18" s="126"/>
       <c r="R18" s="126"/>
     </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B19" t="str">
         <f>L19</f>
         <v>FTE-RSDOIL</v>
@@ -14625,7 +14608,7 @@
       <c r="Q19" s="126"/>
       <c r="R19" s="126"/>
     </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C20" t="str">
         <f>'EB1'!$H$2</f>
         <v>KER</v>
@@ -14659,7 +14642,7 @@
       <c r="Q20" s="126"/>
       <c r="R20" s="126"/>
     </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C21" t="str">
         <f>'EB1'!$I$2</f>
         <v>LPG</v>
@@ -14693,7 +14676,7 @@
       <c r="Q21" s="126"/>
       <c r="R21" s="126"/>
     </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C22" t="str">
         <f>'EB1'!$J$2</f>
         <v>GSL</v>
@@ -14729,7 +14712,7 @@
       <c r="Q22" s="126"/>
       <c r="R22" s="126"/>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C23" t="str">
         <f>'EB1'!$L$2</f>
         <v>HFO</v>
@@ -14743,7 +14726,7 @@
       <c r="H23" s="10"/>
       <c r="M23" s="19"/>
     </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C24" t="str">
         <f>'EB1'!$M$2</f>
         <v>OPP</v>
@@ -14757,7 +14740,7 @@
       <c r="H24" s="10"/>
       <c r="M24" s="19"/>
     </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B25" t="str">
         <f>L20</f>
         <v>FTE-RSDBIO</v>
@@ -14782,7 +14765,7 @@
       <c r="K25" s="23"/>
       <c r="M25" s="19"/>
     </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B26" t="str">
         <f>L21</f>
         <v>FTE-RSDSOL</v>
@@ -14807,7 +14790,7 @@
       <c r="K26" s="23"/>
       <c r="M26" s="19"/>
     </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B27" t="str">
         <f>L22</f>
         <v>FTE-RSDELC</v>
@@ -14834,7 +14817,7 @@
       <c r="K27" s="23"/>
       <c r="M27" s="19"/>
     </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
       <c r="G28" s="66"/>
@@ -14843,20 +14826,20 @@
       <c r="K28" s="23"/>
       <c r="M28" s="19"/>
     </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
       <c r="G29" s="66"/>
       <c r="H29" s="10"/>
       <c r="M29" s="19"/>
     </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="66"/>
       <c r="H30" s="10"/>
     </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B31" s="39"/>
       <c r="C31" s="1" t="s">
         <v>149</v>
@@ -14867,7 +14850,7 @@
       <c r="G31" s="66"/>
       <c r="H31" s="10"/>
     </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B32" s="61"/>
       <c r="C32" s="1" t="s">
         <v>150</v>
@@ -14878,7 +14861,7 @@
       <c r="G32" s="66"/>
       <c r="H32" s="10"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B33" s="23"/>
       <c r="D33" s="23"/>
       <c r="E33" s="95"/>
@@ -14886,7 +14869,7 @@
       <c r="G33" s="66"/>
       <c r="H33" s="10"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="23"/>
       <c r="D34" s="23"/>
       <c r="E34" s="95"/>
@@ -14894,7 +14877,7 @@
       <c r="G34" s="66"/>
       <c r="H34" s="10"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="23"/>
       <c r="D35" s="23"/>
       <c r="E35" s="95"/>
@@ -14902,7 +14885,7 @@
       <c r="G35" s="66"/>
       <c r="H35" s="10"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="23"/>
       <c r="D36" s="23"/>
       <c r="E36" s="95"/>
@@ -14910,7 +14893,7 @@
       <c r="G36" s="66"/>
       <c r="H36" s="10"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B37" s="23"/>
       <c r="D37" s="23"/>
       <c r="E37" s="11"/>
@@ -14918,7 +14901,7 @@
       <c r="G37" s="66"/>
       <c r="H37" s="10"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B38" s="23"/>
       <c r="D38" s="23"/>
       <c r="E38" s="11"/>
@@ -14937,32 +14920,32 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="B1:U35"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.140625" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.109375" customWidth="1"/>
     <col min="10" max="10" width="2" customWidth="1"/>
-    <col min="11" max="11" width="11.5703125" customWidth="1"/>
+    <col min="11" max="11" width="11.5546875" customWidth="1"/>
     <col min="12" max="12" width="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.140625" customWidth="1"/>
-    <col min="15" max="15" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="77.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.7109375" customWidth="1"/>
-    <col min="18" max="18" width="11.7109375" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" customWidth="1"/>
-    <col min="20" max="20" width="13.85546875" customWidth="1"/>
-    <col min="21" max="21" width="8.42578125" customWidth="1"/>
+    <col min="13" max="13" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.109375" customWidth="1"/>
+    <col min="15" max="15" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="77.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.6640625" customWidth="1"/>
+    <col min="18" max="18" width="11.6640625" customWidth="1"/>
+    <col min="19" max="19" width="13.44140625" customWidth="1"/>
+    <col min="20" max="20" width="13.88671875" customWidth="1"/>
+    <col min="21" max="21" width="8.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:21" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="7" t="s">
         <v>73</v>
       </c>
@@ -14985,7 +14968,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:21" ht="31.2" x14ac:dyDescent="0.3">
       <c r="B2" s="9" t="str">
         <f>'EB1'!B5</f>
         <v>RSD</v>
@@ -15024,7 +15007,7 @@
       <c r="T2" s="122"/>
       <c r="U2" s="122"/>
     </row>
-    <row r="3" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:21" x14ac:dyDescent="0.25">
       <c r="M3" s="123" t="s">
         <v>7</v>
       </c>
@@ -15053,7 +15036,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:21" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -15087,7 +15070,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -15114,7 +15097,7 @@
       <c r="T5" s="122"/>
       <c r="U5" s="122"/>
     </row>
-    <row r="6" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
@@ -15139,7 +15122,7 @@
       <c r="T6" s="122"/>
       <c r="U6" s="122"/>
     </row>
-    <row r="7" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -15164,7 +15147,7 @@
       <c r="T7" s="122"/>
       <c r="U7" s="122"/>
     </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
       <c r="M8" s="126" t="s">
         <v>106</v>
       </c>
@@ -15186,7 +15169,7 @@
       <c r="T8" s="126"/>
       <c r="U8" s="126"/>
     </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:21" x14ac:dyDescent="0.25">
       <c r="D10" s="4" t="s">
         <v>13</v>
       </c>
@@ -15206,7 +15189,7 @@
       <c r="T10" s="126"/>
       <c r="U10" s="126"/>
     </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B11" s="17" t="s">
         <v>1</v>
       </c>
@@ -15263,7 +15246,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="2:21" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:21" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="15" t="s">
         <v>39</v>
       </c>
@@ -15320,7 +15303,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="2:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:21" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="14" t="s">
         <v>90</v>
       </c>
@@ -15350,7 +15333,7 @@
       <c r="T13" s="125"/>
       <c r="U13" s="125"/>
     </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="str">
         <f t="shared" ref="B14:B18" si="0">O14</f>
         <v>RSCEELC</v>
@@ -15379,7 +15362,7 @@
       <c r="I14" s="104">
         <v>15</v>
       </c>
-      <c r="K14" s="150">
+      <c r="K14" s="148">
         <f t="shared" ref="K14:K16" si="3">E14*G14*H14</f>
         <v>6.1537268203200002</v>
       </c>
@@ -15406,7 +15389,7 @@
       <c r="T14" s="126"/>
       <c r="U14" s="126"/>
     </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B15" s="105" t="str">
         <f t="shared" si="0"/>
         <v>RAPEELC</v>
@@ -15435,7 +15418,7 @@
       <c r="I15" s="108">
         <v>5</v>
       </c>
-      <c r="K15" s="151">
+      <c r="K15" s="149">
         <f t="shared" si="3"/>
         <v>5.3845109677799998</v>
       </c>
@@ -15463,7 +15446,7 @@
       <c r="T15" s="129"/>
       <c r="U15" s="129"/>
     </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B16" t="str">
         <f t="shared" si="0"/>
         <v>ROTEOIL</v>
@@ -15492,7 +15475,7 @@
       <c r="I16" s="39">
         <v>10</v>
       </c>
-      <c r="K16" s="149">
+      <c r="K16" s="147">
         <f t="shared" si="3"/>
         <v>8.8662481956000008</v>
       </c>
@@ -15520,7 +15503,7 @@
       <c r="T16" s="126"/>
       <c r="U16" s="126"/>
     </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B17" t="str">
         <f t="shared" si="0"/>
         <v>ROTEBIO</v>
@@ -15549,7 +15532,7 @@
       <c r="I17" s="39">
         <v>10</v>
       </c>
-      <c r="K17" s="149">
+      <c r="K17" s="147">
         <f>E17*G17*H17</f>
         <v>29.902180028400004</v>
       </c>
@@ -15577,7 +15560,7 @@
       <c r="T17" s="126"/>
       <c r="U17" s="126"/>
     </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B18" t="str">
         <f t="shared" si="0"/>
         <v>ROTEELC</v>
@@ -15606,7 +15589,7 @@
       <c r="I18" s="39">
         <v>10</v>
       </c>
-      <c r="K18" s="149">
+      <c r="K18" s="147">
         <f>E18*G18*H18</f>
         <v>3.8460792627</v>
       </c>
@@ -15634,67 +15617,67 @@
       <c r="T18" s="126"/>
       <c r="U18" s="126"/>
     </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
       <c r="E19" s="6"/>
       <c r="F19" s="16"/>
       <c r="G19" s="16"/>
       <c r="H19" s="16"/>
     </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
       <c r="E20" s="6"/>
       <c r="F20" s="16"/>
       <c r="G20" s="16"/>
       <c r="H20" s="16"/>
       <c r="P20" s="19"/>
     </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
       <c r="E21" s="6"/>
       <c r="F21" s="16"/>
       <c r="G21" s="16"/>
       <c r="H21" s="16"/>
       <c r="P21" s="19"/>
     </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
       <c r="E22" s="6"/>
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
       <c r="H22" s="16"/>
       <c r="P22" s="19"/>
     </row>
-    <row r="24" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:21" x14ac:dyDescent="0.25">
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
       <c r="G25" s="1"/>
     </row>
-    <row r="30" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B30" s="39"/>
       <c r="C30" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="31" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B31" s="61"/>
       <c r="C31" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="32" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:21" x14ac:dyDescent="0.25">
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
     </row>
-    <row r="33" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
     </row>
-    <row r="34" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
     </row>
-    <row r="35" spans="10:12" x14ac:dyDescent="0.2">
+    <row r="35" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
@@ -15710,20 +15693,20 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="B1:K32"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" customWidth="1"/>
     <col min="6" max="6" width="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5703125" customWidth="1"/>
-    <col min="9" max="9" width="10.28515625" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5546875" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="7" t="s">
         <v>73</v>
       </c>
@@ -15737,7 +15720,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="9" t="s">
         <v>83</v>
       </c>
@@ -15748,7 +15731,7 @@
         <v>PJ</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C5" s="3" t="s">
         <v>13</v>
       </c>
@@ -15759,7 +15742,7 @@
       </c>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>80</v>
       </c>
@@ -15785,7 +15768,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="7" spans="2:11" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B7" s="15" t="s">
         <v>81</v>
       </c>
@@ -15807,7 +15790,7 @@
       <c r="I7" s="15"/>
       <c r="J7" s="15"/>
     </row>
-    <row r="8" spans="2:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:11" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="14" t="s">
         <v>90</v>
       </c>
@@ -15824,7 +15807,7 @@
       <c r="I8" s="14"/>
       <c r="J8" s="15"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" s="25" t="s">
         <v>35</v>
       </c>
@@ -15853,7 +15836,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>35</v>
       </c>
@@ -15882,7 +15865,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>35</v>
       </c>
@@ -15911,7 +15894,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>35</v>
       </c>
@@ -15940,7 +15923,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>35</v>
       </c>
@@ -15969,7 +15952,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
         <v>35</v>
       </c>
@@ -15998,7 +15981,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
         <v>35</v>
       </c>
@@ -16028,7 +16011,7 @@
       </c>
       <c r="K15" s="16"/>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
         <v>35</v>
       </c>
@@ -16057,7 +16040,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
         <v>35</v>
       </c>
@@ -16086,7 +16069,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G18" s="1" t="s">
         <v>123</v>
       </c>
@@ -16101,7 +16084,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G19" s="1" t="s">
         <v>123</v>
       </c>
@@ -16116,7 +16099,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G20" s="26" t="s">
         <v>123</v>
       </c>
@@ -16131,7 +16114,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G21" s="1" t="s">
         <v>123</v>
       </c>
@@ -16146,7 +16129,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G22" s="1" t="s">
         <v>123</v>
       </c>
@@ -16161,7 +16144,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G23" s="1" t="s">
         <v>123</v>
       </c>
@@ -16176,7 +16159,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G24" s="26" t="s">
         <v>123</v>
       </c>
@@ -16191,7 +16174,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G25" s="1" t="s">
         <v>123</v>
       </c>
@@ -16206,7 +16189,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G26" s="1" t="s">
         <v>123</v>
       </c>
@@ -16221,7 +16204,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G27" s="1" t="s">
         <v>123</v>
       </c>
@@ -16236,7 +16219,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G28" s="26" t="s">
         <v>123</v>
       </c>
@@ -16251,7 +16234,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G29" s="1" t="s">
         <v>123</v>
       </c>
@@ -16266,7 +16249,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="39"/>
       <c r="C30" s="1" t="s">
         <v>149</v>
@@ -16285,7 +16268,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="61"/>
       <c r="C31" s="1" t="s">
         <v>150</v>
@@ -16304,7 +16287,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G32" s="26" t="s">
         <v>123</v>
       </c>
